--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$S$479</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$S$480</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$219</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25">
@@ -1101,7 +1101,7 @@
     <row r="37">
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-1 (FRS_BRD01_NEW_BUSINESS.md). 93 FRs, 122 BRD IDs, 237 test conditions, 10 scenarios, 475 test cases (206 positive, 269 negative), 311 with an automation reference.</t>
+          <t>Source: FRS BRD-1 (FRS_BRD01_NEW_BUSINESS.md). 93 FRs, 122 BRD IDs, 237 test conditions, 10 scenarios, 476 test cases (206 positive, 270 negative), 311 with an automation reference.</t>
         </is>
       </c>
     </row>
@@ -15738,7 +15738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S479"/>
+  <dimension ref="A1:S480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -51116,16 +51116,17 @@
 MSG-NB-101: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
 MSG-NB-102: "Select the client and the product" (QUOTATION_INCOMPLETE)
 MSG-NB-103: "Select the product" (QUOTATION_INCOMPLETE)
-MSG-NB-104: "Quotation &lt;quotation no&gt; is &lt;status&gt;" (QUOTATION_NOT_EDITABLE)
+MSG-NB-104: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
 MSG-NB-105: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
 MSG-NB-106: "Add at least one risk item" (QUOTATION_NO_ITEMS)
 MSG-NB-107: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
 MSG-NB-108: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
-MSG-NB-109: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
-MSG-NB-110: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
-MSG-NB-111: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-112: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
-MSG-NB-113: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-109: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
+MSG-NB-110: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
+MSG-NB-111: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
+MSG-NB-112: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-113: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
+MSG-NB-114: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M444" s="12" t="inlineStr">
@@ -51201,8 +51202,8 @@
       <c r="L445" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-115: "Enter the item rate between 0 and 100"
-MSG-NB-116: "Explain why the scheme rate cannot be used"</t>
+MSG-NB-116: "Enter the item rate between 0 and 100"
+MSG-NB-117: "Explain why the scheme rate cannot be used"</t>
         </is>
       </c>
       <c r="M445" s="12" t="inlineStr">
@@ -51278,19 +51279,19 @@
       <c r="L446" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-123: "Select the client or prospect"
-MSG-NB-124: "Select the product"
-MSG-NB-125: "The period end must be after the period start"
-MSG-NB-126: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
-MSG-NB-127: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-128: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
-MSG-NB-129: "Complete the PRF header" (PRF_INCOMPLETE)
-MSG-NB-130: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
-MSG-NB-131: "PRF &lt;prf no&gt; cannot be changed while &lt;status&gt;" (PRF_NOT_EDITABLE)
-MSG-NB-132: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
-MSG-NB-133: "The period end must be after the period start" (PRF_PERIOD_INVALID)
-MSG-NB-134: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
-MSG-NB-135: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-124: "Select the client or prospect"
+MSG-NB-125: "Select the product"
+MSG-NB-126: "The period end must be after the period start"
+MSG-NB-127: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
+MSG-NB-128: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-129: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
+MSG-NB-130: "Complete the PRF header" (PRF_INCOMPLETE)
+MSG-NB-131: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
+MSG-NB-132: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
+MSG-NB-133: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
+MSG-NB-134: "The period end must be after the period start" (PRF_PERIOD_INVALID)
+MSG-NB-135: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
+MSG-NB-136: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M446" s="12" t="inlineStr">
@@ -51366,26 +51367,27 @@
       <c r="L447" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-145: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-146: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-147: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
-MSG-NB-148: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
-MSG-NB-149: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
-MSG-NB-150: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
-MSG-NB-151: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
-MSG-NB-152: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
-MSG-NB-153: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
-MSG-NB-154: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
-MSG-NB-155: "The chosen terms are gone" (PS_TERMS_MISSING)
-MSG-NB-156: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
-MSG-NB-157: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
-MSG-NB-158: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
-MSG-NB-159: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
-MSG-NB-160: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
-MSG-NB-161: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
-MSG-NB-162: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
-MSG-NB-163: "No insurer terms have been received" (TERMS_NONE)
-MSG-NB-164: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
+MSG-NB-140: "Enter the premium quoted"
+MSG-NB-147: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-148: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-149: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
+MSG-NB-150: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
+MSG-NB-151: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
+MSG-NB-152: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
+MSG-NB-153: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
+MSG-NB-154: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
+MSG-NB-155: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
+MSG-NB-156: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
+MSG-NB-157: "The chosen terms are gone" (PS_TERMS_MISSING)
+MSG-NB-158: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
+MSG-NB-159: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
+MSG-NB-160: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
+MSG-NB-161: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
+MSG-NB-162: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
+MSG-NB-163: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
+MSG-NB-164: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
+MSG-NB-165: "No insurer terms have been received" (TERMS_NONE)
+MSG-NB-166: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
         </is>
       </c>
       <c r="M447" s="12" t="inlineStr">
@@ -51461,12 +51463,12 @@
       <c r="L448" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-167: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_ACTIVE)
-MSG-NB-168: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-169: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-170: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
-MSG-NB-171: "Enter the Free First Year start" (FFY_START_REQUIRED)
-MSG-NB-172: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
+MSG-NB-169: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
+MSG-NB-170: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-171: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-172: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
+MSG-NB-173: "Enter the Free First Year start" (FFY_START_REQUIRED)
+MSG-NB-174: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
         </is>
       </c>
       <c r="M448" s="12" t="inlineStr">
@@ -51542,17 +51544,17 @@
       <c r="L449" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-175: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-176: "Account &lt;arn&gt; is &lt;status&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
-MSG-NB-177: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
-MSG-NB-178: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
-MSG-NB-179: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-180: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-181: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
-MSG-NB-182: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
-MSG-NB-183: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
-MSG-NB-184: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
-MSG-NB-185: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
+MSG-NB-177: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-178: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
+MSG-NB-179: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
+MSG-NB-180: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
+MSG-NB-181: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-182: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-183: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
+MSG-NB-184: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
+MSG-NB-185: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
+MSG-NB-186: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
+MSG-NB-187: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
         </is>
       </c>
       <c r="M449" s="12" t="inlineStr">
@@ -51628,24 +51630,28 @@
       <c r="L450" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-188: "Duplicate risks: &lt;list&gt;"
-MSG-NB-189: "Not ready to submit: &lt;list&gt;"
-MSG-NB-190: "These risks are already on account &lt;list&gt; — open the existing account instead of creating a new one."
-MSG-NB-191: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
-MSG-NB-192: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
-MSG-NB-193: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
-MSG-NB-194: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
-MSG-NB-195: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
-MSG-NB-196: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
-MSG-NB-197: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-198: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
-MSG-NB-199: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-200: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
-MSG-NB-201: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
-MSG-NB-202: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
-MSG-NB-203: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
-MSG-NB-204: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-205: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-189: "Choose the client and product to save the draft."
+MSG-NB-191: "Duplicate risks: &lt;list&gt;"
+MSG-NB-192: "Not ready to submit: &lt;list&gt;"
+MSG-NB-193: "The draft is not saved yet: click Save Draft to check it before submission."
+MSG-NB-194: "The draft was not saved: correct what the message above describes, then save the draft again."
+MSG-NB-195: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
+MSG-NB-196: "These risks are already on account &lt;list&gt; — open the existing account instead of creating a new one."
+MSG-NB-197: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
+MSG-NB-198: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
+MSG-NB-199: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
+MSG-NB-200: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
+MSG-NB-201: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
+MSG-NB-202: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
+MSG-NB-203: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-204: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
+MSG-NB-205: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-206: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
+MSG-NB-207: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
+MSG-NB-208: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
+MSG-NB-209: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
+MSG-NB-210: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-211: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M450" s="12" t="inlineStr">
@@ -51721,9 +51727,9 @@
       <c r="L451" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-210: "Account &lt;arn&gt; is &lt;status&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-211: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
-MSG-NB-212: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
+MSG-NB-216: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-217: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
+MSG-NB-218: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
         </is>
       </c>
       <c r="M451" s="12" t="inlineStr">
@@ -51799,15 +51805,15 @@
       <c r="L452" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-215: "Record Hold Cover Confirmation"
-MSG-NB-216: "Record Hold Cover Decline"
-MSG-NB-217: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
-MSG-NB-218: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
-MSG-NB-219: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
-MSG-NB-220: "A hold cover is requested while the account is being placed, not &lt;status&gt;" (HOLD_COVER_NOT_ALLOWED)
-MSG-NB-221: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
-MSG-NB-222: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
-MSG-NB-223: "Choose the insurer on the account first" (INSURER_NOT_SET)</t>
+MSG-NB-221: "Record Hold Cover Confirmation"
+MSG-NB-222: "Record Hold Cover Decline"
+MSG-NB-223: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
+MSG-NB-224: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
+MSG-NB-225: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
+MSG-NB-226: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
+MSG-NB-227: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
+MSG-NB-228: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
+MSG-NB-229: "Choose the insurer on the account first" (INSURER_NOT_SET)</t>
         </is>
       </c>
       <c r="M452" s="12" t="inlineStr">
@@ -51883,20 +51889,20 @@
       <c r="L453" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-232: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-233: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
-MSG-NB-234: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
-MSG-NB-235: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
-MSG-NB-236: "PlacementSlip not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-237: "The account is &lt;status&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
-MSG-NB-238: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
-MSG-NB-239: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
-MSG-NB-240: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
-MSG-NB-241: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
-MSG-NB-242: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
-MSG-NB-243: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
-MSG-NB-244: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
-MSG-NB-245: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
+MSG-NB-238: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-239: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
+MSG-NB-240: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
+MSG-NB-241: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
+MSG-NB-242: "PlacementSlip not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-243: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
+MSG-NB-244: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
+MSG-NB-245: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
+MSG-NB-246: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
+MSG-NB-247: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
+MSG-NB-248: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
+MSG-NB-249: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
+MSG-NB-250: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
+MSG-NB-251: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
         </is>
       </c>
       <c r="M453" s="12" t="inlineStr">
@@ -51972,10 +51978,10 @@
       <c r="L454" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-249: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
-MSG-NB-250: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
-MSG-NB-251: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
-MSG-NB-252: "BillingBatch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-255: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
+MSG-NB-256: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
+MSG-NB-257: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
+MSG-NB-258: "BillingBatch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M454" s="12" t="inlineStr">
@@ -52051,19 +52057,19 @@
       <c r="L455" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-254: "&lt;arn&gt; is &lt;status&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-255: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
-MSG-NB-256: "BillingBatch not found: &lt;batch id&gt;" (NOT_FOUND)
-MSG-NB-257: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
-MSG-NB-258: "PaymentReport not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-259: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
-MSG-NB-260: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
-MSG-NB-261: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
-MSG-NB-262: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
-MSG-NB-263: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-264: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-265: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
-MSG-NB-266: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
+MSG-NB-260: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-261: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
+MSG-NB-262: "BillingBatch not found: &lt;batch id&gt;" (NOT_FOUND)
+MSG-NB-263: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
+MSG-NB-264: "PaymentReport not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-265: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
+MSG-NB-266: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
+MSG-NB-267: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
+MSG-NB-268: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
+MSG-NB-269: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-270: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
+MSG-NB-272: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
         </is>
       </c>
       <c r="M455" s="12" t="inlineStr">
@@ -52139,14 +52145,14 @@
       <c r="L456" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-269: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
-MSG-NB-270: "Account &lt;arn&gt; is &lt;status&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
-MSG-NB-271: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
-MSG-NB-272: "The e-policy &lt;file name&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)
-MSG-NB-273: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
-MSG-NB-274: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-275: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
-MSG-NB-276: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-275: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
+MSG-NB-276: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
+MSG-NB-277: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
+MSG-NB-278: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
+MSG-NB-279: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
+MSG-NB-280: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-281: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
+MSG-NB-282: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M456" s="12" t="inlineStr">
@@ -52222,12 +52228,12 @@
       <c r="L457" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-277: "Check before confirming &lt;list&gt;"
-MSG-NB-279: "Enter one policy number per policy year."
-MSG-NB-283: "Rejected by &lt;user&gt;: &lt;reject reason&gt;"
-MSG-NB-284: "The policy numbers must be different."
-MSG-NB-285: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
-MSG-NB-286: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
+MSG-NB-283: "Check before confirming &lt;list&gt;"
+MSG-NB-285: "Enter one policy number per policy year."
+MSG-NB-289: "Rejected by &lt;user&gt;: &lt;reject reason&gt;"
+MSG-NB-290: "The policy numbers must be different."
+MSG-NB-291: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
+MSG-NB-292: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
         </is>
       </c>
       <c r="M457" s="12" t="inlineStr">
@@ -52303,10 +52309,10 @@
       <c r="L458" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-289: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
-MSG-NB-290: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
-MSG-NB-291: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
-MSG-NB-292: "InsuranceAdvice not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-295: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
+MSG-NB-296: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
+MSG-NB-297: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
+MSG-NB-298: "InsuranceAdvice not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M458" s="12" t="inlineStr">
@@ -52382,8 +52388,8 @@
       <c r="L459" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-295: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
-MSG-NB-296: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
+MSG-NB-301: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
+MSG-NB-302: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
         </is>
       </c>
       <c r="M459" s="12" t="inlineStr">
@@ -52459,20 +52465,22 @@
       <c r="L460" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-299: "A negative endorsement reduces the sum insured (enter a minus)"
-MSG-NB-300: "A positive endorsement increases the sum insured"
-MSG-NB-301: "Choose the reason"
-MSG-NB-302: "Describe the cancellation"
-MSG-NB-303: "Describe the change"
-MSG-NB-304: "Enter a rate of zero or more, or leave it blank"
-MSG-NB-305: "Enter the cancellation date"
-MSG-NB-306: "Enter the change of the sum insured"
-MSG-NB-307: "Enter the effective date"
-MSG-NB-309: "No queued account to book" (BATCH_EMPTY)
-MSG-NB-310: "Select at least one account to book" (BATCH_EMPTY)
-MSG-NB-311: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-312: "BookingQueue not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-313: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
+MSG-NB-305: "A negative endorsement reduces the sum insured (enter a minus)"
+MSG-NB-306: "A positive endorsement increases the sum insured"
+MSG-NB-307: "Choose the reason"
+MSG-NB-308: "Describe the cancellation"
+MSG-NB-309: "Describe the change"
+MSG-NB-310: "Enter a booking date that is not in the future"
+MSG-NB-311: "Enter a rate of zero or more, or leave it blank"
+MSG-NB-312: "Enter the cancellation date"
+MSG-NB-313: "Enter the change of the sum insured"
+MSG-NB-314: "Enter the effective date"
+MSG-NB-316: "The booking date cannot be in the future"
+MSG-NB-317: "No queued account to book" (BATCH_EMPTY)
+MSG-NB-318: "Select at least one account to book" (BATCH_EMPTY)
+MSG-NB-319: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-320: "BookingQueue not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-321: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
         </is>
       </c>
       <c r="M460" s="12" t="inlineStr">
@@ -52548,24 +52556,25 @@
       <c r="L461" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-315: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
-MSG-NB-316: "Account &lt;arn&gt; is &lt;status&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
-MSG-NB-317: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
-MSG-NB-318: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
-MSG-NB-319: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
-MSG-NB-320: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
-MSG-NB-321: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
-MSG-NB-322: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-323: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
-MSG-NB-324: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
-MSG-NB-325: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
-MSG-NB-326: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
-MSG-NB-327: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
-MSG-NB-328: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
-MSG-NB-329: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
-MSG-NB-330: "No invoice" (INVOICE_NOT_FOUND)
-MSG-NB-331: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
-MSG-NB-332: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
+MSG-NB-323: "Enter a booking date that is not in the future"
+MSG-NB-324: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
+MSG-NB-325: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
+MSG-NB-326: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
+MSG-NB-327: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
+MSG-NB-328: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
+MSG-NB-329: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
+MSG-NB-330: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
+MSG-NB-331: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-332: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
+MSG-NB-333: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
+MSG-NB-334: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
+MSG-NB-335: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
+MSG-NB-336: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
+MSG-NB-337: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
+MSG-NB-338: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
+MSG-NB-339: "No invoice" (INVOICE_NOT_FOUND)
+MSG-NB-340: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
+MSG-NB-341: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
         </is>
       </c>
       <c r="M461" s="12" t="inlineStr">
@@ -52641,15 +52650,15 @@
       <c r="L462" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-339: "Account &lt;arn&gt; is &lt;status&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
-MSG-NB-340: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
-MSG-NB-341: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
-MSG-NB-342: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
-MSG-NB-343: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
-MSG-NB-344: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-345: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-346: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
-MSG-NB-347: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-NB-348: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
+MSG-NB-349: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
+MSG-NB-350: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
+MSG-NB-351: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
+MSG-NB-352: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
+MSG-NB-353: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-354: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-355: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
+MSG-NB-356: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M462" s="12" t="inlineStr">
@@ -52725,14 +52734,15 @@
       <c r="L463" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-349: "E-mail: &lt;dispatch error&gt;"
-MSG-NB-351: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
-MSG-NB-352: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
-MSG-NB-353: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-354: "ServiceInvoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-355: "ServiceInvoice not found: &lt;si no&gt;" (NOT_FOUND)
-MSG-NB-356: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
-MSG-NB-357: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
+MSG-NB-358: "E-mail: &lt;dispatch error&gt;"
+MSG-NB-359: "Give the reason of the credit"
+MSG-NB-361: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
+MSG-NB-362: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
+MSG-NB-363: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-364: "ServiceInvoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-365: "ServiceInvoice not found: &lt;si no&gt;" (NOT_FOUND)
+MSG-NB-366: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
+MSG-NB-367: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
         </is>
       </c>
       <c r="M463" s="12" t="inlineStr">
@@ -52808,12 +52818,12 @@
       <c r="L464" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-360: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-361: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
-MSG-NB-362: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
-MSG-NB-363: "AutoBookRule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-364: "IncentiveRule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-365: "ServiceInvoiceType not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-370: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-371: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
+MSG-NB-372: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
+MSG-NB-373: "AutoBookRule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-374: "IncentiveRule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-375: "ServiceInvoiceType not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M464" s="12" t="inlineStr">
@@ -52889,31 +52899,31 @@
       <c r="L465" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-370: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
-MSG-NB-371: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-372: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-373: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
-MSG-NB-374: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
-MSG-NB-375: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
-MSG-NB-376: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
-MSG-NB-377: "The file has no data rows" (BULK_FILE_EMPTY)
-MSG-NB-378: "The file has no header row" (BULK_FILE_EMPTY)
-MSG-NB-379: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
-MSG-NB-380: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
-MSG-NB-381: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
-MSG-NB-382: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
-MSG-NB-383: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
-MSG-NB-384: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
-MSG-NB-385: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
-MSG-NB-386: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
-MSG-NB-387: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
-MSG-NB-388: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
-MSG-NB-389: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
-MSG-NB-390: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
-MSG-NB-391: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-392: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-393: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-394: "BulkJob not found: &lt;job id&gt;" (NOT_FOUND)</t>
+MSG-NB-380: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
+MSG-NB-381: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-382: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-383: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
+MSG-NB-384: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
+MSG-NB-385: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
+MSG-NB-386: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
+MSG-NB-387: "The file has no data rows" (BULK_FILE_EMPTY)
+MSG-NB-388: "The file has no header row" (BULK_FILE_EMPTY)
+MSG-NB-389: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-390: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
+MSG-NB-391: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
+MSG-NB-392: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
+MSG-NB-393: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
+MSG-NB-394: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
+MSG-NB-395: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
+MSG-NB-396: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
+MSG-NB-397: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
+MSG-NB-398: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
+MSG-NB-399: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
+MSG-NB-400: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
+MSG-NB-401: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-402: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-403: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-404: "BulkJob not found: &lt;job id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M465" s="12" t="inlineStr">
@@ -52977,18 +52987,18 @@
       <c r="L466" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-396: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
-MSG-NB-397: "The file is empty" (ATTACHMENT_EMPTY)
-MSG-NB-398: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
-MSG-NB-399: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
-MSG-NB-400: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
-MSG-NB-401: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
-MSG-NB-402: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
-MSG-NB-403: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
-MSG-NB-404: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
-MSG-NB-405: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
-MSG-NB-406: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-407: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-406: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
+MSG-NB-407: "The file is empty" (ATTACHMENT_EMPTY)
+MSG-NB-408: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
+MSG-NB-409: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
+MSG-NB-410: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
+MSG-NB-411: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
+MSG-NB-412: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
+MSG-NB-413: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
+MSG-NB-414: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
+MSG-NB-415: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
+MSG-NB-416: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-417: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M466" s="12" t="inlineStr">
@@ -53052,16 +53062,16 @@
       <c r="L467" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-409: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-410: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-411: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-412: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
-MSG-NB-413: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
-MSG-NB-414: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
-MSG-NB-415: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
-MSG-NB-416: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
-MSG-NB-417: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
-MSG-NB-418: "The item is closed" (WORK_CASE_CLOSED)</t>
+MSG-NB-419: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-420: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-421: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-422: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
+MSG-NB-423: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
+MSG-NB-424: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
+MSG-NB-425: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
+MSG-NB-426: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
+MSG-NB-427: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
+MSG-NB-428: "The item is closed" (WORK_CASE_CLOSED)</t>
         </is>
       </c>
       <c r="M467" s="12" t="inlineStr">
@@ -53137,10 +53147,10 @@
       <c r="L468" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-421: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-422: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
-MSG-NB-423: "The item is closed" (WORK_CASE_CLOSED)
-MSG-NB-424: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
+MSG-NB-431: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-432: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
+MSG-NB-433: "The item is closed" (WORK_CASE_CLOSED)
+MSG-NB-434: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M468" s="12" t="inlineStr">
@@ -53216,14 +53226,14 @@
       <c r="L469" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-427: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
-MSG-NB-428: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
-MSG-NB-429: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
-MSG-NB-430: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
-MSG-NB-431: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
-MSG-NB-432: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
-MSG-NB-433: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
-MSG-NB-434: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-437: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
+MSG-NB-438: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
+MSG-NB-439: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
+MSG-NB-440: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
+MSG-NB-441: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
+MSG-NB-442: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
+MSG-NB-443: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
+MSG-NB-444: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M469" s="12" t="inlineStr">
@@ -53299,12 +53309,17 @@
       <c r="L470" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-435: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-436: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
-MSG-NB-437: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
-MSG-NB-438: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
-MSG-NB-439: "LovType not found: &lt;type code&gt;" (NOT_FOUND)
-MSG-NB-440: "LovValue not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-446: "Enter a whole number"
+MSG-NB-447: "Enter the first valid date"
+MSG-NB-448: "Enter the label"
+MSG-NB-449: "Must not be before the first valid date"
+MSG-NB-450: "Use capital letters, digits and _ (up to 40)"
+MSG-NB-451: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-452: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
+MSG-NB-453: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
+MSG-NB-454: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
+MSG-NB-455: "LovType not found: &lt;type code&gt;" (NOT_FOUND)
+MSG-NB-456: "LovValue not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M470" s="12" t="inlineStr">
@@ -53380,13 +53395,13 @@
       <c r="L471" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-441: "Enter a whole number of bookings (0 or more)"
-MSG-NB-442: "Enter an amount of 0 or more"
-MSG-NB-443: "Enter the period"
-MSG-NB-444: "Enter the unit code or the officer username"
-MSG-NB-447: "The period end must not be before the start"
-MSG-NB-448: "Targets cannot be negative" (TARGET_NEGATIVE)
-MSG-NB-449: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
+MSG-NB-457: "Enter a whole number of bookings (0 or more)"
+MSG-NB-458: "Enter an amount of 0 or more"
+MSG-NB-459: "Enter the period"
+MSG-NB-460: "Enter the unit code or the officer username"
+MSG-NB-463: "The period end must not be before the start"
+MSG-NB-464: "Targets cannot be negative" (TARGET_NEGATIVE)
+MSG-NB-465: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
         </is>
       </c>
       <c r="M471" s="12" t="inlineStr">
@@ -53462,9 +53477,10 @@
       <c r="L472" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-450: "ReportVariant not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-451: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
-MSG-NB-452: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
+MSG-NB-466: "Enter a name"
+MSG-NB-469: "ReportVariant not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-470: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
+MSG-NB-471: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
         </is>
       </c>
       <c r="M472" s="12" t="inlineStr">
@@ -53540,13 +53556,13 @@
       <c r="L473" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-457: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
-MSG-NB-458: "Document template not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-459: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-460: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
-MSG-NB-461: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
-MSG-NB-462: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
-MSG-NB-463: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
+MSG-NB-476: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
+MSG-NB-477: "Document template not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-478: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-479: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
+MSG-NB-480: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
+MSG-NB-481: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
+MSG-NB-482: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
         </is>
       </c>
       <c r="M473" s="12" t="inlineStr">
@@ -53572,11 +53588,19 @@
         </is>
       </c>
       <c r="B474" s="12" t="inlineStr"/>
-      <c r="C474" s="12" t="inlineStr"/>
-      <c r="D474" s="12" t="inlineStr"/>
+      <c r="C474" s="12" t="inlineStr">
+        <is>
+          <t>FR-NB-137</t>
+        </is>
+      </c>
+      <c r="D474" s="12" t="inlineStr">
+        <is>
+          <t>BRNB.106, Data retention</t>
+        </is>
+      </c>
       <c r="E474" s="12" t="inlineStr">
         <is>
-          <t>Messages of Every screen (Common screen elements)</t>
+          <t>Messages of Data Retention (SCR-NB-43)</t>
         </is>
       </c>
       <c r="F474" s="12" t="inlineStr">
@@ -53586,15 +53610,19 @@
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H474" s="12" t="inlineStr">
         <is>
-          <t>Any New Business record</t>
-        </is>
-      </c>
-      <c r="I474" s="12" t="inlineStr"/>
+          <t>Setup &amp; Administration › Broking Setup › Data Retention</t>
+        </is>
+      </c>
+      <c r="I474" s="12" t="inlineStr">
+        <is>
+          <t>SCR-NB-43</t>
+        </is>
+      </c>
       <c r="J474" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -53602,23 +53630,19 @@
       </c>
       <c r="K474" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
-2. Open Any New Business record.
+          <t>1. Sign in as approver.
+2. Open Setup &amp; Administration › Broking Setup › Data Retention.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L474" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-466: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-NB-467: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-NB-468: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
-MSG-NB-469: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-NB-470: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-NB-471: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
-MSG-NB-472: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
-MSG-NB-473: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-NB-474: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-NB-484: "Between 0 and 50 years"
+MSG-NB-485: "Between 1 and 50 years"
+MSG-NB-486: "Enter a description"
+MSG-NB-487: "Enter at least one status"
+MSG-NB-490: "The &lt;record type&gt; module does not report retention candidates yet; the records will be counted once it does."</t>
         </is>
       </c>
       <c r="M474" s="12" t="inlineStr">
@@ -53644,19 +53668,11 @@
         </is>
       </c>
       <c r="B475" s="12" t="inlineStr"/>
-      <c r="C475" s="12" t="inlineStr">
-        <is>
-          <t>FR-NB-019</t>
-        </is>
-      </c>
-      <c r="D475" s="12" t="inlineStr">
-        <is>
-          <t>BRNB.039, BRNB.064, BRNB.024</t>
-        </is>
-      </c>
+      <c r="C475" s="12" t="inlineStr"/>
+      <c r="D475" s="12" t="inlineStr"/>
       <c r="E475" s="12" t="inlineStr">
         <is>
-          <t>Messages of Bulk upload wizard (SCR-NB-36): every upload type</t>
+          <t>Messages of Every screen (Common screen elements)</t>
         </is>
       </c>
       <c r="F475" s="12" t="inlineStr">
@@ -53671,14 +53687,10 @@
       </c>
       <c r="H475" s="12" t="inlineStr">
         <is>
-          <t>Client &amp; Policy › Bulk Processing › Bulk Uploads › Bulk Upload</t>
-        </is>
-      </c>
-      <c r="I475" s="12" t="inlineStr">
-        <is>
-          <t>SCR-NB-36</t>
-        </is>
-      </c>
+          <t>Any New Business record</t>
+        </is>
+      </c>
+      <c r="I475" s="12" t="inlineStr"/>
       <c r="J475" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -53687,15 +53699,22 @@
       <c r="K475" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
-2. Open Client &amp; Policy › Bulk Processing › Bulk Uploads › Bulk Upload.
+2. Open Any New Business record.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L475" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-479: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-NB-480: "&lt;Column&gt; is mandatory"</t>
+MSG-NB-493: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-NB-494: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-NB-495: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
+MSG-NB-496: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-NB-497: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-NB-498: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
+MSG-NB-499: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
+MSG-NB-500: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-NB-501: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M475" s="12" t="inlineStr">
@@ -53733,7 +53752,7 @@
       </c>
       <c r="E476" s="12" t="inlineStr">
         <is>
-          <t>Messages of Bulk upload wizard (SCR-NB-36): Bulk quotation acceptance</t>
+          <t>Messages of Bulk upload wizard (SCR-NB-36): every upload type</t>
         </is>
       </c>
       <c r="F476" s="12" t="inlineStr">
@@ -53771,7 +53790,8 @@
       <c r="L476" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-481: "&lt;quotation no&gt; is &lt;status&gt;, not sent to the client"</t>
+MSG-NB-506: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-NB-507: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M476" s="12" t="inlineStr">
@@ -53809,7 +53829,7 @@
       </c>
       <c r="E477" s="12" t="inlineStr">
         <is>
-          <t>Messages of Bulk upload wizard (SCR-NB-36): Booking upload</t>
+          <t>Messages of Bulk upload wizard (SCR-NB-36): Bulk quotation acceptance</t>
         </is>
       </c>
       <c r="F477" s="12" t="inlineStr">
@@ -53847,8 +53867,7 @@
       <c r="L477" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-482: "Account &lt;arn&gt; belongs to another company"
-MSG-NB-485: "The booking date &lt;date&gt; is in the future"</t>
+MSG-NB-508: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
         </is>
       </c>
       <c r="M477" s="12" t="inlineStr">
@@ -53886,7 +53905,7 @@
       </c>
       <c r="E478" s="12" t="inlineStr">
         <is>
-          <t>Messages of Bulk upload wizard (SCR-NB-36): Bulk client creation and update</t>
+          <t>Messages of Bulk upload wizard (SCR-NB-36): Booking upload</t>
         </is>
       </c>
       <c r="F478" s="12" t="inlineStr">
@@ -53924,9 +53943,8 @@
       <c r="L478" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-483: "Client Type must be INDIVIDUAL or CORPORATE"
-MSG-NB-484: "Client code &lt;code&gt; does not exist"
-MSG-NB-486: "The row matches several clients: &lt;details&gt;"</t>
+MSG-NB-509: "Account &lt;arn&gt; belongs to another company"
+MSG-NB-512: "The booking date &lt;date&gt; is in the future"</t>
         </is>
       </c>
       <c r="M478" s="12" t="inlineStr">
@@ -53952,11 +53970,19 @@
         </is>
       </c>
       <c r="B479" s="12" t="inlineStr"/>
-      <c r="C479" s="12" t="inlineStr"/>
-      <c r="D479" s="12" t="inlineStr"/>
+      <c r="C479" s="12" t="inlineStr">
+        <is>
+          <t>FR-NB-019</t>
+        </is>
+      </c>
+      <c r="D479" s="12" t="inlineStr">
+        <is>
+          <t>BRNB.039, BRNB.064, BRNB.024</t>
+        </is>
+      </c>
       <c r="E479" s="12" t="inlineStr">
         <is>
-          <t>Messages of Several screens</t>
+          <t>Messages of Bulk upload wizard (SCR-NB-36): Bulk client creation and update</t>
         </is>
       </c>
       <c r="F479" s="12" t="inlineStr">
@@ -53971,10 +53997,14 @@
       </c>
       <c r="H479" s="12" t="inlineStr">
         <is>
-          <t>Any New Business record</t>
-        </is>
-      </c>
-      <c r="I479" s="12" t="inlineStr"/>
+          <t>Client &amp; Policy › Bulk Processing › Bulk Uploads › Bulk Upload</t>
+        </is>
+      </c>
+      <c r="I479" s="12" t="inlineStr">
+        <is>
+          <t>SCR-NB-36</t>
+        </is>
+      </c>
       <c r="J479" s="12" t="inlineStr">
         <is>
           <t>Seed data of the SIT environment.</t>
@@ -53983,25 +54013,16 @@
       <c r="K479" s="12" t="inlineStr">
         <is>
           <t>1. Sign in as ao.
-2. Open Any New Business record.
+2. Open Client &amp; Policy › Bulk Processing › Bulk Uploads › Bulk Upload.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
       </c>
       <c r="L479" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-487: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-488: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-489: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-490: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
-MSG-NB-491: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-492: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
-MSG-NB-493: "Notification not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-494: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-495: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-496: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
-MSG-NB-497: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-498: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)</t>
+MSG-NB-510: "Client Type must be INDIVIDUAL or CORPORATE"
+MSG-NB-511: "Client code &lt;code&gt; does not exist"
+MSG-NB-513: "The row matches several clients: &lt;details&gt;"</t>
         </is>
       </c>
       <c r="M479" s="12" t="inlineStr">
@@ -54020,12 +54041,87 @@
       <c r="R479" s="28" t="n"/>
       <c r="S479" s="12" t="n"/>
     </row>
+    <row r="480">
+      <c r="A480" s="12" t="inlineStr">
+        <is>
+          <t>TC-NB-MSG-44</t>
+        </is>
+      </c>
+      <c r="B480" s="12" t="inlineStr"/>
+      <c r="C480" s="12" t="inlineStr"/>
+      <c r="D480" s="12" t="inlineStr"/>
+      <c r="E480" s="12" t="inlineStr">
+        <is>
+          <t>Messages of Several screens</t>
+        </is>
+      </c>
+      <c r="F480" s="12" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="G480" s="12" t="inlineStr">
+        <is>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
+        </is>
+      </c>
+      <c r="H480" s="12" t="inlineStr">
+        <is>
+          <t>Any New Business record</t>
+        </is>
+      </c>
+      <c r="I480" s="12" t="inlineStr"/>
+      <c r="J480" s="12" t="inlineStr">
+        <is>
+          <t>Seed data of the SIT environment.</t>
+        </is>
+      </c>
+      <c r="K480" s="12" t="inlineStr">
+        <is>
+          <t>1. Sign in as ao.
+2. Open Any New Business record.
+3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
+        </is>
+      </c>
+      <c r="L480" s="12" t="inlineStr">
+        <is>
+          <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
+MSG-NB-514: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-515: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-516: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-517: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
+MSG-NB-518: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-519: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
+MSG-NB-520: "Notification not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-521: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-522: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-523: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
+MSG-NB-524: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-525: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="M480" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N480" s="12" t="inlineStr"/>
+      <c r="O480" s="27" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P480" s="12" t="n"/>
+      <c r="Q480" s="12" t="n"/>
+      <c r="R480" s="28" t="n"/>
+      <c r="S480" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:S479"/>
+  <autoFilter ref="A4:S480"/>
   <mergeCells count="1">
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O979">
+  <conditionalFormatting sqref="O5:O980">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -54039,19 +54135,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:S979">
+  <conditionalFormatting sqref="A5:S980">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="F5:F979" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
+    <dataValidation sqref="F5:F980" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
       <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M979" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="M5:M980" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O979" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="O5:O980" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -58060,10 +58156,10 @@
         <v>2</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I97" s="12" t="n">
         <v>3</v>
@@ -62126,10 +62222,10 @@
         <v>2</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H204" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I204" s="12" t="n">
         <v>3</v>
@@ -62696,10 +62792,10 @@
         <v>2</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H219" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I219" s="12" t="n">
         <v>3</v>
@@ -63704,7 +63800,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>TC-NB-SCR-36, TC-NB-MSG-29, TC-NB-MSG-39, TC-NB-MSG-40, TC-NB-MSG-41, TC-NB-MSG-42</t>
+          <t>TC-NB-SCR-36, TC-NB-MSG-29, TC-NB-MSG-40, TC-NB-MSG-41, TC-NB-MSG-42, TC-NB-MSG-43</t>
         </is>
       </c>
     </row>
@@ -63875,11 +63971,11 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>TC-NB-137.1-01, TC-NB-137.2-01, TC-NB-137.2-02, TC-NB-SCR-43</t>
+          <t>TC-NB-137.1-01, TC-NB-137.2-01, TC-NB-137.2-02, TC-NB-SCR-43, TC-NB-MSG-38</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -47253,7 +47253,7 @@
       <c r="L396" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-06 New Quotation and Edit Quotation of the FRS.
-Fields in this order: 1 Client or prospect (Look-up, mandatory Y); 2 Market segment (Drop-down, mandatory N); 3 Source channel (Drop-down, mandatory N); 4 Product (Drop-down, mandatory Y); 5 Insurer (Drop-down, mandatory N); 6 Insurer branch (LGT) (Drop-down, mandatory N); 7 Period from (Date, mandatory N); 8 Period to (Date, mandatory N); 9 Valid until (Date, mandatory N); 10 Rating basis (Drop-down, mandatory N); 11 Premium paid directly to the insurer (Check box, mandatory N (shown for products eligible for direct payment)); 12 Remarks (Text, mandatory N); 13 Vehicle: Plate no., Conduction sticker, Engine no., Chassis no. (Text, mandatory Cond.: plate no. or conduction sticker per vehicle; others per the product's field rules); 14 Vehicle: Make, Model, Year model, Body type, Colour, Seats (Text / Number / Drop-down, mandatory Cond.: per the product's field rules); 15 Location: Address, City, Province, Occupancy, Construction class (Text / Drop-down, mandatory Address Y for a location; others per the field rules); 16 Location: Insured items (description, sum insured) (Table, mandatory N); 17 Person: Name, Birth date, Relationship (Text / Date, mandatory Name Y for a person); 18 Description (Text, mandatory N); 19 Sum insured (Amount, mandatory Y to rate the premium); 20 Rate % (non-motor) (Number, mandatory N); 21 Excess BI limit, PD limit (motor) (Amount, mandatory N); 22 Item n: risk group (Number, mandatory N (shown with 2 or more items)); 23 Live premium (Display, mandatory -); 24 TSU routing notice (Banner, mandatory -); 25 Summary (Display, mandatory -).
+Fields in this order: 1 Client or prospect (Look-up, mandatory Y); 2 Market segment (Drop-down, mandatory Y at submission); 3 Source channel (Drop-down, mandatory N); 4 Product (Drop-down, mandatory Y); 5 Insurer (Drop-down, mandatory N); 6 Insurer branch (LGT) (Drop-down, mandatory N); 7 Period from (Date, mandatory N); 8 Period to (Date, mandatory N); 9 Valid until (Date, mandatory N); 10 Rating basis (Drop-down, mandatory N); 11 Premium paid directly to the insurer (Check box, mandatory N (shown for products eligible for direct payment)); 12 Remarks (Text, mandatory N); 13 Vehicle: Plate no., Conduction sticker, Engine no., Chassis no. (Text, mandatory Cond.: plate no. or conduction sticker per vehicle; others per the product's field rules); 14 Vehicle: Make, Model, Year model, Body type, Colour, Seats (Text / Number / Drop-down, mandatory Cond.: per the product's field rules); 15 Location: Address, City, Province, Occupancy, Construction class (Text / Drop-down, mandatory Address Y for a location; others per the field rules); 16 Location: Insured items (description, sum insured) (Table, mandatory N); 17 Person: Name, Birth date, Relationship (Text / Date, mandatory Name Y for a person); 18 Description (Text, mandatory N); 19 Sum insured (Amount, mandatory Y to rate the premium); 20 Rate % (non-motor) (Number, mandatory N); 21 Excess BI limit, PD limit (motor) (Amount, mandatory N); 22 Item n: risk group (Number, mandatory N (shown with 2 or more items)); 23 Live premium (Display, mandatory -); 24 TSU routing notice (Banner, mandatory -); 25 Summary (Display, mandatory -).
 Actions: Save Draft; Next / Back; Submit for Review.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -51116,16 +51116,17 @@
 MSG-NB-101: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
 MSG-NB-102: "Select the client and the product" (QUOTATION_INCOMPLETE)
 MSG-NB-103: "Select the product" (QUOTATION_INCOMPLETE)
-MSG-NB-104: "Quotation &lt;quotation no&gt; is &lt;status&gt;" (QUOTATION_NOT_EDITABLE)
+MSG-NB-104: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
 MSG-NB-105: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
 MSG-NB-106: "Add at least one risk item" (QUOTATION_NO_ITEMS)
 MSG-NB-107: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
 MSG-NB-108: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
-MSG-NB-109: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
-MSG-NB-110: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
-MSG-NB-111: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-112: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
-MSG-NB-113: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-109: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
+MSG-NB-110: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
+MSG-NB-111: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
+MSG-NB-112: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-113: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
+MSG-NB-114: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M444" s="12" t="inlineStr">
@@ -51201,8 +51202,8 @@
       <c r="L445" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-115: "Enter the item rate between 0 and 100"
-MSG-NB-116: "Explain why the scheme rate cannot be used"</t>
+MSG-NB-116: "Enter the item rate between 0 and 100"
+MSG-NB-117: "Explain why the scheme rate cannot be used"</t>
         </is>
       </c>
       <c r="M445" s="12" t="inlineStr">
@@ -51278,19 +51279,19 @@
       <c r="L446" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-123: "Select the client or prospect"
-MSG-NB-124: "Select the product"
-MSG-NB-125: "The period end must be after the period start"
-MSG-NB-126: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
-MSG-NB-127: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-128: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
-MSG-NB-129: "Complete the PRF header" (PRF_INCOMPLETE)
-MSG-NB-130: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
-MSG-NB-131: "PRF &lt;prf no&gt; cannot be changed while &lt;status&gt;" (PRF_NOT_EDITABLE)
-MSG-NB-132: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
-MSG-NB-133: "The period end must be after the period start" (PRF_PERIOD_INVALID)
-MSG-NB-134: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
-MSG-NB-135: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-124: "Select the client or prospect"
+MSG-NB-125: "Select the product"
+MSG-NB-126: "The period end must be after the period start"
+MSG-NB-127: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
+MSG-NB-128: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-129: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
+MSG-NB-130: "Complete the PRF header" (PRF_INCOMPLETE)
+MSG-NB-131: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
+MSG-NB-132: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
+MSG-NB-133: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
+MSG-NB-134: "The period end must be after the period start" (PRF_PERIOD_INVALID)
+MSG-NB-135: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
+MSG-NB-136: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M446" s="12" t="inlineStr">
@@ -51366,26 +51367,26 @@
       <c r="L447" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-145: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-146: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-147: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
-MSG-NB-148: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
-MSG-NB-149: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
-MSG-NB-150: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
-MSG-NB-151: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
-MSG-NB-152: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
-MSG-NB-153: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
-MSG-NB-154: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
-MSG-NB-155: "The chosen terms are gone" (PS_TERMS_MISSING)
-MSG-NB-156: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
-MSG-NB-157: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
-MSG-NB-158: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
-MSG-NB-159: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
-MSG-NB-160: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
-MSG-NB-161: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
-MSG-NB-162: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
-MSG-NB-163: "No insurer terms have been received" (TERMS_NONE)
-MSG-NB-164: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
+MSG-NB-146: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-147: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-148: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
+MSG-NB-149: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
+MSG-NB-150: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
+MSG-NB-151: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
+MSG-NB-152: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
+MSG-NB-153: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
+MSG-NB-154: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
+MSG-NB-155: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
+MSG-NB-156: "The chosen terms are gone" (PS_TERMS_MISSING)
+MSG-NB-157: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
+MSG-NB-158: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
+MSG-NB-159: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
+MSG-NB-160: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
+MSG-NB-161: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
+MSG-NB-162: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
+MSG-NB-163: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
+MSG-NB-164: "No insurer terms have been received" (TERMS_NONE)
+MSG-NB-165: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
         </is>
       </c>
       <c r="M447" s="12" t="inlineStr">
@@ -51461,12 +51462,12 @@
       <c r="L448" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-167: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_ACTIVE)
-MSG-NB-168: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-169: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-170: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
-MSG-NB-171: "Enter the Free First Year start" (FFY_START_REQUIRED)
-MSG-NB-172: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
+MSG-NB-168: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
+MSG-NB-169: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-170: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-171: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
+MSG-NB-172: "Enter the Free First Year start" (FFY_START_REQUIRED)
+MSG-NB-173: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
         </is>
       </c>
       <c r="M448" s="12" t="inlineStr">
@@ -51542,17 +51543,17 @@
       <c r="L449" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-175: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-176: "Account &lt;arn&gt; is &lt;status&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
-MSG-NB-177: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
-MSG-NB-178: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
-MSG-NB-179: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-180: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-181: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
-MSG-NB-182: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
-MSG-NB-183: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
-MSG-NB-184: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
-MSG-NB-185: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
+MSG-NB-176: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-177: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
+MSG-NB-178: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
+MSG-NB-179: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
+MSG-NB-180: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-181: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-182: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
+MSG-NB-183: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
+MSG-NB-184: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
+MSG-NB-185: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
+MSG-NB-186: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
         </is>
       </c>
       <c r="M449" s="12" t="inlineStr">
@@ -51628,24 +51629,28 @@
       <c r="L450" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-188: "Duplicate risks: &lt;list&gt;"
-MSG-NB-189: "Not ready to submit: &lt;list&gt;"
-MSG-NB-190: "These risks are already on account &lt;list&gt; — open the existing account instead of creating a new one."
-MSG-NB-191: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
-MSG-NB-192: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
-MSG-NB-193: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
-MSG-NB-194: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
-MSG-NB-195: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
-MSG-NB-196: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
-MSG-NB-197: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-198: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
-MSG-NB-199: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-200: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
-MSG-NB-201: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
-MSG-NB-202: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
-MSG-NB-203: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
-MSG-NB-204: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-205: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-188: "Choose the client and product to save the draft."
+MSG-NB-190: "Duplicate risks: &lt;list&gt;"
+MSG-NB-191: "Not ready to submit: &lt;list&gt;"
+MSG-NB-192: "The draft is not saved yet: click Save Draft to check it before submission."
+MSG-NB-193: "The draft was not saved: correct what the message above describes, then save the draft again."
+MSG-NB-194: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
+MSG-NB-195: "These risks are already on account &lt;list&gt; — open the existing account instead of creating a new one."
+MSG-NB-196: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
+MSG-NB-197: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
+MSG-NB-198: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
+MSG-NB-199: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
+MSG-NB-200: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
+MSG-NB-201: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
+MSG-NB-202: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-203: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
+MSG-NB-204: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-205: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
+MSG-NB-206: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
+MSG-NB-207: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
+MSG-NB-208: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
+MSG-NB-209: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-210: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M450" s="12" t="inlineStr">
@@ -51721,9 +51726,9 @@
       <c r="L451" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-210: "Account &lt;arn&gt; is &lt;status&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-211: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
-MSG-NB-212: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
+MSG-NB-215: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-216: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
+MSG-NB-217: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
         </is>
       </c>
       <c r="M451" s="12" t="inlineStr">
@@ -51799,15 +51804,15 @@
       <c r="L452" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-215: "Record Hold Cover Confirmation"
-MSG-NB-216: "Record Hold Cover Decline"
-MSG-NB-217: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
-MSG-NB-218: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
-MSG-NB-219: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
-MSG-NB-220: "A hold cover is requested while the account is being placed, not &lt;status&gt;" (HOLD_COVER_NOT_ALLOWED)
-MSG-NB-221: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
-MSG-NB-222: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
-MSG-NB-223: "Choose the insurer on the account first" (INSURER_NOT_SET)</t>
+MSG-NB-220: "Record Hold Cover Confirmation"
+MSG-NB-221: "Record Hold Cover Decline"
+MSG-NB-222: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
+MSG-NB-223: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
+MSG-NB-224: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
+MSG-NB-225: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
+MSG-NB-226: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
+MSG-NB-227: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
+MSG-NB-228: "Choose the insurer on the account first" (INSURER_NOT_SET)</t>
         </is>
       </c>
       <c r="M452" s="12" t="inlineStr">
@@ -51883,20 +51888,20 @@
       <c r="L453" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-232: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-233: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
-MSG-NB-234: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
-MSG-NB-235: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
-MSG-NB-236: "PlacementSlip not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-237: "The account is &lt;status&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
-MSG-NB-238: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
-MSG-NB-239: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
-MSG-NB-240: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
-MSG-NB-241: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
-MSG-NB-242: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
-MSG-NB-243: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
-MSG-NB-244: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
-MSG-NB-245: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
+MSG-NB-237: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-238: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
+MSG-NB-239: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
+MSG-NB-240: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
+MSG-NB-241: "PlacementSlip not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-242: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
+MSG-NB-243: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
+MSG-NB-244: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
+MSG-NB-245: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
+MSG-NB-246: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
+MSG-NB-247: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
+MSG-NB-248: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
+MSG-NB-249: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
+MSG-NB-250: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
         </is>
       </c>
       <c r="M453" s="12" t="inlineStr">
@@ -51972,10 +51977,10 @@
       <c r="L454" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-249: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
-MSG-NB-250: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
-MSG-NB-251: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
-MSG-NB-252: "BillingBatch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-254: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
+MSG-NB-255: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
+MSG-NB-256: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
+MSG-NB-257: "BillingBatch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M454" s="12" t="inlineStr">
@@ -52051,19 +52056,19 @@
       <c r="L455" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-254: "&lt;arn&gt; is &lt;status&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-255: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
-MSG-NB-256: "BillingBatch not found: &lt;batch id&gt;" (NOT_FOUND)
-MSG-NB-257: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
-MSG-NB-258: "PaymentReport not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-259: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
-MSG-NB-260: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
-MSG-NB-261: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
-MSG-NB-262: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
-MSG-NB-263: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-264: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-265: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
-MSG-NB-266: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
+MSG-NB-259: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-260: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
+MSG-NB-261: "BillingBatch not found: &lt;batch id&gt;" (NOT_FOUND)
+MSG-NB-262: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
+MSG-NB-263: "PaymentReport not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-264: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
+MSG-NB-265: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
+MSG-NB-266: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
+MSG-NB-267: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
+MSG-NB-268: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-269: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-270: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
+MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
         </is>
       </c>
       <c r="M455" s="12" t="inlineStr">
@@ -52139,14 +52144,14 @@
       <c r="L456" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-269: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
-MSG-NB-270: "Account &lt;arn&gt; is &lt;status&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
-MSG-NB-271: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
-MSG-NB-272: "The e-policy &lt;file name&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)
-MSG-NB-273: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
-MSG-NB-274: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-275: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
-MSG-NB-276: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-274: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
+MSG-NB-275: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
+MSG-NB-276: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
+MSG-NB-277: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
+MSG-NB-278: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
+MSG-NB-279: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-280: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
+MSG-NB-281: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M456" s="12" t="inlineStr">
@@ -52222,12 +52227,12 @@
       <c r="L457" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-277: "Check before confirming &lt;list&gt;"
-MSG-NB-279: "Enter one policy number per policy year."
-MSG-NB-283: "Rejected by &lt;user&gt;: &lt;reject reason&gt;"
-MSG-NB-284: "The policy numbers must be different."
-MSG-NB-285: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
-MSG-NB-286: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
+MSG-NB-282: "Check before confirming &lt;list&gt;"
+MSG-NB-284: "Enter one policy number per policy year."
+MSG-NB-288: "Rejected by &lt;user&gt;: &lt;reject reason&gt;"
+MSG-NB-289: "The policy numbers must be different."
+MSG-NB-290: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
+MSG-NB-291: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
         </is>
       </c>
       <c r="M457" s="12" t="inlineStr">
@@ -52303,10 +52308,10 @@
       <c r="L458" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-289: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
-MSG-NB-290: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
-MSG-NB-291: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
-MSG-NB-292: "InsuranceAdvice not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-294: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
+MSG-NB-295: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
+MSG-NB-296: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
+MSG-NB-297: "InsuranceAdvice not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M458" s="12" t="inlineStr">
@@ -52382,8 +52387,8 @@
       <c r="L459" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-295: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
-MSG-NB-296: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
+MSG-NB-300: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
+MSG-NB-301: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
         </is>
       </c>
       <c r="M459" s="12" t="inlineStr">
@@ -52459,20 +52464,20 @@
       <c r="L460" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-299: "A negative endorsement reduces the sum insured (enter a minus)"
-MSG-NB-300: "A positive endorsement increases the sum insured"
-MSG-NB-301: "Choose the reason"
-MSG-NB-302: "Describe the cancellation"
-MSG-NB-303: "Describe the change"
-MSG-NB-304: "Enter a rate of zero or more, or leave it blank"
-MSG-NB-305: "Enter the cancellation date"
-MSG-NB-306: "Enter the change of the sum insured"
-MSG-NB-307: "Enter the effective date"
-MSG-NB-309: "No queued account to book" (BATCH_EMPTY)
-MSG-NB-310: "Select at least one account to book" (BATCH_EMPTY)
-MSG-NB-311: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-312: "BookingQueue not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-313: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
+MSG-NB-304: "A negative endorsement reduces the sum insured (enter a minus)"
+MSG-NB-305: "A positive endorsement increases the sum insured"
+MSG-NB-306: "Choose the reason"
+MSG-NB-307: "Describe the cancellation"
+MSG-NB-308: "Describe the change"
+MSG-NB-309: "Enter a rate of zero or more, or leave it blank"
+MSG-NB-310: "Enter the cancellation date"
+MSG-NB-311: "Enter the change of the sum insured"
+MSG-NB-312: "Enter the effective date"
+MSG-NB-314: "No queued account to book" (BATCH_EMPTY)
+MSG-NB-315: "Select at least one account to book" (BATCH_EMPTY)
+MSG-NB-316: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-317: "BookingQueue not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-318: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
         </is>
       </c>
       <c r="M460" s="12" t="inlineStr">
@@ -52548,24 +52553,24 @@
       <c r="L461" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-315: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
-MSG-NB-316: "Account &lt;arn&gt; is &lt;status&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
-MSG-NB-317: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
-MSG-NB-318: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
-MSG-NB-319: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
-MSG-NB-320: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
-MSG-NB-321: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
-MSG-NB-322: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-323: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
-MSG-NB-324: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
-MSG-NB-325: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
-MSG-NB-326: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
-MSG-NB-327: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
-MSG-NB-328: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
-MSG-NB-329: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
-MSG-NB-330: "No invoice" (INVOICE_NOT_FOUND)
-MSG-NB-331: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
-MSG-NB-332: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
+MSG-NB-320: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
+MSG-NB-321: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
+MSG-NB-322: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
+MSG-NB-323: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
+MSG-NB-324: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
+MSG-NB-325: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
+MSG-NB-326: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
+MSG-NB-327: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-328: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
+MSG-NB-329: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
+MSG-NB-330: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
+MSG-NB-331: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
+MSG-NB-332: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
+MSG-NB-333: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
+MSG-NB-334: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
+MSG-NB-335: "No invoice" (INVOICE_NOT_FOUND)
+MSG-NB-336: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
+MSG-NB-337: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
         </is>
       </c>
       <c r="M461" s="12" t="inlineStr">
@@ -52641,15 +52646,15 @@
       <c r="L462" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-339: "Account &lt;arn&gt; is &lt;status&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
-MSG-NB-340: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
-MSG-NB-341: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
-MSG-NB-342: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
-MSG-NB-343: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
-MSG-NB-344: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-345: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-346: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
-MSG-NB-347: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-NB-344: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
+MSG-NB-345: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
+MSG-NB-346: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
+MSG-NB-347: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
+MSG-NB-348: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
+MSG-NB-349: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-350: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-351: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
+MSG-NB-352: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M462" s="12" t="inlineStr">
@@ -52725,14 +52730,14 @@
       <c r="L463" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-349: "E-mail: &lt;dispatch error&gt;"
-MSG-NB-351: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
-MSG-NB-352: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
-MSG-NB-353: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-354: "ServiceInvoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-355: "ServiceInvoice not found: &lt;si no&gt;" (NOT_FOUND)
-MSG-NB-356: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
-MSG-NB-357: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
+MSG-NB-354: "E-mail: &lt;dispatch error&gt;"
+MSG-NB-356: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
+MSG-NB-357: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
+MSG-NB-358: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-359: "ServiceInvoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-360: "ServiceInvoice not found: &lt;si no&gt;" (NOT_FOUND)
+MSG-NB-361: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
+MSG-NB-362: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
         </is>
       </c>
       <c r="M463" s="12" t="inlineStr">
@@ -52808,12 +52813,12 @@
       <c r="L464" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-360: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-361: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
-MSG-NB-362: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
-MSG-NB-363: "AutoBookRule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-364: "IncentiveRule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-365: "ServiceInvoiceType not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-365: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-366: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
+MSG-NB-367: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
+MSG-NB-368: "AutoBookRule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-369: "IncentiveRule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-370: "ServiceInvoiceType not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M464" s="12" t="inlineStr">
@@ -52889,31 +52894,31 @@
       <c r="L465" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-370: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
-MSG-NB-371: "Account &lt;arn&gt; is &lt;status&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-372: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-373: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
-MSG-NB-374: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
-MSG-NB-375: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
-MSG-NB-376: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
-MSG-NB-377: "The file has no data rows" (BULK_FILE_EMPTY)
-MSG-NB-378: "The file has no header row" (BULK_FILE_EMPTY)
-MSG-NB-379: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
-MSG-NB-380: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
-MSG-NB-381: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
-MSG-NB-382: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
-MSG-NB-383: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
-MSG-NB-384: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
-MSG-NB-385: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
-MSG-NB-386: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
-MSG-NB-387: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
-MSG-NB-388: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
-MSG-NB-389: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
-MSG-NB-390: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
-MSG-NB-391: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-392: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-393: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-394: "BulkJob not found: &lt;job id&gt;" (NOT_FOUND)</t>
+MSG-NB-375: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
+MSG-NB-376: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-377: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-378: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
+MSG-NB-379: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
+MSG-NB-380: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
+MSG-NB-381: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
+MSG-NB-382: "The file has no data rows" (BULK_FILE_EMPTY)
+MSG-NB-383: "The file has no header row" (BULK_FILE_EMPTY)
+MSG-NB-384: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-385: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
+MSG-NB-386: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
+MSG-NB-387: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
+MSG-NB-388: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
+MSG-NB-389: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
+MSG-NB-390: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
+MSG-NB-391: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
+MSG-NB-392: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
+MSG-NB-393: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
+MSG-NB-394: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
+MSG-NB-395: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
+MSG-NB-396: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-397: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-398: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-399: "BulkJob not found: &lt;job id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M465" s="12" t="inlineStr">
@@ -52977,18 +52982,18 @@
       <c r="L466" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-396: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
-MSG-NB-397: "The file is empty" (ATTACHMENT_EMPTY)
-MSG-NB-398: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
-MSG-NB-399: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
-MSG-NB-400: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
-MSG-NB-401: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
-MSG-NB-402: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
-MSG-NB-403: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
-MSG-NB-404: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
-MSG-NB-405: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
-MSG-NB-406: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-407: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-401: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
+MSG-NB-402: "The file is empty" (ATTACHMENT_EMPTY)
+MSG-NB-403: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
+MSG-NB-404: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
+MSG-NB-405: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
+MSG-NB-406: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
+MSG-NB-407: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
+MSG-NB-408: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
+MSG-NB-409: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
+MSG-NB-410: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
+MSG-NB-411: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-412: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M466" s="12" t="inlineStr">
@@ -53052,16 +53057,16 @@
       <c r="L467" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-409: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-410: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-411: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-412: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
-MSG-NB-413: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
-MSG-NB-414: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
-MSG-NB-415: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
-MSG-NB-416: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
-MSG-NB-417: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
-MSG-NB-418: "The item is closed" (WORK_CASE_CLOSED)</t>
+MSG-NB-414: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-415: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-416: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-417: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
+MSG-NB-418: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
+MSG-NB-419: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
+MSG-NB-420: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
+MSG-NB-421: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
+MSG-NB-422: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
+MSG-NB-423: "The item is closed" (WORK_CASE_CLOSED)</t>
         </is>
       </c>
       <c r="M467" s="12" t="inlineStr">
@@ -53137,10 +53142,10 @@
       <c r="L468" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-421: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-422: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
-MSG-NB-423: "The item is closed" (WORK_CASE_CLOSED)
-MSG-NB-424: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
+MSG-NB-426: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-427: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
+MSG-NB-428: "The item is closed" (WORK_CASE_CLOSED)
+MSG-NB-429: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M468" s="12" t="inlineStr">
@@ -53216,14 +53221,14 @@
       <c r="L469" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-427: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
-MSG-NB-428: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
-MSG-NB-429: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
-MSG-NB-430: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
-MSG-NB-431: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
-MSG-NB-432: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
-MSG-NB-433: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
-MSG-NB-434: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-432: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
+MSG-NB-433: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
+MSG-NB-434: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
+MSG-NB-435: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
+MSG-NB-436: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
+MSG-NB-437: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
+MSG-NB-438: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
+MSG-NB-439: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M469" s="12" t="inlineStr">
@@ -53299,12 +53304,12 @@
       <c r="L470" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-435: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-436: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
-MSG-NB-437: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
-MSG-NB-438: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
-MSG-NB-439: "LovType not found: &lt;type code&gt;" (NOT_FOUND)
-MSG-NB-440: "LovValue not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-440: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-441: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
+MSG-NB-442: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
+MSG-NB-443: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
+MSG-NB-444: "LovType not found: &lt;type code&gt;" (NOT_FOUND)
+MSG-NB-445: "LovValue not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M470" s="12" t="inlineStr">
@@ -53380,13 +53385,13 @@
       <c r="L471" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-441: "Enter a whole number of bookings (0 or more)"
-MSG-NB-442: "Enter an amount of 0 or more"
-MSG-NB-443: "Enter the period"
-MSG-NB-444: "Enter the unit code or the officer username"
-MSG-NB-447: "The period end must not be before the start"
-MSG-NB-448: "Targets cannot be negative" (TARGET_NEGATIVE)
-MSG-NB-449: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
+MSG-NB-446: "Enter a whole number of bookings (0 or more)"
+MSG-NB-447: "Enter an amount of 0 or more"
+MSG-NB-448: "Enter the period"
+MSG-NB-449: "Enter the unit code or the officer username"
+MSG-NB-452: "The period end must not be before the start"
+MSG-NB-453: "Targets cannot be negative" (TARGET_NEGATIVE)
+MSG-NB-454: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
         </is>
       </c>
       <c r="M471" s="12" t="inlineStr">
@@ -53462,9 +53467,9 @@
       <c r="L472" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-450: "ReportVariant not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-451: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
-MSG-NB-452: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
+MSG-NB-455: "ReportVariant not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-456: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
+MSG-NB-457: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
         </is>
       </c>
       <c r="M472" s="12" t="inlineStr">
@@ -53540,13 +53545,13 @@
       <c r="L473" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-457: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
-MSG-NB-458: "Document template not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-459: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-460: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
-MSG-NB-461: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
-MSG-NB-462: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
-MSG-NB-463: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
+MSG-NB-462: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
+MSG-NB-463: "Document template not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-464: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-465: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
+MSG-NB-466: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
+MSG-NB-467: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
+MSG-NB-468: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
         </is>
       </c>
       <c r="M473" s="12" t="inlineStr">
@@ -53610,15 +53615,15 @@
       <c r="L474" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-466: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-NB-467: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-NB-468: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
-MSG-NB-469: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-NB-470: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-NB-471: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
-MSG-NB-472: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
-MSG-NB-473: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-NB-474: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-NB-471: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-NB-472: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-NB-473: "An unexpected error occurred. Quote reference &lt;reference&gt; to support." (INTERNAL_ERROR)
+MSG-NB-474: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-NB-475: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-NB-476: "The request body is not valid JSON or has fields of the wrong type" (MALFORMED_REQUEST)
+MSG-NB-477: "No such endpoint: &lt;resource path&gt;" (NOT_FOUND)
+MSG-NB-478: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-NB-479: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M474" s="12" t="inlineStr">
@@ -53694,8 +53699,8 @@
       <c r="L475" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-479: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-NB-480: "&lt;Column&gt; is mandatory"</t>
+MSG-NB-484: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-NB-485: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M475" s="12" t="inlineStr">
@@ -53771,7 +53776,7 @@
       <c r="L476" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-481: "&lt;quotation no&gt; is &lt;status&gt;, not sent to the client"</t>
+MSG-NB-486: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
         </is>
       </c>
       <c r="M476" s="12" t="inlineStr">
@@ -53847,8 +53852,8 @@
       <c r="L477" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-482: "Account &lt;arn&gt; belongs to another company"
-MSG-NB-485: "The booking date &lt;date&gt; is in the future"</t>
+MSG-NB-487: "Account &lt;arn&gt; belongs to another company"
+MSG-NB-490: "The booking date &lt;date&gt; is in the future"</t>
         </is>
       </c>
       <c r="M477" s="12" t="inlineStr">
@@ -53924,9 +53929,9 @@
       <c r="L478" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-483: "Client Type must be INDIVIDUAL or CORPORATE"
-MSG-NB-484: "Client code &lt;code&gt; does not exist"
-MSG-NB-486: "The row matches several clients: &lt;details&gt;"</t>
+MSG-NB-488: "Client Type must be INDIVIDUAL or CORPORATE"
+MSG-NB-489: "Client code &lt;code&gt; does not exist"
+MSG-NB-491: "The row matches several clients: &lt;details&gt;"</t>
         </is>
       </c>
       <c r="M478" s="12" t="inlineStr">
@@ -53990,18 +53995,18 @@
       <c r="L479" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-487: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-488: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-489: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-490: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
-MSG-NB-491: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-492: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
-MSG-NB-493: "Notification not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-494: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-495: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-496: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
-MSG-NB-497: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-498: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)</t>
+MSG-NB-492: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-493: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-494: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-495: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
+MSG-NB-496: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-497: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
+MSG-NB-498: "Notification not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-499: "ProposalRequest not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-500: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-501: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
+MSG-NB-502: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-503: "WorkCase not found: &lt;case id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M479" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -12725,7 +12725,7 @@
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>Booking an issued account creates the invoice, the balanced journal and the service invoice in one transaction and the account shows Booked.</t>
+          <t>Booking an issued account creates the invoice, the balanced journal and the service invoice together (all or nothing) and the account shows Booked.</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr"/>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr"/>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr"/>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr"/>
@@ -17828,7 +17828,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr"/>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr"/>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr"/>
@@ -18735,7 +18735,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr"/>
@@ -19344,12 +19344,13 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>1. Look for edit or delete on Audit Trail rows; the DBA runs UPDATE, DELETE and TRUNCATE on the audit table in SIT.</t>
+          <t>1. Look for edit or delete on Audit Trail rows.
+2. The infrastructure administrator tries to change, delete and clear audit entries directly in the SIT environment.</t>
         </is>
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
-          <t>No such action on screen; the database refuses all three statements.</t>
+          <t>No such action on screen; every attempt is refused and the audit entries are unchanged.</t>
         </is>
       </c>
       <c r="M60" s="12" t="inlineStr">
@@ -20019,7 +20020,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr"/>
@@ -20168,7 +20169,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr"/>
@@ -20327,7 +20328,7 @@
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>The DBA changes the stored bytes of one test file in SIT.
+          <t>The infrastructure administrator alters the stored copy of one test file in SIT.
 Data: TD-NB-02 Seed clients; TD-NB-08 Seed issuance</t>
         </is>
       </c>
@@ -21313,7 +21314,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr"/>
@@ -22154,7 +22155,7 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr"/>
@@ -22768,7 +22769,7 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr"/>
@@ -24827,7 +24828,7 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr"/>
@@ -25206,7 +25207,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr"/>
@@ -25740,7 +25741,7 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I144" s="12" t="inlineStr"/>
@@ -26045,7 +26046,7 @@
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr"/>
@@ -26652,7 +26653,7 @@
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I156" s="12" t="inlineStr"/>
@@ -26725,7 +26726,7 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr"/>
@@ -27105,7 +27106,7 @@
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I162" s="12" t="inlineStr"/>
@@ -27792,7 +27793,7 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr"/>
@@ -28173,7 +28174,7 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I176" s="12" t="inlineStr"/>
@@ -29472,7 +29473,7 @@
       </c>
       <c r="H193" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I193" s="12" t="inlineStr"/>
@@ -29545,7 +29546,7 @@
       </c>
       <c r="H194" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I194" s="12" t="inlineStr"/>
@@ -29923,7 +29924,7 @@
       </c>
       <c r="H199" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I199" s="12" t="inlineStr"/>
@@ -33034,7 +33035,7 @@
       </c>
       <c r="H240" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I240" s="12" t="inlineStr"/>
@@ -33337,7 +33338,7 @@
       </c>
       <c r="H244" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I244" s="12" t="inlineStr"/>
@@ -33701,7 +33702,7 @@
       </c>
       <c r="E249" s="12" t="inlineStr">
         <is>
-          <t>Insurer set up for SFTP</t>
+          <t>Insurer set up for a channel other than e-mail</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
@@ -33716,14 +33717,10 @@
       </c>
       <c r="H249" s="12" t="inlineStr">
         <is>
-          <t>Placement &amp; Booking &gt; Placement Slips</t>
-        </is>
-      </c>
-      <c r="I249" s="12" t="inlineStr">
-        <is>
-          <t>SCR-NB-20</t>
-        </is>
-      </c>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
+        </is>
+      </c>
+      <c r="I249" s="12" t="inlineStr"/>
       <c r="J249" s="12" t="inlineStr">
         <is>
           <t>Data: TD-NB-07 Seed placement and billing</t>
@@ -33731,13 +33728,13 @@
       </c>
       <c r="K249" s="12" t="inlineStr">
         <is>
-          <t>1. Set the placement channel of an insurer branch to SFTP; save.</t>
+          <t>1. Save an insurer with a placement channel other than e-mail.</t>
         </is>
       </c>
       <c r="L249" s="12" t="inlineStr">
         <is>
           <t>Refused; only e-mail is available.
-Message "Only e-mail placement is available; SFTP and API channels await BDOI (Q06)" (PLACEMENT_CHANNEL_PARKED).</t>
+Message "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED).</t>
         </is>
       </c>
       <c r="M249" s="12" t="inlineStr">
@@ -34326,7 +34323,7 @@
       </c>
       <c r="H257" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I257" s="12" t="inlineStr"/>
@@ -34628,7 +34625,7 @@
       </c>
       <c r="H261" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I261" s="12" t="inlineStr"/>
@@ -35159,7 +35156,7 @@
       </c>
       <c r="H268" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I268" s="12" t="inlineStr"/>
@@ -35384,7 +35381,7 @@
       </c>
       <c r="H271" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I271" s="12" t="inlineStr"/>
@@ -35457,7 +35454,7 @@
       </c>
       <c r="H272" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I272" s="12" t="inlineStr"/>
@@ -35606,7 +35603,7 @@
       </c>
       <c r="H274" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I274" s="12" t="inlineStr"/>
@@ -36215,7 +36212,7 @@
       </c>
       <c r="H282" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I282" s="12" t="inlineStr"/>
@@ -37436,7 +37433,7 @@
       </c>
       <c r="H298" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I298" s="12" t="inlineStr"/>
@@ -37509,7 +37506,7 @@
       </c>
       <c r="H299" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I299" s="12" t="inlineStr"/>
@@ -37890,7 +37887,7 @@
       </c>
       <c r="H304" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I304" s="12" t="inlineStr"/>
@@ -38116,7 +38113,7 @@
       </c>
       <c r="H307" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I307" s="12" t="inlineStr"/>
@@ -38874,7 +38871,7 @@
       </c>
       <c r="H317" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I317" s="12" t="inlineStr"/>
@@ -39176,7 +39173,7 @@
       </c>
       <c r="H321" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I321" s="12" t="inlineStr"/>
@@ -39934,7 +39931,7 @@
       </c>
       <c r="H331" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I331" s="12" t="inlineStr"/>
@@ -41002,7 +40999,7 @@
       </c>
       <c r="H345" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I345" s="12" t="inlineStr"/>
@@ -42067,7 +42064,7 @@
       </c>
       <c r="H359" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I359" s="12" t="inlineStr"/>
@@ -42212,7 +42209,7 @@
       </c>
       <c r="H361" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I361" s="12" t="inlineStr"/>
@@ -43122,7 +43119,7 @@
       </c>
       <c r="H373" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I373" s="12" t="inlineStr"/>
@@ -44081,7 +44078,7 @@
       </c>
       <c r="H386" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I386" s="12" t="inlineStr"/>
@@ -44170,7 +44167,7 @@
       </c>
       <c r="L387" s="12" t="inlineStr">
         <is>
-          <t>None is offered; the database refuses changes.</t>
+          <t>None is offered; an attempt to change an entry outside the screens is refused.</t>
         </is>
       </c>
       <c r="M387" s="12" t="inlineStr">
@@ -48097,19 +48094,21 @@
 MSG-NB-012: "The birth date must be in the past" (CLIENT_BIRTH_DATE)
 MSG-NB-013: "This client already exists: &lt;existing&gt;" (CLIENT_DUPLICATE)
 MSG-NB-014: "Enter a valid e-mail address" (CLIENT_EMAIL_FORMAT)
-MSG-NB-015: "An inactive client cannot be changed" (CLIENT_INACTIVE)
-MSG-NB-016: "Client &lt;code&gt; is inactive" (CLIENT_INACTIVE)
-MSG-NB-017: "The client is already inactive" (CLIENT_INACTIVE)
-MSG-NB-018: "Enter the mobile number as 09xxxxxxxxx or +639xxxxxxxxx" (CLIENT_MOBILE_FORMAT)
-MSG-NB-019: "Enter the &lt;field&gt;" (CLIENT_NAME_REQUIRED)
-MSG-NB-020: "Client &lt;code&gt; is not yet confirmed (onboarding and KYC incomplete)" (CLIENT_NOT_CONFIRMED)
-MSG-NB-021: "Only a prospect can be confirmed" (CLIENT_NOT_PROSPECT)
-MSG-NB-022: "Enter the TIN as 000-000-000-000" (CLIENT_TIN_FORMAT)
-MSG-NB-023: "The client type of a confirmed client cannot be changed" (CLIENT_TYPE_LOCKED)
-MSG-NB-024: "An individual policyholder must be at least &lt;minimum age&gt; years old" (CLIENT_UNDER_AGE)
-MSG-NB-025: "'&lt;code&gt;' is not a valid value of &lt;type&gt; on &lt;today&gt;" (LOV_VALUE_INVALID)
-MSG-NB-026: "Client not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-027: "Client not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-015: "Enter the &lt;label&gt; in at most &lt;max&gt; characters" (CLIENT_FIELD_TOO_LONG)
+MSG-NB-016: "An inactive client cannot be changed" (CLIENT_INACTIVE)
+MSG-NB-017: "Client &lt;code&gt; is inactive" (CLIENT_INACTIVE)
+MSG-NB-018: "The client is already inactive" (CLIENT_INACTIVE)
+MSG-NB-019: "Enter the mobile number as 09xxxxxxxxx or +639xxxxxxxxx" (CLIENT_MOBILE_FORMAT)
+MSG-NB-020: "Enter the &lt;field&gt;" (CLIENT_NAME_REQUIRED)
+MSG-NB-021: "Client &lt;code&gt; is not yet confirmed (onboarding and KYC incomplete)" (CLIENT_NOT_CONFIRMED)
+MSG-NB-022: "Only a prospect can be confirmed" (CLIENT_NOT_PROSPECT)
+MSG-NB-023: "Enter the phone number with digits and separators" (CLIENT_PHONE_FORMAT)
+MSG-NB-024: "Enter the TIN as 000-000-000-000" (CLIENT_TIN_FORMAT)
+MSG-NB-025: "The client type of a confirmed client cannot be changed" (CLIENT_TYPE_LOCKED)
+MSG-NB-026: "An individual policyholder must be at least &lt;minimum age&gt; years old" (CLIENT_UNDER_AGE)
+MSG-NB-027: "'&lt;code&gt;' is not a valid value of &lt;type&gt; on &lt;today&gt;" (LOV_VALUE_INVALID)
+MSG-NB-028: "Client not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-029: "Client not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M437" s="12" t="inlineStr">
@@ -48184,11 +48183,11 @@
       <c r="L438" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-033: "The client is inactive" (CLIENT_INACTIVE)
-MSG-NB-034: "Complete the client information before you &lt;step&gt;: &lt;missing&gt;" (CLIENT_INFO_INCOMPLETE)
-MSG-NB-035: "Upload the mandatory KYC documents before you &lt;step&gt;: &lt;missing&gt;" (KYC_DOCUMENTS_MISSING)
-MSG-NB-036: "The KYC must be verified by a user other than its maker" (KYC_FOUR_EYES)
-MSG-NB-037: "Client &lt;code&gt; has no verified KYC" (KYC_NOT_VERIFIED)</t>
+MSG-NB-035: "The client is inactive" (CLIENT_INACTIVE)
+MSG-NB-036: "Complete the client information before you &lt;step&gt;: &lt;missing&gt;" (CLIENT_INFO_INCOMPLETE)
+MSG-NB-037: "Upload the mandatory KYC documents before you &lt;step&gt;: &lt;missing&gt;" (KYC_DOCUMENTS_MISSING)
+MSG-NB-038: "The KYC must be verified by a user other than its maker" (KYC_FOUR_EYES)
+MSG-NB-039: "Client &lt;code&gt; has no verified KYC" (KYC_NOT_VERIFIED)</t>
         </is>
       </c>
       <c r="M438" s="12" t="inlineStr">
@@ -48263,16 +48262,16 @@
       <c r="L439" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-038: "Enter the first day"
-MSG-NB-039: "Enter the instruction"
-MSG-NB-042: "Select the instruction type"
-MSG-NB-045: "The end date must not be before the start date"
-MSG-NB-046: "The client is already tagged &lt;tag code&gt;" (CLIENT_TAG_EXISTS)
-MSG-NB-047: "The end date must not be before the start date" (INSTRUCTION_DATES)
-MSG-NB-048: "An ended instruction cannot be changed" (INSTRUCTION_ENDED)
-MSG-NB-049: "Enter the instruction" (INSTRUCTION_TEXT_REQUIRED)
-MSG-NB-050: "Client instruction not found: &lt;instruction id&gt;" (NOT_FOUND)
-MSG-NB-051: "Client tag not found: &lt;tag code&gt;" (NOT_FOUND)</t>
+MSG-NB-040: "Enter the first day"
+MSG-NB-041: "Enter the instruction"
+MSG-NB-044: "Select the instruction type"
+MSG-NB-047: "The end date must not be before the start date"
+MSG-NB-048: "The client is already tagged &lt;tag code&gt;" (CLIENT_TAG_EXISTS)
+MSG-NB-049: "The end date must not be before the start date" (INSTRUCTION_DATES)
+MSG-NB-050: "An ended instruction cannot be changed" (INSTRUCTION_ENDED)
+MSG-NB-051: "Enter the instruction" (INSTRUCTION_TEXT_REQUIRED)
+MSG-NB-052: "Client instruction not found: &lt;instruction id&gt;" (NOT_FOUND)
+MSG-NB-053: "Client tag not found: &lt;tag code&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M439" s="12" t="inlineStr">
@@ -48347,11 +48346,11 @@
       <c r="L440" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-054: "Client information incomplete: &lt;missing&gt;" (INFO_INCOMPLETE)
-MSG-NB-055: "The periodic KYC review was due on &lt;kyc review due&gt;" (KYC_EXPIRED)
-MSG-NB-056: "Confirmed client without a sub-ledger party code" (MISSING_PARTY)
-MSG-NB-057: "Party &lt;party code&gt; is not active" (PARTY_INACTIVE)
-MSG-NB-058: "Party &lt;party code&gt; does not exist" (PARTY_NOT_FOUND)</t>
+MSG-NB-056: "Client information incomplete: &lt;missing&gt;" (INFO_INCOMPLETE)
+MSG-NB-057: "The periodic KYC review was due on &lt;kyc review due&gt;" (KYC_EXPIRED)
+MSG-NB-058: "Confirmed client without a sub-ledger party code" (MISSING_PARTY)
+MSG-NB-059: "Party &lt;party code&gt; is not active" (PARTY_INACTIVE)
+MSG-NB-060: "Party &lt;party code&gt; does not exist" (PARTY_NOT_FOUND)</t>
         </is>
       </c>
       <c r="M440" s="12" t="inlineStr">
@@ -48426,15 +48425,15 @@
       <c r="L441" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-065: "Choose the client or give the prospect name"
-MSG-NB-066: "Describe the requested cover"
-MSG-NB-067: "Enter a valid e-mail address"
-MSG-NB-069: "Quotation request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-070: "Give the client code or the prospect's name" (QUOTATION_REQUEST_CLIENT)
-MSG-NB-071: "Request &lt;request no&gt; is already &lt;status&gt;" (QUOTATION_REQUEST_CLOSED)
-MSG-NB-072: "Request &lt;external ref&gt; of &lt;channel&gt; was already received" (QUOTATION_REQUEST_DUPLICATE)
-MSG-NB-073: "Request &lt;request no&gt; has a client" (QUOTATION_REQUEST_HAS_CLIENT)
-MSG-NB-074: "Give the reason for closing" (QUOTATION_REQUEST_REASON)</t>
+MSG-NB-067: "Choose the client or give the prospect name"
+MSG-NB-068: "Describe the requested cover"
+MSG-NB-069: "Enter a valid e-mail address"
+MSG-NB-071: "Quotation request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-072: "Give the client code or the prospect's name" (QUOTATION_REQUEST_CLIENT)
+MSG-NB-073: "Request &lt;request no&gt; is already &lt;status&gt;" (QUOTATION_REQUEST_CLOSED)
+MSG-NB-074: "Request &lt;external ref&gt; of &lt;channel&gt; was already received" (QUOTATION_REQUEST_DUPLICATE)
+MSG-NB-075: "Request &lt;request no&gt; has a client" (QUOTATION_REQUEST_HAS_CLIENT)
+MSG-NB-076: "Give the reason for closing" (QUOTATION_REQUEST_REASON)</t>
         </is>
       </c>
       <c r="M441" s="12" t="inlineStr">
@@ -48509,9 +48508,9 @@
       <c r="L442" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-077: "Select the quotations to send" (QUOTATION_BATCH_EMPTY)
-MSG-NB-078: "Cannot send: &lt;problems&gt;" (QUOTATION_BATCH_INVALID)
-MSG-NB-079: "Quotation &lt;quotation no&gt; must be approved before it is sent" (QUOTATION_NOT_APPROVED)</t>
+MSG-NB-079: "Select the quotations to send" (QUOTATION_BATCH_EMPTY)
+MSG-NB-080: "Cannot send: &lt;problems&gt;" (QUOTATION_BATCH_INVALID)
+MSG-NB-081: "Quotation &lt;quotation no&gt; must be approved before it is sent" (QUOTATION_NOT_APPROVED)</t>
         </is>
       </c>
       <c r="M442" s="12" t="inlineStr">
@@ -48586,9 +48585,9 @@
       <c r="L443" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-080: "Attach the client's acceptance e-mail (document type Client acceptance e-mail) first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-081: "The quotation offers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-082: "Record the client's acceptance first" (QUOTATION_NOT_ACCEPTED)</t>
+MSG-NB-082: "Attach the client's acceptance e-mail (document type Client acceptance e-mail) first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-083: "The quotation offers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-084: "Record the client's acceptance first" (QUOTATION_NOT_ACCEPTED)</t>
         </is>
       </c>
       <c r="M443" s="12" t="inlineStr">
@@ -48663,30 +48662,30 @@
       <c r="L444" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-085: "Add at least one risk item"
-MSG-NB-086: "Enter the sum insured of every item"
-MSG-NB-087: "Select the client or prospect"
-MSG-NB-088: "Select the product"
-MSG-NB-089: "The period end must be after the period start"
-MSG-NB-090: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-091: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-092: "Give the client code or the prospect's name" (QUOTATION_CLIENT_REQUIRED)
-MSG-NB-093: "The validity date has passed: change it before submitting" (QUOTATION_EXPIRED)
-MSG-NB-094: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
-MSG-NB-095: "Select the client and the product" (QUOTATION_INCOMPLETE)
-MSG-NB-096: "Select the product" (QUOTATION_INCOMPLETE)
-MSG-NB-097: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
-MSG-NB-098: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
-MSG-NB-099: "Add at least one risk item" (QUOTATION_NO_ITEMS)
-MSG-NB-100: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
-MSG-NB-101: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
-MSG-NB-102: "Renewal &lt;renewal ref&gt; already has quotation &lt;quotation no&gt;" (QUOTATION_RENEWAL_EXISTS)
-MSG-NB-103: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
-MSG-NB-104: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
-MSG-NB-105: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
-MSG-NB-106: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-107: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
-MSG-NB-108: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-087: "Add at least one risk item"
+MSG-NB-088: "Enter the sum insured of every item"
+MSG-NB-089: "Select the client or prospect"
+MSG-NB-090: "Select the product"
+MSG-NB-091: "The period end must be after the period start"
+MSG-NB-092: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-093: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-094: "Give the client code or the prospect's name" (QUOTATION_CLIENT_REQUIRED)
+MSG-NB-095: "The validity date has passed: change it before submitting" (QUOTATION_EXPIRED)
+MSG-NB-096: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
+MSG-NB-097: "Select the client and the product" (QUOTATION_INCOMPLETE)
+MSG-NB-098: "Select the product" (QUOTATION_INCOMPLETE)
+MSG-NB-099: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
+MSG-NB-100: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
+MSG-NB-101: "Add at least one risk item" (QUOTATION_NO_ITEMS)
+MSG-NB-102: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
+MSG-NB-103: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
+MSG-NB-104: "Renewal &lt;renewal ref&gt; already has quotation &lt;quotation no&gt;" (QUOTATION_RENEWAL_EXISTS)
+MSG-NB-105: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
+MSG-NB-106: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
+MSG-NB-107: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
+MSG-NB-108: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-109: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
+MSG-NB-110: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M444" s="12" t="inlineStr">
@@ -48761,8 +48760,8 @@
       <c r="L445" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-110: "Enter the item rate between 0 and 100"
-MSG-NB-111: "Explain why the scheme rate cannot be used"</t>
+MSG-NB-112: "Enter the item rate between 0 and 100"
+MSG-NB-113: "Explain why the scheme rate cannot be used"</t>
         </is>
       </c>
       <c r="M445" s="12" t="inlineStr">
@@ -48837,20 +48836,20 @@
       <c r="L446" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-118: "Select the client or prospect"
-MSG-NB-119: "Select the product"
-MSG-NB-120: "The period end must be after the period start"
-MSG-NB-121: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
-MSG-NB-122: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-123: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
-MSG-NB-124: "Complete the PRF header" (PRF_INCOMPLETE)
-MSG-NB-125: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
-MSG-NB-126: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
-MSG-NB-127: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
-MSG-NB-128: "The period end must be after the period start" (PRF_PERIOD_INVALID)
-MSG-NB-129: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
-MSG-NB-130: "Renewal &lt;renewal ref&gt; already has proposal request &lt;prf no&gt;" (PROPOSAL_RENEWAL_EXISTS)
-MSG-NB-131: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-120: "Select the client or prospect"
+MSG-NB-121: "Select the product"
+MSG-NB-122: "The period end must be after the period start"
+MSG-NB-123: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
+MSG-NB-124: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-125: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
+MSG-NB-126: "Complete the PRF header" (PRF_INCOMPLETE)
+MSG-NB-127: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
+MSG-NB-128: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
+MSG-NB-129: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
+MSG-NB-130: "The period end must be after the period start" (PRF_PERIOD_INVALID)
+MSG-NB-131: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
+MSG-NB-132: "Renewal &lt;renewal ref&gt; already has proposal request &lt;prf no&gt;" (PROPOSAL_RENEWAL_EXISTS)
+MSG-NB-133: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M446" s="12" t="inlineStr">
@@ -48925,27 +48924,27 @@
       <c r="L447" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-135: "Enter the premium quoted"
-MSG-NB-142: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-143: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-144: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
-MSG-NB-145: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
-MSG-NB-146: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
-MSG-NB-147: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
-MSG-NB-148: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
-MSG-NB-149: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
-MSG-NB-150: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
-MSG-NB-151: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
-MSG-NB-152: "The chosen terms are gone" (PS_TERMS_MISSING)
-MSG-NB-153: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
-MSG-NB-154: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
-MSG-NB-155: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
-MSG-NB-156: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
-MSG-NB-157: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
-MSG-NB-158: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
-MSG-NB-159: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
-MSG-NB-160: "No insurer terms have been received" (TERMS_NONE)
-MSG-NB-161: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
+MSG-NB-137: "Enter the premium quoted"
+MSG-NB-144: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-145: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-146: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
+MSG-NB-147: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
+MSG-NB-148: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
+MSG-NB-149: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
+MSG-NB-150: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
+MSG-NB-151: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
+MSG-NB-152: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
+MSG-NB-153: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
+MSG-NB-154: "The chosen terms are gone" (PS_TERMS_MISSING)
+MSG-NB-155: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
+MSG-NB-156: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
+MSG-NB-157: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
+MSG-NB-158: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
+MSG-NB-159: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
+MSG-NB-160: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
+MSG-NB-161: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
+MSG-NB-162: "No insurer terms have been received" (TERMS_NONE)
+MSG-NB-163: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
         </is>
       </c>
       <c r="M447" s="12" t="inlineStr">
@@ -49020,12 +49019,12 @@
       <c r="L448" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-164: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
-MSG-NB-165: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-166: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-167: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
-MSG-NB-168: "Enter the Free First Year start" (FFY_START_REQUIRED)
-MSG-NB-169: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
+MSG-NB-166: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
+MSG-NB-167: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-168: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-169: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
+MSG-NB-170: "Enter the Free First Year start" (FFY_START_REQUIRED)
+MSG-NB-171: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
         </is>
       </c>
       <c r="M448" s="12" t="inlineStr">
@@ -49100,22 +49099,22 @@
       <c r="L449" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-172: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-173: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
-MSG-NB-174: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
-MSG-NB-175: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
-MSG-NB-176: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
-MSG-NB-177: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
-MSG-NB-178: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
-MSG-NB-179: "Select the new insurer" (INSURER_REQUIRED)
-MSG-NB-180: "Select an insurer other than the current one" (INSURER_UNCHANGED)
-MSG-NB-181: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-182: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-183: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
-MSG-NB-184: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
-MSG-NB-185: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
-MSG-NB-186: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
-MSG-NB-187: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
+MSG-NB-174: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-175: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
+MSG-NB-176: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
+MSG-NB-177: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
+MSG-NB-178: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
+MSG-NB-179: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
+MSG-NB-180: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
+MSG-NB-181: "Select the new insurer" (INSURER_REQUIRED)
+MSG-NB-182: "Select an insurer other than the current one" (INSURER_UNCHANGED)
+MSG-NB-183: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-184: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-185: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
+MSG-NB-186: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
+MSG-NB-187: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
+MSG-NB-188: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
+MSG-NB-189: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
         </is>
       </c>
       <c r="M449" s="12" t="inlineStr">
@@ -49190,25 +49189,25 @@
       <c r="L450" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-189: "Choose the client and product to save the draft."
-MSG-NB-190: "The draft is not saved yet: click Save Draft to check it before submission."
-MSG-NB-191: "The draft was not saved: correct what the message above describes, then save the draft again."
-MSG-NB-192: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
-MSG-NB-193: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
-MSG-NB-194: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
-MSG-NB-195: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
-MSG-NB-196: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
-MSG-NB-197: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
-MSG-NB-198: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
-MSG-NB-199: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-200: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
-MSG-NB-201: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-202: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
-MSG-NB-203: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
-MSG-NB-204: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
-MSG-NB-205: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
-MSG-NB-206: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-207: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-191: "Choose the client and product to save the draft."
+MSG-NB-192: "The draft is not saved yet: click Save Draft to check it before submission."
+MSG-NB-193: "The draft was not saved: correct what the message above describes, then save the draft again."
+MSG-NB-194: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
+MSG-NB-195: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
+MSG-NB-196: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
+MSG-NB-197: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
+MSG-NB-198: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
+MSG-NB-199: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
+MSG-NB-200: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
+MSG-NB-201: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-202: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
+MSG-NB-203: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-204: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
+MSG-NB-205: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
+MSG-NB-206: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
+MSG-NB-207: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
+MSG-NB-208: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-209: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M450" s="12" t="inlineStr">
@@ -49283,9 +49282,9 @@
       <c r="L451" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-212: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-213: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
-MSG-NB-214: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
+MSG-NB-214: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-215: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
+MSG-NB-216: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
         </is>
       </c>
       <c r="M451" s="12" t="inlineStr">
@@ -49360,17 +49359,17 @@
       <c r="L452" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-217: "Record Hold Cover Confirmation"
-MSG-NB-218: "Record Hold Cover Decline"
-MSG-NB-219: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
-MSG-NB-220: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
-MSG-NB-221: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
-MSG-NB-222: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
-MSG-NB-223: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
-MSG-NB-224: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
-MSG-NB-225: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
-MSG-NB-226: "Choose the insurer on the account first" (INSURER_NOT_SET)
-MSG-NB-227: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
+MSG-NB-219: "Record Hold Cover Confirmation"
+MSG-NB-220: "Record Hold Cover Decline"
+MSG-NB-221: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
+MSG-NB-222: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
+MSG-NB-223: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
+MSG-NB-224: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
+MSG-NB-225: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
+MSG-NB-226: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
+MSG-NB-227: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
+MSG-NB-228: "Choose the insurer on the account first" (INSURER_NOT_SET)
+MSG-NB-229: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
         </is>
       </c>
       <c r="M452" s="12" t="inlineStr">
@@ -49445,20 +49444,20 @@
       <c r="L453" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-236: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-237: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
-MSG-NB-238: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
-MSG-NB-239: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
-MSG-NB-240: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-241: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
-MSG-NB-242: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
-MSG-NB-243: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
-MSG-NB-244: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
-MSG-NB-245: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
-MSG-NB-246: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
-MSG-NB-247: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
-MSG-NB-248: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
-MSG-NB-249: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
+MSG-NB-238: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-239: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
+MSG-NB-240: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
+MSG-NB-241: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
+MSG-NB-242: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-243: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
+MSG-NB-244: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
+MSG-NB-245: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
+MSG-NB-246: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
+MSG-NB-247: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
+MSG-NB-248: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
+MSG-NB-249: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
+MSG-NB-250: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
+MSG-NB-251: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
         </is>
       </c>
       <c r="M453" s="12" t="inlineStr">
@@ -49533,10 +49532,10 @@
       <c r="L454" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-253: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
-MSG-NB-254: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
-MSG-NB-255: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
-MSG-NB-256: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-255: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
+MSG-NB-256: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
+MSG-NB-257: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
+MSG-NB-258: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M454" s="12" t="inlineStr">
@@ -49611,19 +49610,19 @@
       <c r="L455" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-258: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-259: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
-MSG-NB-260: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
-MSG-NB-261: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
-MSG-NB-262: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-263: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
-MSG-NB-264: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
-MSG-NB-265: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
-MSG-NB-266: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
-MSG-NB-267: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-268: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-269: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
-MSG-NB-270: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
+MSG-NB-260: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-261: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
+MSG-NB-262: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
+MSG-NB-263: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
+MSG-NB-264: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-265: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
+MSG-NB-266: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
+MSG-NB-267: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
+MSG-NB-268: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
+MSG-NB-269: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-270: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
+MSG-NB-272: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
         </is>
       </c>
       <c r="M455" s="12" t="inlineStr">
@@ -49698,14 +49697,14 @@
       <c r="L456" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-273: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
-MSG-NB-274: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
-MSG-NB-275: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
-MSG-NB-276: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
-MSG-NB-277: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
-MSG-NB-278: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-279: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
-MSG-NB-280: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-275: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
+MSG-NB-276: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
+MSG-NB-277: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
+MSG-NB-278: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
+MSG-NB-279: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
+MSG-NB-280: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-281: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
+MSG-NB-282: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M456" s="12" t="inlineStr">
@@ -49780,10 +49779,10 @@
       <c r="L457" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-282: "Enter one policy number per policy year."
-MSG-NB-285: "The policy numbers must be different."
-MSG-NB-286: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
-MSG-NB-287: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
+MSG-NB-284: "Enter one policy number per policy year."
+MSG-NB-287: "The policy numbers must be different."
+MSG-NB-288: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
+MSG-NB-289: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
         </is>
       </c>
       <c r="M457" s="12" t="inlineStr">
@@ -49858,10 +49857,10 @@
       <c r="L458" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-290: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
-MSG-NB-291: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
-MSG-NB-292: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
-MSG-NB-293: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-292: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
+MSG-NB-293: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
+MSG-NB-294: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
+MSG-NB-295: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M458" s="12" t="inlineStr">
@@ -49936,8 +49935,8 @@
       <c r="L459" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-296: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
-MSG-NB-297: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
+MSG-NB-298: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
+MSG-NB-299: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
         </is>
       </c>
       <c r="M459" s="12" t="inlineStr">
@@ -50012,22 +50011,22 @@
       <c r="L460" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-300: "A negative endorsement reduces the sum insured (enter a minus)"
-MSG-NB-301: "A positive endorsement increases the sum insured"
-MSG-NB-302: "Choose the reason"
-MSG-NB-303: "Describe the cancellation"
-MSG-NB-304: "Describe the change"
-MSG-NB-305: "Enter a booking date that is not in the future"
-MSG-NB-306: "Enter a rate of zero or more, or leave it blank"
-MSG-NB-307: "Enter the cancellation date"
-MSG-NB-308: "Enter the change of the sum insured"
-MSG-NB-309: "Enter the effective date"
-MSG-NB-311: "The booking date cannot be in the future"
-MSG-NB-312: "No queued account to book" (BATCH_EMPTY)
-MSG-NB-313: "Select at least one account to book" (BATCH_EMPTY)
-MSG-NB-314: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-315: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-316: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
+MSG-NB-302: "A negative endorsement reduces the sum insured (enter a minus)"
+MSG-NB-303: "A positive endorsement increases the sum insured"
+MSG-NB-304: "Choose the reason"
+MSG-NB-305: "Describe the cancellation"
+MSG-NB-306: "Describe the change"
+MSG-NB-307: "Enter a booking date that is not in the future"
+MSG-NB-308: "Enter a rate of zero or more, or leave it blank"
+MSG-NB-309: "Enter the cancellation date"
+MSG-NB-310: "Enter the change of the sum insured"
+MSG-NB-311: "Enter the effective date"
+MSG-NB-313: "The booking date cannot be in the future"
+MSG-NB-314: "No queued account to book" (BATCH_EMPTY)
+MSG-NB-315: "Select at least one account to book" (BATCH_EMPTY)
+MSG-NB-316: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-317: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-318: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
         </is>
       </c>
       <c r="M460" s="12" t="inlineStr">
@@ -50102,25 +50101,25 @@
       <c r="L461" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-318: "Enter a booking date that is not in the future"
-MSG-NB-319: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
-MSG-NB-320: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
-MSG-NB-321: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
-MSG-NB-322: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
-MSG-NB-323: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
-MSG-NB-324: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
-MSG-NB-325: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
-MSG-NB-326: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-327: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
-MSG-NB-328: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
-MSG-NB-329: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
-MSG-NB-330: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
-MSG-NB-331: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
-MSG-NB-332: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
-MSG-NB-333: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
-MSG-NB-334: "No invoice" (INVOICE_NOT_FOUND)
-MSG-NB-335: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
-MSG-NB-336: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
+MSG-NB-320: "Enter a booking date that is not in the future"
+MSG-NB-321: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
+MSG-NB-322: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
+MSG-NB-323: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
+MSG-NB-324: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
+MSG-NB-325: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
+MSG-NB-326: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
+MSG-NB-327: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
+MSG-NB-328: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-329: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
+MSG-NB-330: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
+MSG-NB-331: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
+MSG-NB-332: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
+MSG-NB-333: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
+MSG-NB-334: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
+MSG-NB-335: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
+MSG-NB-336: "No invoice" (INVOICE_NOT_FOUND)
+MSG-NB-337: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
+MSG-NB-338: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
         </is>
       </c>
       <c r="M461" s="12" t="inlineStr">
@@ -50195,15 +50194,15 @@
       <c r="L462" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-342: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
-MSG-NB-343: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
-MSG-NB-344: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
-MSG-NB-345: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
-MSG-NB-346: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
-MSG-NB-347: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-348: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-349: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
-MSG-NB-350: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-NB-344: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
+MSG-NB-345: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
+MSG-NB-346: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
+MSG-NB-347: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
+MSG-NB-348: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
+MSG-NB-349: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-350: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-351: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
+MSG-NB-352: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M462" s="12" t="inlineStr">
@@ -50278,14 +50277,14 @@
       <c r="L463" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-352: "Give the reason of the credit"
-MSG-NB-354: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
-MSG-NB-355: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
-MSG-NB-356: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-357: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
-MSG-NB-358: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-359: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
-MSG-NB-360: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
+MSG-NB-354: "Give the reason of the credit"
+MSG-NB-356: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
+MSG-NB-357: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
+MSG-NB-358: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-359: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
+MSG-NB-360: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-361: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
+MSG-NB-362: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
         </is>
       </c>
       <c r="M463" s="12" t="inlineStr">
@@ -50360,12 +50359,12 @@
       <c r="L464" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-363: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-364: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
-MSG-NB-365: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
-MSG-NB-366: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-367: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-368: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-365: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-366: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
+MSG-NB-367: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
+MSG-NB-368: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-369: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-370: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M464" s="12" t="inlineStr">
@@ -50440,31 +50439,31 @@
       <c r="L465" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-373: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
-MSG-NB-374: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-375: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-376: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
-MSG-NB-377: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
-MSG-NB-378: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
-MSG-NB-379: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
-MSG-NB-380: "The file has no data rows" (BULK_FILE_EMPTY)
-MSG-NB-381: "The file has no header row" (BULK_FILE_EMPTY)
-MSG-NB-382: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
-MSG-NB-383: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
-MSG-NB-384: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
-MSG-NB-385: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
-MSG-NB-386: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
-MSG-NB-387: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
-MSG-NB-388: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
-MSG-NB-389: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
-MSG-NB-390: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
-MSG-NB-391: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
-MSG-NB-392: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
-MSG-NB-393: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
-MSG-NB-394: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-395: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-396: "Bulk job not found: &lt;job id&gt;" (NOT_FOUND)
-MSG-NB-397: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)</t>
+MSG-NB-375: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
+MSG-NB-376: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-377: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-378: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
+MSG-NB-379: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
+MSG-NB-380: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
+MSG-NB-381: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
+MSG-NB-382: "The file has no data rows" (BULK_FILE_EMPTY)
+MSG-NB-383: "The file has no header row" (BULK_FILE_EMPTY)
+MSG-NB-384: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-385: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
+MSG-NB-386: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
+MSG-NB-387: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
+MSG-NB-388: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
+MSG-NB-389: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
+MSG-NB-390: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
+MSG-NB-391: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
+MSG-NB-392: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
+MSG-NB-393: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
+MSG-NB-394: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
+MSG-NB-395: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
+MSG-NB-396: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-397: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-398: "Bulk job not found: &lt;job id&gt;" (NOT_FOUND)
+MSG-NB-399: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M465" s="12" t="inlineStr">
@@ -50527,18 +50526,18 @@
       <c r="L466" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-399: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
-MSG-NB-400: "The file is empty" (ATTACHMENT_EMPTY)
-MSG-NB-401: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
-MSG-NB-402: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
-MSG-NB-403: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
-MSG-NB-404: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
-MSG-NB-405: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
-MSG-NB-406: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
-MSG-NB-407: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
-MSG-NB-408: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
-MSG-NB-409: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-410: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-401: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
+MSG-NB-402: "The file is empty" (ATTACHMENT_EMPTY)
+MSG-NB-403: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
+MSG-NB-404: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
+MSG-NB-405: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
+MSG-NB-406: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
+MSG-NB-407: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
+MSG-NB-408: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
+MSG-NB-409: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
+MSG-NB-410: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
+MSG-NB-411: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-412: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M466" s="12" t="inlineStr">
@@ -50601,16 +50600,16 @@
       <c r="L467" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-412: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-413: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-414: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-415: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
-MSG-NB-416: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
-MSG-NB-417: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
-MSG-NB-418: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
-MSG-NB-419: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
-MSG-NB-420: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
-MSG-NB-421: "The item is closed" (WORK_CASE_CLOSED)</t>
+MSG-NB-414: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-415: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-416: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-417: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
+MSG-NB-418: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
+MSG-NB-419: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
+MSG-NB-420: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
+MSG-NB-421: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
+MSG-NB-422: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
+MSG-NB-423: "The item is closed" (WORK_CASE_CLOSED)</t>
         </is>
       </c>
       <c r="M467" s="12" t="inlineStr">
@@ -50685,10 +50684,10 @@
       <c r="L468" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-424: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-425: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
-MSG-NB-426: "The item is closed" (WORK_CASE_CLOSED)
-MSG-NB-427: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
+MSG-NB-426: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-427: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
+MSG-NB-428: "The item is closed" (WORK_CASE_CLOSED)
+MSG-NB-429: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M468" s="12" t="inlineStr">
@@ -50763,14 +50762,14 @@
       <c r="L469" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-430: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
-MSG-NB-431: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
-MSG-NB-432: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
-MSG-NB-433: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
-MSG-NB-434: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
-MSG-NB-435: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
-MSG-NB-436: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
-MSG-NB-437: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-432: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
+MSG-NB-433: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
+MSG-NB-434: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
+MSG-NB-435: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
+MSG-NB-436: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
+MSG-NB-437: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
+MSG-NB-438: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
+MSG-NB-439: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M469" s="12" t="inlineStr">
@@ -50845,17 +50844,17 @@
       <c r="L470" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-439: "Enter a whole number"
-MSG-NB-440: "Enter the first valid date"
-MSG-NB-441: "Enter the label"
-MSG-NB-442: "Must not be before the first valid date"
-MSG-NB-443: "Use capital letters, digits and _ (up to 40)"
-MSG-NB-444: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-445: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
-MSG-NB-446: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
-MSG-NB-447: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
-MSG-NB-448: "List type not found: &lt;type code&gt;" (NOT_FOUND)
-MSG-NB-449: "List value not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-441: "Enter a whole number"
+MSG-NB-442: "Enter the first valid date"
+MSG-NB-443: "Enter the label"
+MSG-NB-444: "Must not be before the first valid date"
+MSG-NB-445: "Use capital letters, digits and _ (up to 40)"
+MSG-NB-446: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-447: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
+MSG-NB-448: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
+MSG-NB-449: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
+MSG-NB-450: "List type not found: &lt;type code&gt;" (NOT_FOUND)
+MSG-NB-451: "List value not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M470" s="12" t="inlineStr">
@@ -50930,13 +50929,13 @@
       <c r="L471" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-450: "Enter a whole number of bookings (0 or more)"
-MSG-NB-451: "Enter an amount of 0 or more"
-MSG-NB-452: "Enter the period"
-MSG-NB-453: "Enter the unit code or the officer username"
-MSG-NB-456: "The period end must not be before the start"
-MSG-NB-457: "Targets cannot be negative" (TARGET_NEGATIVE)
-MSG-NB-458: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
+MSG-NB-452: "Enter a whole number of bookings (0 or more)"
+MSG-NB-453: "Enter an amount of 0 or more"
+MSG-NB-454: "Enter the period"
+MSG-NB-455: "Enter the unit code or the officer username"
+MSG-NB-458: "The period end must not be before the start"
+MSG-NB-459: "Targets cannot be negative" (TARGET_NEGATIVE)
+MSG-NB-460: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
         </is>
       </c>
       <c r="M471" s="12" t="inlineStr">
@@ -51011,11 +51010,11 @@
       <c r="L472" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-459: "Enter a name"
-MSG-NB-460: "The saved parameter variant is deleted."
-MSG-NB-463: "Report variant not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-464: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
-MSG-NB-465: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
+MSG-NB-461: "Enter a name"
+MSG-NB-462: "The saved parameter variant is deleted."
+MSG-NB-465: "Report variant not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-466: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
+MSG-NB-467: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
         </is>
       </c>
       <c r="M472" s="12" t="inlineStr">
@@ -51090,13 +51089,13 @@
       <c r="L473" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-469: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
-MSG-NB-470: "Document template not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-471: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-472: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
-MSG-NB-473: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
-MSG-NB-474: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
-MSG-NB-475: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
+MSG-NB-471: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
+MSG-NB-472: "Document template not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-473: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-474: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
+MSG-NB-475: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
+MSG-NB-476: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
+MSG-NB-477: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
         </is>
       </c>
       <c r="M473" s="12" t="inlineStr">
@@ -51171,10 +51170,10 @@
       <c r="L474" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-477: "Between 0 and 50 years"
-MSG-NB-478: "Between 1 and 50 years"
-MSG-NB-479: "Enter a description"
-MSG-NB-480: "Enter at least one status"</t>
+MSG-NB-479: "Between 0 and 50 years"
+MSG-NB-480: "Between 1 and 50 years"
+MSG-NB-481: "Enter a description"
+MSG-NB-482: "Enter at least one status"</t>
         </is>
       </c>
       <c r="M474" s="12" t="inlineStr">
@@ -51237,13 +51236,13 @@
       <c r="L475" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-485: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-NB-486: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-NB-487: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-NB-488: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-NB-489: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-NB-490: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-NB-491: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-NB-487: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-NB-488: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-NB-489: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-NB-490: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-NB-491: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-NB-492: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-NB-493: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M475" s="12" t="inlineStr">
@@ -51318,8 +51317,8 @@
       <c r="L476" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-499: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-NB-500: "&lt;Column&gt; is mandatory"</t>
+MSG-NB-501: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-NB-502: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M476" s="12" t="inlineStr">
@@ -51394,7 +51393,7 @@
       <c r="L477" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-501: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
+MSG-NB-503: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
         </is>
       </c>
       <c r="M477" s="12" t="inlineStr">
@@ -51469,8 +51468,8 @@
       <c r="L478" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-502: "Account &lt;arn&gt; belongs to another company"
-MSG-NB-505: "The booking date &lt;date&gt; is in the future"</t>
+MSG-NB-504: "Account &lt;arn&gt; belongs to another company"
+MSG-NB-507: "The booking date &lt;date&gt; is in the future"</t>
         </is>
       </c>
       <c r="M478" s="12" t="inlineStr">
@@ -51545,9 +51544,9 @@
       <c r="L479" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-503: "Client Type must be INDIVIDUAL or CORPORATE"
-MSG-NB-504: "Client code &lt;code&gt; does not exist"
-MSG-NB-506: "The row matches several clients: &lt;details&gt;"</t>
+MSG-NB-505: "Client Type must be INDIVIDUAL or CORPORATE"
+MSG-NB-506: "Client code &lt;code&gt; does not exist"
+MSG-NB-508: "The row matches several clients: &lt;details&gt;"</t>
         </is>
       </c>
       <c r="M479" s="12" t="inlineStr">
@@ -51610,25 +51609,25 @@
       <c r="L480" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-507: "Legacy policy &lt;legacy ref&gt; is already imported" (ACCOUNT_LEGACY_IMPORTED)
-MSG-NB-508: "Account &lt;arn&gt; was not imported from legacy" (ACCOUNT_NOT_MIGRATED)
-MSG-NB-509: "Client &lt;code&gt; was not migrated" (CLIENT_NOT_MIGRATED)
-MSG-NB-510: "A migrated client needs its source system and legacy code" (CLIENT_ORIGIN_REQUIRED)
-MSG-NB-511: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-512: "Account not found: &lt;account id&gt;" (NOT_FOUND)
-MSG-NB-513: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-514: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-515: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
-MSG-NB-516: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-517: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
-MSG-NB-518: "Client not found: &lt;client id&gt;" (NOT_FOUND)
-MSG-NB-519: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
-MSG-NB-520: "Notification not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-521: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-522: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-523: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
-MSG-NB-524: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-525: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
+MSG-NB-509: "Legacy policy &lt;legacy ref&gt; is already imported" (ACCOUNT_LEGACY_IMPORTED)
+MSG-NB-510: "Account &lt;arn&gt; was not imported from legacy" (ACCOUNT_NOT_MIGRATED)
+MSG-NB-511: "Client &lt;code&gt; was not migrated" (CLIENT_NOT_MIGRATED)
+MSG-NB-512: "A migrated client needs its source system and legacy code" (CLIENT_ORIGIN_REQUIRED)
+MSG-NB-513: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-514: "Account not found: &lt;account id&gt;" (NOT_FOUND)
+MSG-NB-515: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-516: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-517: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
+MSG-NB-518: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-519: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
+MSG-NB-520: "Client not found: &lt;client id&gt;" (NOT_FOUND)
+MSG-NB-521: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
+MSG-NB-522: "Notification not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-523: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-524: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-525: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
+MSG-NB-526: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-527: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M480" s="12" t="inlineStr">
@@ -60274,11 +60273,11 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>TC-NB-080.3-01, TC-NB-080.3-02, TC-NB-081.1-01, TC-NB-081.2-02, TC-NB-SCR-20</t>
+          <t>TC-NB-080.3-01, TC-NB-080.3-02, TC-NB-081.1-01, TC-NB-SCR-20</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -42603,8 +42603,8 @@
       </c>
       <c r="L366" s="12" t="inlineStr">
         <is>
-          <t>The account locks at the third failure and the correct password is refused.
-Message "Account is locked. Contact your administrator." (AUTHENTICATION_FAILED).</t>
+          <t>The account locks at the third failure and the correct password is refused with the same message as a wrong password.
+Message "Invalid user name or password" (AUTHENTICATION_FAILED).</t>
         </is>
       </c>
       <c r="M366" s="12" t="inlineStr">
@@ -49099,22 +49099,22 @@
       <c r="L449" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-174: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-175: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
-MSG-NB-176: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
-MSG-NB-177: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
-MSG-NB-178: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
-MSG-NB-179: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
-MSG-NB-180: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
-MSG-NB-181: "Select the new insurer" (INSURER_REQUIRED)
-MSG-NB-182: "Select an insurer other than the current one" (INSURER_UNCHANGED)
-MSG-NB-183: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-184: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-185: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
-MSG-NB-186: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
-MSG-NB-187: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
-MSG-NB-188: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
-MSG-NB-189: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
+MSG-NB-173: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-174: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
+MSG-NB-175: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
+MSG-NB-176: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
+MSG-NB-177: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
+MSG-NB-178: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
+MSG-NB-179: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
+MSG-NB-180: "Select the new insurer" (INSURER_REQUIRED)
+MSG-NB-181: "Select an insurer other than the current one" (INSURER_UNCHANGED)
+MSG-NB-182: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-183: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-184: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
+MSG-NB-185: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
+MSG-NB-186: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
+MSG-NB-187: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
+MSG-NB-188: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
         </is>
       </c>
       <c r="M449" s="12" t="inlineStr">
@@ -49189,25 +49189,25 @@
       <c r="L450" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-191: "Choose the client and product to save the draft."
-MSG-NB-192: "The draft is not saved yet: click Save Draft to check it before submission."
-MSG-NB-193: "The draft was not saved: correct what the message above describes, then save the draft again."
-MSG-NB-194: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
-MSG-NB-195: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
-MSG-NB-196: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
-MSG-NB-197: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
-MSG-NB-198: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
-MSG-NB-199: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
-MSG-NB-200: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
-MSG-NB-201: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-202: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
-MSG-NB-203: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-204: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
-MSG-NB-205: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
-MSG-NB-206: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
-MSG-NB-207: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
-MSG-NB-208: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-209: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-190: "Choose the client and product to save the draft."
+MSG-NB-191: "The draft is not saved yet: click Save Draft to check it before submission."
+MSG-NB-192: "The draft was not saved: correct what the message above describes, then save the draft again."
+MSG-NB-193: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
+MSG-NB-194: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
+MSG-NB-195: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
+MSG-NB-196: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
+MSG-NB-197: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
+MSG-NB-198: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
+MSG-NB-199: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
+MSG-NB-200: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-201: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
+MSG-NB-202: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-203: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
+MSG-NB-204: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
+MSG-NB-205: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
+MSG-NB-206: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
+MSG-NB-207: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-208: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M450" s="12" t="inlineStr">
@@ -49282,9 +49282,9 @@
       <c r="L451" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-214: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-215: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
-MSG-NB-216: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
+MSG-NB-213: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-214: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
+MSG-NB-215: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
         </is>
       </c>
       <c r="M451" s="12" t="inlineStr">
@@ -49359,17 +49359,17 @@
       <c r="L452" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-219: "Record Hold Cover Confirmation"
-MSG-NB-220: "Record Hold Cover Decline"
-MSG-NB-221: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
-MSG-NB-222: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
-MSG-NB-223: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
-MSG-NB-224: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
-MSG-NB-225: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
-MSG-NB-226: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
-MSG-NB-227: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
-MSG-NB-228: "Choose the insurer on the account first" (INSURER_NOT_SET)
-MSG-NB-229: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
+MSG-NB-218: "Record Hold Cover Confirmation"
+MSG-NB-219: "Record Hold Cover Decline"
+MSG-NB-220: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
+MSG-NB-221: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
+MSG-NB-222: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
+MSG-NB-223: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
+MSG-NB-224: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
+MSG-NB-225: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
+MSG-NB-226: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
+MSG-NB-227: "Choose the insurer on the account first" (INSURER_NOT_SET)
+MSG-NB-228: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
         </is>
       </c>
       <c r="M452" s="12" t="inlineStr">
@@ -49444,20 +49444,20 @@
       <c r="L453" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-238: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-239: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
-MSG-NB-240: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
-MSG-NB-241: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
-MSG-NB-242: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-243: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
-MSG-NB-244: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
-MSG-NB-245: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
-MSG-NB-246: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
-MSG-NB-247: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
-MSG-NB-248: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
-MSG-NB-249: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
-MSG-NB-250: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
-MSG-NB-251: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
+MSG-NB-237: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-238: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
+MSG-NB-239: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
+MSG-NB-240: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
+MSG-NB-241: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-242: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
+MSG-NB-243: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
+MSG-NB-244: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
+MSG-NB-245: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
+MSG-NB-246: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
+MSG-NB-247: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
+MSG-NB-248: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
+MSG-NB-249: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
+MSG-NB-250: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
         </is>
       </c>
       <c r="M453" s="12" t="inlineStr">
@@ -49532,10 +49532,10 @@
       <c r="L454" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-255: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
-MSG-NB-256: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
-MSG-NB-257: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
-MSG-NB-258: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-254: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
+MSG-NB-255: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
+MSG-NB-256: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
+MSG-NB-257: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M454" s="12" t="inlineStr">
@@ -49610,19 +49610,19 @@
       <c r="L455" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-260: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-261: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
-MSG-NB-262: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
-MSG-NB-263: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
-MSG-NB-264: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-265: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
-MSG-NB-266: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
-MSG-NB-267: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
-MSG-NB-268: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
-MSG-NB-269: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-270: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
-MSG-NB-272: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
+MSG-NB-259: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-260: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
+MSG-NB-261: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
+MSG-NB-262: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
+MSG-NB-263: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-264: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
+MSG-NB-265: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
+MSG-NB-266: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
+MSG-NB-267: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
+MSG-NB-268: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-269: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-270: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
+MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
         </is>
       </c>
       <c r="M455" s="12" t="inlineStr">
@@ -49697,14 +49697,14 @@
       <c r="L456" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-275: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
-MSG-NB-276: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
-MSG-NB-277: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
-MSG-NB-278: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
-MSG-NB-279: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
-MSG-NB-280: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-281: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
-MSG-NB-282: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-274: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
+MSG-NB-275: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
+MSG-NB-276: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
+MSG-NB-277: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
+MSG-NB-278: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
+MSG-NB-279: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-280: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
+MSG-NB-281: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M456" s="12" t="inlineStr">
@@ -49779,10 +49779,10 @@
       <c r="L457" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-284: "Enter one policy number per policy year."
-MSG-NB-287: "The policy numbers must be different."
-MSG-NB-288: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
-MSG-NB-289: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
+MSG-NB-283: "Enter one policy number per policy year."
+MSG-NB-286: "The policy numbers must be different."
+MSG-NB-287: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
+MSG-NB-288: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
         </is>
       </c>
       <c r="M457" s="12" t="inlineStr">
@@ -49857,10 +49857,10 @@
       <c r="L458" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-292: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
-MSG-NB-293: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
-MSG-NB-294: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
-MSG-NB-295: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-291: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
+MSG-NB-292: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
+MSG-NB-293: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
+MSG-NB-294: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M458" s="12" t="inlineStr">
@@ -49935,8 +49935,8 @@
       <c r="L459" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-298: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
-MSG-NB-299: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
+MSG-NB-297: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
+MSG-NB-298: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
         </is>
       </c>
       <c r="M459" s="12" t="inlineStr">
@@ -50011,22 +50011,22 @@
       <c r="L460" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-302: "A negative endorsement reduces the sum insured (enter a minus)"
-MSG-NB-303: "A positive endorsement increases the sum insured"
-MSG-NB-304: "Choose the reason"
-MSG-NB-305: "Describe the cancellation"
-MSG-NB-306: "Describe the change"
-MSG-NB-307: "Enter a booking date that is not in the future"
-MSG-NB-308: "Enter a rate of zero or more, or leave it blank"
-MSG-NB-309: "Enter the cancellation date"
-MSG-NB-310: "Enter the change of the sum insured"
-MSG-NB-311: "Enter the effective date"
-MSG-NB-313: "The booking date cannot be in the future"
-MSG-NB-314: "No queued account to book" (BATCH_EMPTY)
-MSG-NB-315: "Select at least one account to book" (BATCH_EMPTY)
-MSG-NB-316: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-317: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-318: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
+MSG-NB-301: "A negative endorsement reduces the sum insured (enter a minus)"
+MSG-NB-302: "A positive endorsement increases the sum insured"
+MSG-NB-303: "Choose the reason"
+MSG-NB-304: "Describe the cancellation"
+MSG-NB-305: "Describe the change"
+MSG-NB-306: "Enter a booking date that is not in the future"
+MSG-NB-307: "Enter a rate of zero or more, or leave it blank"
+MSG-NB-308: "Enter the cancellation date"
+MSG-NB-309: "Enter the change of the sum insured"
+MSG-NB-310: "Enter the effective date"
+MSG-NB-312: "The booking date cannot be in the future"
+MSG-NB-313: "No queued account to book" (BATCH_EMPTY)
+MSG-NB-314: "Select at least one account to book" (BATCH_EMPTY)
+MSG-NB-315: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-316: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-317: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
         </is>
       </c>
       <c r="M460" s="12" t="inlineStr">
@@ -50101,25 +50101,25 @@
       <c r="L461" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-320: "Enter a booking date that is not in the future"
-MSG-NB-321: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
-MSG-NB-322: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
-MSG-NB-323: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
-MSG-NB-324: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
-MSG-NB-325: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
-MSG-NB-326: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
-MSG-NB-327: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
-MSG-NB-328: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-329: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
-MSG-NB-330: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
-MSG-NB-331: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
-MSG-NB-332: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
-MSG-NB-333: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
-MSG-NB-334: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
-MSG-NB-335: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
-MSG-NB-336: "No invoice" (INVOICE_NOT_FOUND)
-MSG-NB-337: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
-MSG-NB-338: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
+MSG-NB-319: "Enter a booking date that is not in the future"
+MSG-NB-320: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
+MSG-NB-321: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
+MSG-NB-322: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
+MSG-NB-323: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
+MSG-NB-324: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
+MSG-NB-325: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
+MSG-NB-326: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
+MSG-NB-327: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-328: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
+MSG-NB-329: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
+MSG-NB-330: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
+MSG-NB-331: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
+MSG-NB-332: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
+MSG-NB-333: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
+MSG-NB-334: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
+MSG-NB-335: "No invoice" (INVOICE_NOT_FOUND)
+MSG-NB-336: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
+MSG-NB-337: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
         </is>
       </c>
       <c r="M461" s="12" t="inlineStr">
@@ -50194,15 +50194,15 @@
       <c r="L462" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-344: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
-MSG-NB-345: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
-MSG-NB-346: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
-MSG-NB-347: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
-MSG-NB-348: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
-MSG-NB-349: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-350: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-351: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
-MSG-NB-352: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-NB-343: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
+MSG-NB-344: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
+MSG-NB-345: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
+MSG-NB-346: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
+MSG-NB-347: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
+MSG-NB-348: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-349: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-350: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
+MSG-NB-351: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M462" s="12" t="inlineStr">
@@ -50277,14 +50277,14 @@
       <c r="L463" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-354: "Give the reason of the credit"
-MSG-NB-356: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
-MSG-NB-357: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
-MSG-NB-358: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-359: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
-MSG-NB-360: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-361: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
-MSG-NB-362: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
+MSG-NB-353: "Give the reason of the credit"
+MSG-NB-355: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
+MSG-NB-356: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
+MSG-NB-357: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-358: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
+MSG-NB-359: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-360: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
+MSG-NB-361: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
         </is>
       </c>
       <c r="M463" s="12" t="inlineStr">
@@ -50359,12 +50359,12 @@
       <c r="L464" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-365: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-366: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
-MSG-NB-367: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
-MSG-NB-368: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-369: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-370: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-364: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-365: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
+MSG-NB-366: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
+MSG-NB-367: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-368: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-369: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M464" s="12" t="inlineStr">
@@ -50439,16 +50439,17 @@
       <c r="L465" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-375: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
-MSG-NB-376: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-377: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-378: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
-MSG-NB-379: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
-MSG-NB-380: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
-MSG-NB-381: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
-MSG-NB-382: "The file has no data rows" (BULK_FILE_EMPTY)
-MSG-NB-383: "The file has no header row" (BULK_FILE_EMPTY)
-MSG-NB-384: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-374: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
+MSG-NB-375: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-376: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-377: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
+MSG-NB-378: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
+MSG-NB-379: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
+MSG-NB-380: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
+MSG-NB-381: "The file has no data rows" (BULK_FILE_EMPTY)
+MSG-NB-382: "The file has no header row" (BULK_FILE_EMPTY)
+MSG-NB-383: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-384: "The spreadsheet has more than 100000 rows" (BULK_FILE_TOO_LARGE)
 MSG-NB-385: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
 MSG-NB-386: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
 MSG-NB-387: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
@@ -51621,13 +51622,14 @@
 MSG-NB-518: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
 MSG-NB-519: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
 MSG-NB-520: "Client not found: &lt;client id&gt;" (NOT_FOUND)
-MSG-NB-521: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
-MSG-NB-522: "Notification not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-523: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-524: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-525: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
-MSG-NB-526: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-527: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
+MSG-NB-521: "Company not found: &lt;company id&gt;" (NOT_FOUND)
+MSG-NB-522: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
+MSG-NB-523: "Notification not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-524: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-525: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-526: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
+MSG-NB-527: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-528: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M480" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -44785,7 +44785,7 @@
       <c r="L395" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-05 Quotations of the FRS.
-Fields in this order: 1 My Drafts / For Review / Sent / Accepted / Expiring (Toggle buttons, mandatory -); 2 Drafts / For Review / Sent to Client / Accepted / Not Proceeded (Tab, mandatory -); 3 Search Quotation No., ARN or client (Text, mandatory N); 4 Only My Drafts / Expiring within 7 days (Check box, mandatory N); 5 Select (Check box, mandatory N); 6 Quotation No. (Column, mandatory -); 7 ARN (Column, mandatory -); 8 Client (Column, mandatory -); 9 Product (Column, mandatory -); 10 Insurer (Column, mandatory -); 11 Gross Premium (Column, mandatory -); 12 Valid Until (Column, mandatory -); 13 Status (Column, mandatory -).
+Fields in this order: 1 My Drafts / For Review / Sent / Accepted / Expiring (Toggle buttons, mandatory -); 2 Drafts / For Review / Sent to Client / Accepted / Not Proceeded (Tab, mandatory -); 3 Search Quotation No., ARN or client (Text, mandatory N); 4 Only My Drafts / Expiring within 7 days (Check box, mandatory N); 5 Select (Check box, mandatory N); 6 Quotation No. (Column, mandatory -); 7 ARN (Column, mandatory -); 8 Client (Column, mandatory -); 9 Product / Insurer (Column, mandatory -); 10 Gross Premium (Column, mandatory -); 11 Valid Until (Column, mandatory -); 12 Status (Column, mandatory -).
 Actions: Request Inbox; Bulk Upload; New Quotation; Send via Email (n); Open a row.</t>
         </is>
       </c>
@@ -45021,7 +45021,7 @@
       <c r="L398" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-08 Quotation Requests of the FRS.
-Fields in this order: 1 To Quote / Quoted / Closed (Tab, mandatory -); 2 Search Request No. (Text, mandatory N); 3 Request No. (Column, mandatory -); 4 Channel (Column, mandatory -); 5 Client / Prospect (Column, mandatory -); 6 Product (Column, mandatory -); 7 Requested Cover (Column, mandatory -); 8 Status (Column, mandatory -); 9 Channel (Drop-down, mandatory Y); 10 Source reference (Text, mandatory N); 11 Existing client (Look-up, mandatory Cond.: the client or the prospect name); 12 Prospect name (Text, mandatory Cond.: when no client is chosen); 13 Prospect e-mail (Text, mandatory N); 14 Prospect mobile (Text, mandatory N); 15 Requested product (Drop-down, mandatory N); 16 Market segment (Drop-down, mandatory N); 17 Requested cover (Text area, mandatory Y); 18 Request e-mail (File, mandatory N); 19 Reason for Closing (Text area, mandatory Y).
+Fields in this order: 1 To Quote / Quoted / Closed (Tab, mandatory -); 2 Search Request No. (Text, mandatory N); 3 Request No. (Column, mandatory -); 4 Channel (Column, mandatory -); 5 Client / Prospect (Column, mandatory -); 6 Product (Column, mandatory -); 7 Requested Cover (Column, mandatory -); 8 Status (Column, mandatory -); 9 Actions (Row action menu, mandatory -); 10 Channel (Drop-down, mandatory Y); 11 Source reference (Text, mandatory N); 12 Existing client (Look-up, mandatory Cond.: the client or the prospect name); 13 Prospect name (Text, mandatory Cond.: when no client is chosen); 14 Prospect e-mail (Text, mandatory N); 15 Prospect mobile (Text, mandatory N); 16 Requested product (Drop-down, mandatory N); 17 Market segment (Drop-down, mandatory N); 18 Requested cover (Text area, mandatory Y); 19 Request e-mail (File, mandatory N); 20 Reason for Closing (Text area, mandatory Y).
 Actions: Capture Request; Create Prospect; Create Quotation; Close; Open Quotation.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -45099,7 +45099,7 @@
       <c r="L399" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-09 Proposal Requests of the FRS.
-Fields in this order: 1 Drafts / For Approval / With TSU / With Client / Accepted / Not Proceeded (Tab, mandatory -); 2 Search PRF No., ARN or client (Text, mandatory N); 3 Only My PRFs (Check box, mandatory N); 4 PRF No. (Column, mandatory -); 5 ARN (Column, mandatory -); 6 Client (Column, mandatory -); 7 Product (Column, mandatory -); 8 Sum Insured (Column, mandatory -); 9 Slips (Column, mandatory -); 10 Chosen Insurer (Column, mandatory -); 11 Stage (Column, mandatory -).
+Fields in this order: 1 Drafts / For Approval / With TSU / With Client / Accepted / Not Proceeded (Tab, mandatory -); 2 Search PRF No., ARN or client (Text, mandatory N); 3 Only My PRFs (Check box, mandatory N); 4 PRF No. (Column, mandatory -); 5 ARN (Column, mandatory -); 6 Client (Column, mandatory -); 7 Product (Column, mandatory -); 8 Sum Insured (Column, mandatory -); 9 Slips / Chosen Insurer (Column, mandatory -); 10 Stage (Column, mandatory -).
 Actions: TSU Workbench; New PRF; Open a row.</t>
         </is>
       </c>
@@ -45334,7 +45334,7 @@
       <c r="L402" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-12 TSU Workbench of the FRS.
-Fields in this order: 1 Received by TSU, Quotation slip in preparation, Quotation slip for approval, Awaiting insurer terms, Insurer terms received, Proposal slip for approval (Tile, mandatory -); 2 Reference, Description, Stage, From, In Stage, Due, Assignee (Column, mandatory -).
+Fields in this order: 1 Received by TSU, Quotation slip in preparation, Quotation slip for approval, Awaiting insurer terms, Insurer terms received, Proposal slip for approval (Tile, mandatory -); 2 Reference, Description, Stage, From, In Stage, Due, Assignee, Actions (Column, mandatory -).
 Actions: Claim; Assign; Open a row.</t>
         </is>
       </c>
@@ -45411,7 +45411,7 @@
       <c r="L403" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-13 Accounts of the FRS.
-Fields in this order: 1 All / My Drafts / Returned to Me / Awaiting Payment / FFY / Direct Payment (Tab, mandatory -); 2 Search ARN, client code or name (Text, mandatory N); 3 PN Number (Text, mandatory N); 4 Plate, Conduction, Engine or Chassis (Text, mandatory N); 5 Location of Risk (Text, mandatory N); 6 Product (Text, mandatory N); 7 Insurer (Text, mandatory N); 8 Status (Drop-down, mandatory N); 9 Business Type (Drop-down, mandatory N); 10 Starts On or After / Starts On or Before (Date, mandatory N); 11 Include Voided (Check box, mandatory N); 12 ARN (Column, mandatory -); 13 Client (Column, mandatory -); 14 Product / Insurer / Period / Gross Premium (Column, mandatory -); 15 Status (Column, mandatory -); 16 Flags (Column, mandatory -); 17 Officer (Column, mandatory -).
+Fields in this order: 1 All / My Drafts / Returned to Me / Awaiting Payment / FFY / Direct Payment (Tab, mandatory -); 2 Search ARN, client code or name (Text, mandatory N); 3 PN Number (Text, mandatory N); 4 Plate, Conduction, Engine or Chassis (Text, mandatory N); 5 Location of Risk (Text, mandatory N); 6 Product (Text, mandatory N); 7 Insurer (Text, mandatory N); 8 Status (Drop-down, mandatory N); 9 Business Type (Drop-down, mandatory N); 10 Starts On or After / Starts On or Before (Date, mandatory N); 11 Include Voided (Check box, mandatory N); 12 ARN (Column, mandatory -); 13 Client (Column, mandatory -); 14 Product / Insurer (Column, mandatory -); 15 Period / Gross Premium (Column, mandatory -); 16 Status / Flags (Column, mandatory -); 17 Officer (Column, mandatory -).
 Actions: Bulk Upload; New Account; Filters / Apply Filters / Clear Filters; Open a row.</t>
         </is>
       </c>
@@ -45881,7 +45881,7 @@
         <is>
           <t>The screen matches SCR-NB-19 Account Placement of the FRS.
 Fields in this order: 1 Product, Insurer, Gross premium, Payment gate, Placement slip, Hold cover (Display, mandatory -); 2 Rule, Gate, Segment / line (Display, mandatory -); 3 Evidence (Table, mandatory -); 4 Confirmation channel (Drop-down, mandatory Y); 5 Remarks (Text area, mandatory N); 6 Placement slips (Table, mandatory -); 7 Hold covers (Table, mandatory -); 8 Hold cover starts on / Confirmed on (Date, mandatory N); 9 Insurer reference (Text, mandatory Y to record a confirmation); 10 Expires on (Date, mandatory N); 11 Insurer returns (Table, mandatory -).
-Actions: Open Account; Record Client Confirmation / Release Direct Payment; Generate Placement Slip; Send / Resend, Regenerate, PDF, Excel (slip); Request Hold Cover; Record Confirmation; Record Decline; Record Insurer Return; Resubmit for Placement; Return To Marketing; Cancel Placement / Reactivate.
+Actions: Open Account; Record Client Confirmation / Release Direct Payment; Generate Placement Slip; Send / Resend, Regenerate, Download PDF, Download Excel (slip); Request Hold Cover; Record Confirmation; Record Decline; Record Insurer Return; Resubmit for Placement; Return To Marketing; Cancel Placement / Reactivate.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -45959,8 +45959,8 @@
       <c r="L410" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-20 Placement Slips of the FRS.
-Fields in this order: 1 All Slips / To Send / Sent / Superseded (Tab, mandatory -); 2 Slip (Column, mandatory -); 3 Status (Column, mandatory -); 4 Insurer / Branch (Column, mandatory -); 5 Accounts (Column, mandatory -); 6 Sent (Column, mandatory -); 7 To, Cc, Subject, Message (Text, mandatory To, Subject and Message Y); 8 Password-protect the attachments (Check box, mandatory N).
-Actions: PDF / Excel; Send / Resend; Regenerate.
+Fields in this order: 1 All Slips / To Send / Sent / Superseded (Tab, mandatory -); 2 Slip (Column, mandatory -); 3 Status (Column, mandatory -); 4 Insurer / Branch (Column, mandatory -); 5 Accounts (Column, mandatory -); 6 Sent (Column, mandatory -); 7 Actions (Row action menu, mandatory -); 8 To, Cc, Subject, Message (Text, mandatory To, Subject and Message Y); 9 Password-protect the attachments (Check box, mandatory N).
+Actions: Download PDF / Download Excel; Send / Resend; Regenerate.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -46038,8 +46038,8 @@
       <c r="L411" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-21 CLPC Billing of the FRS.
-Fields in this order: 1 Billing Batches / Payment Reports (Tab, mandatory -); 2 Reference, Borrower, PN No., Loan Application No., Premium (Column, mandatory -); 3 Select (Check box, mandatory N); 4 Batch, Billing Date, Status, Accounts, Total Premium (Column, mandatory -); 5 Report, Kind, File, Status, Matched / Unpaid / Unmatched / Ambiguous, Uploaded (Column, mandatory -); 6 Report (Drop-down, mandatory Y); 7 Billing batch (Drop-down, mandatory Y for a CLPC report); 8 File (File, mandatory Y).
-Actions: Bill Selected (n) / Bill All; Excel / ODS; Upload Payment Report / Upload Report.
+Fields in this order: 1 Billing Batches / Payment Reports (Tab, mandatory -); 2 Reference, Borrower, PN No., Loan Application No., Premium (Column, mandatory -); 3 Select (Check box, mandatory N); 4 Batch, Billing Date, Status, Accounts, Total Premium, Actions (Column, mandatory -); 5 Report, Kind, File, Status, Matched / Unpaid / Unmatched / Ambiguous, Uploaded (Column, mandatory -); 6 Report (Drop-down, mandatory Y); 7 Billing batch (Drop-down, mandatory Y for a CLPC report); 8 File (File, mandatory Y).
+Actions: Bill Selected (n) / Bill All; Download Excel / Download ODS; Upload Payment Report / Upload Report.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -46117,7 +46117,7 @@
       <c r="L412" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-22 Payment Report of the FRS.
-Fields in this order: 1 Matched / Unpaid / Unmatched / Ambiguous (Tile, mandatory -); 2 Row, Reported Reference, Paid, Amount, Payment Date, Account, Detail (Column, mandatory -); 3 Account (ARN) (Drop-down or Text, mandatory Y).
+Fields in this order: 1 Matched / Unpaid / Unmatched / Ambiguous (Tile, mandatory -); 2 Row, Reported Reference, Paid, Amount, Payment Date, Account, Detail, Actions (Column, mandatory -); 3 Account (ARN) (Drop-down or Text, mandatory Y).
 Actions: Match; Confirm Matches; Discard.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -46195,8 +46195,8 @@
       <c r="L413" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-23 Issuance Workbench of the FRS.
-Fields in this order: 1 Placed – Awaiting Policy / Policy Received – Review Extraction / Ready to Dispatch / IA to Generate (Tile and tab, mandatory -); 2 Search Reference No. (Text, mandatory N); 3 Select (Check box, mandatory N); 4 Name / Client Code (Column, mandatory -); 5 ARN (Column, mandatory -); 6 Status (Column, mandatory -); 7 Product Line (Column, mandatory -); 8 Policy No. (Column, mandatory -); 9 E-policy / Mortgagee / Upload E-policy (Column, mandatory -).
-Actions: Upload E-policies; Upload E-policy (row); Generate Insurance Advice; Send E-policies.</t>
+Fields in this order: 1 Placed – Awaiting Policy / Policy Received – Review Extraction / Ready to Dispatch / IA to Generate (Tile and tab, mandatory -); 2 Search Reference No. (Text, mandatory N); 3 Select (Check box, mandatory N); 4 Name / Client Code (Column, mandatory -); 5 ARN (Column, mandatory -); 6 Status (Column, mandatory -); 7 Product Line (Column, mandatory -); 8 Policy No. (Column, mandatory -); 9 E-policy / Mortgagee / Actions (Column, mandatory -).
+Actions: Upload E-policies; Upload E-policy (row action menu); Generate Insurance Advice; Send E-policies.</t>
         </is>
       </c>
       <c r="M413" s="12" t="inlineStr">
@@ -46431,8 +46431,8 @@
       <c r="L416" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-26 Insurance Advice of the FRS.
-Fields in this order: 1 Search IA No., ARN or client (Text, mandatory N); 2 Select (Check box, mandatory N); 3 IA No. (Column, mandatory -); 4 Insured / ARN (Column, mandatory -); 5 Mortgagee (Column, mandatory -); 6 Policy No. (Column, mandatory -); 7 Generated (Column, mandatory -); 8 Status / Last Sent (Column, mandatory -); 9 Accounts (ARN) (Text area, mandatory Y); 10 To (Text, mandatory Y); 11 Cc, Password hint (Text, mandatory N).
-Actions: Generate Insurance Advice; Send Selected; PDF.
+Fields in this order: 1 Search IA No., ARN or client (Text, mandatory N); 2 Select (Check box, mandatory N); 3 IA No. (Column, mandatory -); 4 Insured / ARN (Column, mandatory -); 5 Mortgagee (Column, mandatory -); 6 Policy No. (Column, mandatory -); 7 Generated (Column, mandatory -); 8 Status / Last Sent (Column, mandatory -); 9 Actions (Row action menu, mandatory -); 10 Accounts (ARN) (Text area, mandatory Y); 11 To (Text, mandatory Y); 12 Cc, Password hint (Text, mandatory N).
+Actions: Generate Insurance Advice; Send Selected; Download PDF.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -46510,8 +46510,8 @@
       <c r="L417" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-27 E-policy Dispatch of the FRS.
-Fields in this order: 1 Ready to Dispatch / Dispatch Report (Tab, mandatory -); 2 Name / Client Code, ARN, Policy No., E-policy (Column, mandatory -); 3 To, Cc, Subject, Message (Text, mandatory To, Subject and Message Y); 4 Password hint (Text, mandatory N); 5 Queued, Reference No., To, Subject, Outcome, Delivered (Column, mandatory -).
-Actions: Send (row); Send Selected.
+Fields in this order: 1 Ready to Dispatch / Dispatch Report (Tab, mandatory -); 2 Name / Client Code, ARN, Policy No., E-policy, Actions (Column, mandatory -); 3 To, Cc, Subject, Message (Text, mandatory To, Subject and Message Y); 4 Password hint (Text, mandatory N); 5 Queued, Reference No., To, Subject, Outcome, Delivered (Column, mandatory -).
+Actions: Send (row action menu); Send Selected.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -46590,7 +46590,7 @@
         <is>
           <t>The screen matches SCR-NB-28 Booking Workbench of the FRS.
 Fields in this order: 1 Ready to Book / Queued for Batch / Booked Today / Failed (Tile, mandatory -); 2 Ready to Book / Queued for Batch / Booked Account / Failed (Tab, mandatory -); 3 Accounts sent from placement (Banner, mandatory -); 4 Search Reference No. (Text, mandatory N); 5 Product line (Drop-down, mandatory N); 6 Select (Check box, mandatory N); 7 Name / Client Code, ARN, Invoice No., Status, Product Line, Department, Booking Date (Column, mandatory -); 8 Booking date (Date, mandatory Y); 9 Booking date (Date, mandatory N); 10 Cost center (Text, mandatory N).
-Actions: Batch Runs; Upload Bookings; Add All to Batch; Add to Batch; Book Now; Confirm Batch; Cancel Batch; Edit / Remove (row); Open a row.
+Actions: Batch Runs; Upload Bookings; Add All to Batch; Add to Batch; Book Now; Confirm Batch; Cancel Batch; Edit / Remove (row action menu); Open a row.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -46905,7 +46905,7 @@
       <c r="L422" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-32 Service Invoices of the FRS.
-Fields in this order: 1 All / Service Invoices / Credits (Tab, mandatory -); 2 Search Service Invoice No., invoice, ARN or recipient (Text, mandatory N); 3 Service Invoice No., Issue Date, Kind, Type, Booked Invoice, ARN, Recipient, Net, Dispatch (Column, mandatory -); 4 Service invoice, Invoice, ARN (Reference, mandatory -); 5 Recipient, Billing e-mail, Issue date, Template, Owner, Credit of (Display, mandatory -); 6 Lines (Display, mandatory -); 7 E-mail dispatch problem (Banner, mandatory -); 8 Commission to credit / VAT to credit (Amount, mandatory N); 9 Reason (Text, mandatory Y).
+Fields in this order: 1 All / Service Invoices / Credits (Tab, mandatory -); 2 Search Service Invoice No., invoice, ARN or recipient (Text, mandatory N); 3 Service Invoice No., Kind / Type, Recipient, Invoice No., Issue Date, Net, E-mail (Column, mandatory -); 4 Service invoice, Invoice, ARN (Reference, mandatory -); 5 Recipient, Billing e-mail, Issue date, Template, Owner, Credit of (Display, mandatory -); 6 Lines (Display, mandatory -); 7 E-mail dispatch problem (Banner, mandatory -); 8 Commission to credit / VAT to credit (Amount, mandatory N); 9 Reason (Text, mandatory Y).
 Actions: Open a row; Download PDF; Send via Email; Credit.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -47377,7 +47377,7 @@
       <c r="L428" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-38 My Work of the FRS.
-Fields in this order: 1 Assigned to me / Open in my queues / Overdue / Queues I work (Figure, mandatory -); 2 One tile per stage of each workflow the user works (Tile, mandatory -); 3 Assigned to me / Team queue / All my queues (Tab, mandatory -); 4 Overdue only (Check box, mandatory N); 5 Reference or name (Text, mandatory N); 6 Reference, Description, Stage, From, In Stage, Due, Assignee (Column, mandatory -); 7 Assignee (Drop-down, mandatory N).
+Fields in this order: 1 Assigned to me / Open in my queues / Overdue / Queues I work (Figure, mandatory -); 2 One tile per stage of each workflow the user works (Tile, mandatory -); 3 Assigned to me / Team queue / All my queues (Tab, mandatory -); 4 Overdue only (Check box, mandatory N); 5 Reference or name (Text, mandatory N); 6 Reference, Description, Stage, From, In Stage, Due, Assignee, Actions (Column, mandatory -); 7 Assignee (Drop-down, mandatory N).
 Actions: Claim; Assign; Clear Stage Filter; Open a row.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -47691,7 +47691,7 @@
       <c r="L432" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-42 Lists of Values of the FRS.
-Fields in this order: 1 List names (List, mandatory -); 2 Code, Label, Order, Parent, Effective, Status, Maker / Checker (Column, mandatory -); 3 Code (Text, mandatory Y); 4 Label (Text, mandatory Y); 5 Sort order (Number, mandatory Y); 6 Parent value (Text, mandatory N); 7 Effective from (Date, mandatory Y); 8 Effective to (Date, mandatory N).
+Fields in this order: 1 List names (List, mandatory -); 2 Code, Label, Order, Parent, Effective, Status, Maker / Checker, Actions (Column, mandatory -); 3 Code (Text, mandatory Y); 4 Label (Text, mandatory Y); 5 Sort order (Number, mandatory Y); 6 Parent value (Text, mandatory N); 7 Effective from (Date, mandatory Y); 8 Effective to (Date, mandatory N).
 Actions: New Value; Edit / Deactivate; Authorize.
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
@@ -47770,8 +47770,8 @@
       <c r="L433" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-43 Data Retention of the FRS.
-Fields in this order: 1 Record Type, Statuses, Years Online, Years Archive, Action, Rule, Last Review, Eligible Records (Column, mandatory -); 2 Statuses (Text, mandatory Y); 3 Years online (Number, mandatory Y); 4 Years in archive (Number, mandatory Y); 5 Action (Drop-down, mandatory N); 6 Active (Check box, mandatory N); 7 Description (Text, mandatory Y); 8 Reference, Description, Status, Last Activity (Column, mandatory -).
-Actions: Run Review Now; Records (row); Edit (row).
+Fields in this order: 1 Record Type, Statuses, Years Online, Years Archive, Action, Rule, Last Review, Eligible Records, Actions (Column, mandatory -); 2 Statuses (Text, mandatory Y); 3 Years online (Number, mandatory Y); 4 Years in archive (Number, mandatory Y); 5 Action (Drop-down, mandatory N); 6 Active (Check box, mandatory N); 7 Description (Text, mandatory Y); 8 Reference, Description, Status, Last Activity (Column, mandatory -).
+Actions: Run Review Now; Records (row action menu); Edit (row action menu).
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -47849,8 +47849,8 @@
       <c r="L434" s="12" t="inlineStr">
         <is>
           <t>The screen matches SCR-NB-44 Document Templates of the FRS.
-Fields in this order: 1 Template list (List, mandatory -); 2 Current version (Display, mandatory -); 3 Version, Title, Effective from, Status, Created (Column, mandatory -); 4 Load from Word (File, mandatory N); 5 Title (Text, mandatory Y); 6 Effective from (Date, mandatory Y); 7 Text (Text area, mandatory Y).
-Actions: New Version; Download icon of a version (as Word).
+Fields in this order: 1 Template list (List, mandatory -); 2 Current version (Display, mandatory -); 3 Version, Title, Effective from, Status, Created, Actions (Column, mandatory -); 4 Load from Word (File, mandatory N); 5 Title (Text, mandatory Y); 6 Effective from (Date, mandatory Y); 7 Text (Text area, mandatory Y).
+Actions: New Version; Download Word (row action menu of a version).
 The message of the field table is shown word for word and nothing is saved.</t>
         </is>
       </c>
@@ -48183,11 +48183,11 @@
       <c r="L438" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-035: "The client is inactive" (CLIENT_INACTIVE)
-MSG-NB-036: "Complete the client information before you &lt;step&gt;: &lt;missing&gt;" (CLIENT_INFO_INCOMPLETE)
-MSG-NB-037: "Upload the mandatory KYC documents before you &lt;step&gt;: &lt;missing&gt;" (KYC_DOCUMENTS_MISSING)
-MSG-NB-038: "The KYC must be verified by a user other than its maker" (KYC_FOUR_EYES)
-MSG-NB-039: "Client &lt;code&gt; has no verified KYC" (KYC_NOT_VERIFIED)</t>
+MSG-NB-034: "The client is inactive" (CLIENT_INACTIVE)
+MSG-NB-035: "Complete the client information before you &lt;step&gt;: &lt;missing&gt;" (CLIENT_INFO_INCOMPLETE)
+MSG-NB-036: "Upload the mandatory KYC documents before you &lt;step&gt;: &lt;missing&gt;" (KYC_DOCUMENTS_MISSING)
+MSG-NB-037: "The KYC must be verified by a user other than its maker" (KYC_FOUR_EYES)
+MSG-NB-038: "Client &lt;code&gt; has no verified KYC" (KYC_NOT_VERIFIED)</t>
         </is>
       </c>
       <c r="M438" s="12" t="inlineStr">
@@ -48262,16 +48262,16 @@
       <c r="L439" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-040: "Enter the first day"
-MSG-NB-041: "Enter the instruction"
-MSG-NB-044: "Select the instruction type"
-MSG-NB-047: "The end date must not be before the start date"
-MSG-NB-048: "The client is already tagged &lt;tag code&gt;" (CLIENT_TAG_EXISTS)
-MSG-NB-049: "The end date must not be before the start date" (INSTRUCTION_DATES)
-MSG-NB-050: "An ended instruction cannot be changed" (INSTRUCTION_ENDED)
-MSG-NB-051: "Enter the instruction" (INSTRUCTION_TEXT_REQUIRED)
-MSG-NB-052: "Client instruction not found: &lt;instruction id&gt;" (NOT_FOUND)
-MSG-NB-053: "Client tag not found: &lt;tag code&gt;" (NOT_FOUND)</t>
+MSG-NB-039: "Enter the first day"
+MSG-NB-040: "Enter the instruction"
+MSG-NB-043: "Select the instruction type"
+MSG-NB-046: "The end date must not be before the start date"
+MSG-NB-047: "The client is already tagged &lt;tag code&gt;" (CLIENT_TAG_EXISTS)
+MSG-NB-048: "The end date must not be before the start date" (INSTRUCTION_DATES)
+MSG-NB-049: "An ended instruction cannot be changed" (INSTRUCTION_ENDED)
+MSG-NB-050: "Enter the instruction" (INSTRUCTION_TEXT_REQUIRED)
+MSG-NB-051: "Client instruction not found: &lt;instruction id&gt;" (NOT_FOUND)
+MSG-NB-052: "Client tag not found: &lt;tag code&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M439" s="12" t="inlineStr">
@@ -48346,11 +48346,11 @@
       <c r="L440" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-056: "Client information incomplete: &lt;missing&gt;" (INFO_INCOMPLETE)
-MSG-NB-057: "The periodic KYC review was due on &lt;kyc review due&gt;" (KYC_EXPIRED)
-MSG-NB-058: "Confirmed client without a sub-ledger party code" (MISSING_PARTY)
-MSG-NB-059: "Party &lt;party code&gt; is not active" (PARTY_INACTIVE)
-MSG-NB-060: "Party &lt;party code&gt; does not exist" (PARTY_NOT_FOUND)</t>
+MSG-NB-055: "Client information incomplete: &lt;missing&gt;" (INFO_INCOMPLETE)
+MSG-NB-056: "The periodic KYC review was due on &lt;kyc review due&gt;" (KYC_EXPIRED)
+MSG-NB-057: "Confirmed client without a sub-ledger party code" (MISSING_PARTY)
+MSG-NB-058: "Party &lt;party code&gt; is not active" (PARTY_INACTIVE)
+MSG-NB-059: "Party &lt;party code&gt; does not exist" (PARTY_NOT_FOUND)</t>
         </is>
       </c>
       <c r="M440" s="12" t="inlineStr">
@@ -48425,15 +48425,15 @@
       <c r="L441" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-067: "Choose the client or give the prospect name"
-MSG-NB-068: "Describe the requested cover"
-MSG-NB-069: "Enter a valid e-mail address"
-MSG-NB-071: "Quotation request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-072: "Give the client code or the prospect's name" (QUOTATION_REQUEST_CLIENT)
-MSG-NB-073: "Request &lt;request no&gt; is already &lt;status&gt;" (QUOTATION_REQUEST_CLOSED)
-MSG-NB-074: "Request &lt;external ref&gt; of &lt;channel&gt; was already received" (QUOTATION_REQUEST_DUPLICATE)
-MSG-NB-075: "Request &lt;request no&gt; has a client" (QUOTATION_REQUEST_HAS_CLIENT)
-MSG-NB-076: "Give the reason for closing" (QUOTATION_REQUEST_REASON)</t>
+MSG-NB-066: "Choose the client or give the prospect name"
+MSG-NB-067: "Describe the requested cover"
+MSG-NB-068: "Enter a valid e-mail address"
+MSG-NB-070: "Quotation request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-071: "Give the client code or the prospect's name" (QUOTATION_REQUEST_CLIENT)
+MSG-NB-072: "Request &lt;request no&gt; is already &lt;status&gt;" (QUOTATION_REQUEST_CLOSED)
+MSG-NB-073: "Request &lt;external ref&gt; of &lt;channel&gt; was already received" (QUOTATION_REQUEST_DUPLICATE)
+MSG-NB-074: "Request &lt;request no&gt; has a client" (QUOTATION_REQUEST_HAS_CLIENT)
+MSG-NB-075: "Give the reason for closing" (QUOTATION_REQUEST_REASON)</t>
         </is>
       </c>
       <c r="M441" s="12" t="inlineStr">
@@ -48508,9 +48508,9 @@
       <c r="L442" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-079: "Select the quotations to send" (QUOTATION_BATCH_EMPTY)
-MSG-NB-080: "Cannot send: &lt;problems&gt;" (QUOTATION_BATCH_INVALID)
-MSG-NB-081: "Quotation &lt;quotation no&gt; must be approved before it is sent" (QUOTATION_NOT_APPROVED)</t>
+MSG-NB-078: "Select the quotations to send" (QUOTATION_BATCH_EMPTY)
+MSG-NB-079: "Cannot send: &lt;problems&gt;" (QUOTATION_BATCH_INVALID)
+MSG-NB-080: "Quotation &lt;quotation no&gt; must be approved before it is sent" (QUOTATION_NOT_APPROVED)</t>
         </is>
       </c>
       <c r="M442" s="12" t="inlineStr">
@@ -48585,9 +48585,9 @@
       <c r="L443" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-082: "Attach the client's acceptance e-mail (document type Client acceptance e-mail) first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-083: "The quotation offers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-084: "Record the client's acceptance first" (QUOTATION_NOT_ACCEPTED)</t>
+MSG-NB-081: "Attach the client's acceptance e-mail (document type Client acceptance e-mail) first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-082: "The quotation offers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-083: "Record the client's acceptance first" (QUOTATION_NOT_ACCEPTED)</t>
         </is>
       </c>
       <c r="M443" s="12" t="inlineStr">
@@ -48662,30 +48662,30 @@
       <c r="L444" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-087: "Add at least one risk item"
-MSG-NB-088: "Enter the sum insured of every item"
-MSG-NB-089: "Select the client or prospect"
-MSG-NB-090: "Select the product"
-MSG-NB-091: "The period end must be after the period start"
-MSG-NB-092: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-093: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-094: "Give the client code or the prospect's name" (QUOTATION_CLIENT_REQUIRED)
-MSG-NB-095: "The validity date has passed: change it before submitting" (QUOTATION_EXPIRED)
-MSG-NB-096: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
-MSG-NB-097: "Select the client and the product" (QUOTATION_INCOMPLETE)
-MSG-NB-098: "Select the product" (QUOTATION_INCOMPLETE)
-MSG-NB-099: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
-MSG-NB-100: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
-MSG-NB-101: "Add at least one risk item" (QUOTATION_NO_ITEMS)
-MSG-NB-102: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
-MSG-NB-103: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
-MSG-NB-104: "Renewal &lt;renewal ref&gt; already has quotation &lt;quotation no&gt;" (QUOTATION_RENEWAL_EXISTS)
-MSG-NB-105: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
-MSG-NB-106: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
-MSG-NB-107: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
-MSG-NB-108: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-109: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
-MSG-NB-110: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-086: "Add at least one risk item"
+MSG-NB-087: "Enter the sum insured of every item"
+MSG-NB-088: "Select the client or prospect"
+MSG-NB-089: "Select the product"
+MSG-NB-090: "The period end must be after the period start"
+MSG-NB-091: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-092: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-093: "Give the client code or the prospect's name" (QUOTATION_CLIENT_REQUIRED)
+MSG-NB-094: "The validity date has passed: change it before submitting" (QUOTATION_EXPIRED)
+MSG-NB-095: "A quotation is approved by someone other than its maker" (QUOTATION_FOUR_EYES)
+MSG-NB-096: "Select the client and the product" (QUOTATION_INCOMPLETE)
+MSG-NB-097: "Select the product" (QUOTATION_INCOMPLETE)
+MSG-NB-098: "Quotation &lt;quotation no&gt; is &lt;&gt;" (QUOTATION_NOT_EDITABLE)
+MSG-NB-099: "The premium cannot be computed: give each item a sum insured (and a rate when the product has no default rate)" (QUOTATION_NOT_RATED)
+MSG-NB-100: "Add at least one risk item" (QUOTATION_NO_ITEMS)
+MSG-NB-101: "The period end must be after the period start" (QUOTATION_PERIOD_INVALID)
+MSG-NB-102: "The product of a quotation cannot change" (QUOTATION_PRODUCT_FIXED)
+MSG-NB-103: "Renewal &lt;renewal ref&gt; already has quotation &lt;quotation no&gt;" (QUOTATION_RENEWAL_EXISTS)
+MSG-NB-104: "Choose the market segment on the Client step before you submit the quotation" (QUOTATION_SEGMENT_REQUIRED)
+MSG-NB-105: "The validity date cannot be in the past" (QUOTATION_VALIDITY_PAST)
+MSG-NB-106: "Version &lt;version no&gt; was submitted and is read-only" (QUOTATION_VERSION_FROZEN)
+MSG-NB-107: "The quotation is priced on version &lt;scheme version&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: save the quotation again to re-price it" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-108: "Unknown rating basis &lt;value&gt;" (RATING_BASIS_INVALID)
+MSG-NB-109: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M444" s="12" t="inlineStr">
@@ -48760,8 +48760,8 @@
       <c r="L445" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-112: "Enter the item rate between 0 and 100"
-MSG-NB-113: "Explain why the scheme rate cannot be used"</t>
+MSG-NB-111: "Enter the item rate between 0 and 100"
+MSG-NB-112: "Explain why the scheme rate cannot be used"</t>
         </is>
       </c>
       <c r="M445" s="12" t="inlineStr">
@@ -48836,20 +48836,20 @@
       <c r="L446" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-120: "Select the client or prospect"
-MSG-NB-121: "Select the product"
-MSG-NB-122: "The period end must be after the period start"
-MSG-NB-123: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
-MSG-NB-124: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-125: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
-MSG-NB-126: "Complete the PRF header" (PRF_INCOMPLETE)
-MSG-NB-127: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
-MSG-NB-128: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
-MSG-NB-129: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
-MSG-NB-130: "The period end must be after the period start" (PRF_PERIOD_INVALID)
-MSG-NB-131: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
-MSG-NB-132: "Renewal &lt;renewal ref&gt; already has proposal request &lt;prf no&gt;" (PROPOSAL_RENEWAL_EXISTS)
-MSG-NB-133: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-119: "Select the client or prospect"
+MSG-NB-120: "Select the product"
+MSG-NB-121: "The period end must be after the period start"
+MSG-NB-122: "Attach the mandatory documents: &lt;missing&gt;" (MISSING_DOCUMENTS)
+MSG-NB-123: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-124: "A PRF is approved by someone other than its maker" (PRF_FOUR_EYES)
+MSG-NB-125: "Complete the PRF header" (PRF_INCOMPLETE)
+MSG-NB-126: "Describe the risk (sections or risk items) before submitting" (PRF_INCOMPLETE)
+MSG-NB-127: "PRF &lt;prf no&gt; cannot be changed while &lt;&gt;" (PRF_NOT_EDITABLE)
+MSG-NB-128: "No TSU rule applies to this package risk: quote it directly as a package quotation" (PRF_NOT_NEEDED)
+MSG-NB-129: "The period end must be after the period start" (PRF_PERIOD_INVALID)
+MSG-NB-130: "The product of a PRF cannot change" (PRF_PRODUCT_FIXED)
+MSG-NB-131: "Renewal &lt;renewal ref&gt; already has proposal request &lt;prf no&gt;" (PROPOSAL_RENEWAL_EXISTS)
+MSG-NB-132: "Product &lt;code&gt; is not offered to segment &lt;market segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M446" s="12" t="inlineStr">
@@ -48924,27 +48924,27 @@
       <c r="L447" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-137: "Enter the premium quoted"
-MSG-NB-144: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
-MSG-NB-145: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
-MSG-NB-146: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
-MSG-NB-147: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
-MSG-NB-148: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
-MSG-NB-149: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
-MSG-NB-150: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
-MSG-NB-151: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
-MSG-NB-152: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
-MSG-NB-153: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
-MSG-NB-154: "The chosen terms are gone" (PS_TERMS_MISSING)
-MSG-NB-155: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
-MSG-NB-156: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
-MSG-NB-157: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
-MSG-NB-158: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
-MSG-NB-159: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
-MSG-NB-160: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
-MSG-NB-161: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
-MSG-NB-162: "No insurer terms have been received" (TERMS_NONE)
-MSG-NB-163: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
+MSG-NB-136: "Enter the premium quoted"
+MSG-NB-143: "Attach the client's acceptance e-mail first" (ACCEPTANCE_EMAIL_REQUIRED)
+MSG-NB-144: "The proposal covers risk groups &lt;offered&gt; only" (ACCEPTANCE_GROUP_UNKNOWN)
+MSG-NB-145: "&lt;name&gt; has no placement e-mail address" (INSURER_NO_EMAIL)
+MSG-NB-146: "Insurer response not found: &lt;response id&gt;" (NOT_FOUND)
+MSG-NB-147: "Record the client's acceptance of the proposal first" (PROPOSAL_NOT_ACCEPTED)
+MSG-NB-148: "No terms of &lt;chosen insurer&gt; are recorded" (PROPOSAL_TERMS_MISSING)
+MSG-NB-149: "The proposal slip is approved by another TSU officer" (PS_FOUR_EYES)
+MSG-NB-150: "Choose the insurer (or flag the recommended one) for the proposal slip" (PS_INSURER_REQUIRED)
+MSG-NB-151: "No proposal slip has been prepared yet" (PS_NOT_PREPARED)
+MSG-NB-152: "&lt;insurer name&gt; has not quoted terms" (PS_TERMS_MISSING)
+MSG-NB-153: "The chosen terms are gone" (PS_TERMS_MISSING)
+MSG-NB-154: "Insurers are selected before the quotation slip is submitted" (QS_CLOSED)
+MSG-NB-155: "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES)
+MSG-NB-156: "No quotation slip has been prepared yet" (QS_NOT_PREPARED)
+MSG-NB-157: "Select at least one insurer of the panel for the quotation slip" (QS_NO_INSURER)
+MSG-NB-158: "Insurer terms are keyed in after the quotation slip is sent" (RESPONSES_CLOSED)
+MSG-NB-159: "Only received terms can be recommended" (RESPONSE_NOT_RECEIVED)
+MSG-NB-160: "Enter the premium quoted by &lt;insurer name&gt;" (RESPONSE_PREMIUM_REQUIRED)
+MSG-NB-161: "No insurer terms have been received" (TERMS_NONE)
+MSG-NB-162: "&lt;pending&gt; insurer(s) have not answered: close the request to proceed" (TERMS_PENDING)</t>
         </is>
       </c>
       <c r="M447" s="12" t="inlineStr">
@@ -49019,12 +49019,12 @@
       <c r="L448" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-166: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
-MSG-NB-167: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-168: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-169: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
-MSG-NB-170: "Enter the Free First Year start" (FFY_START_REQUIRED)
-MSG-NB-171: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
+MSG-NB-165: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_ACTIVE)
+MSG-NB-166: "Product &lt;product code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-167: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-168: "Account &lt;arn&gt; is not tagged Free First Year" (FFY_NOT_TAGGED)
+MSG-NB-169: "Enter the Free First Year start" (FFY_START_REQUIRED)
+MSG-NB-170: "The payment gate of &lt;arn&gt; is passed" (PAYMENT_ARRANGEMENT_LOCKED)</t>
         </is>
       </c>
       <c r="M448" s="12" t="inlineStr">
@@ -49099,22 +49099,22 @@
       <c r="L449" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-173: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-174: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
-MSG-NB-175: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
-MSG-NB-176: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
-MSG-NB-177: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
-MSG-NB-178: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
-MSG-NB-179: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
-MSG-NB-180: "Select the new insurer" (INSURER_REQUIRED)
-MSG-NB-181: "Select an insurer other than the current one" (INSURER_UNCHANGED)
-MSG-NB-182: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-183: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-184: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
-MSG-NB-185: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
-MSG-NB-186: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
-MSG-NB-187: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
-MSG-NB-188: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
+MSG-NB-172: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-173: "Account &lt;arn&gt; is not a renewal account" (ACCOUNT_NOT_RENEWAL)
+MSG-NB-174: "Account &lt;arn&gt; is &lt;&gt;, not &lt;status&gt;" (ACCOUNT_STATUS_INVALID)
+MSG-NB-175: "Account &lt;arn&gt; is &lt;status&gt;, not DRAFT" (ACCOUNT_STATUS_INVALID)
+MSG-NB-176: "The ARN must read ARN-yyyy-nnnnnn (or ARN-yyyy-nnnnnn-nn)" (ARN_INVALID)
+MSG-NB-177: "An account already has ARN &lt;given&gt;" (ARN_IN_USE)
+MSG-NB-178: "The insurer of account &lt;arn&gt; cannot be changed when it is &lt;&gt;" (INSURER_CHANGE_NOT_ALLOWED)
+MSG-NB-179: "Select the new insurer" (INSURER_REQUIRED)
+MSG-NB-180: "Select an insurer other than the current one" (INSURER_UNCHANGED)
+MSG-NB-181: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-182: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-183: "Account &lt;arn&gt; is set up with insurer &lt;insurer code&gt;" (PLACEMENT_INSURER_MISMATCH)
+MSG-NB-184: "Attach the issued policy (policy copy or e-policy) before direct booking" (POLICY_DOCUMENT_REQUIRED)
+MSG-NB-185: "Account &lt;arn&gt; needs &lt;term years&gt; policy number(s), one per year" (POLICY_NUMBERS_MISMATCH)
+MSG-NB-186: "TSU clearance is given before the account is validated" (TSU_CLEARANCE_CLOSED)
+MSG-NB-187: "TSU must clear the account first: &lt;reason&gt;" (TSU_CLEARANCE_REQUIRED)</t>
         </is>
       </c>
       <c r="M449" s="12" t="inlineStr">
@@ -49189,25 +49189,25 @@
       <c r="L450" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-190: "Choose the client and product to save the draft."
-MSG-NB-191: "The draft is not saved yet: click Save Draft to check it before submission."
-MSG-NB-192: "The draft was not saved: correct what the message above describes, then save the draft again."
-MSG-NB-193: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
-MSG-NB-194: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
-MSG-NB-195: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
-MSG-NB-196: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
-MSG-NB-197: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
-MSG-NB-198: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
-MSG-NB-199: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
-MSG-NB-200: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
-MSG-NB-201: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
-MSG-NB-202: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
-MSG-NB-203: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
-MSG-NB-204: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
-MSG-NB-205: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
-MSG-NB-206: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
-MSG-NB-207: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-NB-208: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
+MSG-NB-189: "Choose the client and product to save the draft."
+MSG-NB-190: "The draft is not saved yet: click Save Draft to check it before submission."
+MSG-NB-191: "The draft was not saved: correct what the message above describes, then save the draft again."
+MSG-NB-192: "The draft was not saved: its risks are already on the account shown above. Change the risk items, or open the existing account instead."
+MSG-NB-193: "Select the client" (ACCOUNT_CLIENT_REQUIRED)
+MSG-NB-194: "Complete the mandatory fields of &lt;product code&gt;: &lt;check&gt;" (ACCOUNT_INCOMPLETE)
+MSG-NB-195: "The period end must be after the period start" (ACCOUNT_PERIOD_INVALID)
+MSG-NB-196: "Select the product" (ACCOUNT_PRODUCT_REQUIRED)
+MSG-NB-197: "Only a renewal account names the policy it renews (&lt;renewal of ref&gt;)" (ACCOUNT_RENEWAL_OF_NOT_RENEWAL)
+MSG-NB-198: "A multi-year account needs a term of at least 2 years" (ACCOUNT_TERM_INVALID)
+MSG-NB-199: "Product &lt;code&gt; cannot be paid directly to the insurer" (DIRECT_PAYMENT_NOT_ELIGIBLE)
+MSG-NB-200: "Duplicate of existing account &lt;arns&gt;: &lt;details&gt;" (DUPLICATE_ACCOUNT)
+MSG-NB-201: "Product &lt;code&gt; is not Free First Year eligible" (FFY_NOT_ELIGIBLE)
+MSG-NB-202: "Upload the mandatory documents: &lt;check&gt;" (MISSING_DOCUMENTS)
+MSG-NB-203: "Product &lt;code&gt; carries no mortgagee" (MORTGAGE_NOT_APPLICABLE)
+MSG-NB-204: "Product &lt;code&gt; allows a term of up to &lt;max term years&gt; year(s)" (MULTI_YEAR_NOT_ALLOWED)
+MSG-NB-205: "Compute the premium (sum insured and rate of every item) first" (PREMIUM_NOT_RATED)
+MSG-NB-206: "Account &lt;arn&gt; is priced on version &lt;priced&gt; of &lt;code&gt;; version &lt;scheme version&gt; is current: update the account to re-price it or request a rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-NB-207: "Product &lt;code&gt; is not offered to segment &lt;segment&gt;" (SEGMENT_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M450" s="12" t="inlineStr">
@@ -49282,9 +49282,9 @@
       <c r="L451" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-213: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-214: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
-MSG-NB-215: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
+MSG-NB-212: "Account &lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-213: "Account &lt;arn&gt; is not paid directly to the insurer" (GATE_NOT_DIRECT_PAYMENT)
+MSG-NB-214: "Account &lt;arn&gt; must be paid: match its payment from a payment report" (GATE_REQUIRES_PAYMENT)</t>
         </is>
       </c>
       <c r="M451" s="12" t="inlineStr">
@@ -49359,17 +49359,17 @@
       <c r="L452" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-218: "Record Hold Cover Confirmation"
-MSG-NB-219: "Record Hold Cover Decline"
-MSG-NB-220: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
-MSG-NB-221: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
-MSG-NB-222: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
-MSG-NB-223: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
-MSG-NB-224: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
-MSG-NB-225: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
-MSG-NB-226: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
-MSG-NB-227: "Choose the insurer on the account first" (INSURER_NOT_SET)
-MSG-NB-228: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
+MSG-NB-217: "Record Hold Cover Confirmation"
+MSG-NB-218: "Record Hold Cover Decline"
+MSG-NB-219: "The hold cover of &lt;arn&gt; is &lt;status&gt;" (HOLD_COVER_CLOSED)
+MSG-NB-220: "The hold cover cannot expire before it starts (&lt;start date&gt;)" (HOLD_COVER_DATES)
+MSG-NB-221: "Account &lt;arn&gt; has no open hold cover" (HOLD_COVER_NONE)
+MSG-NB-222: "Account &lt;arn&gt; has no open hold cover request" (HOLD_COVER_NONE)
+MSG-NB-223: "A hold cover is requested while the account is being placed, not &lt;&gt;" (HOLD_COVER_NOT_ALLOWED)
+MSG-NB-224: "Account &lt;arn&gt; already has a hold cover requested or confirmed" (HOLD_COVER_OPEN)
+MSG-NB-225: "Enter the insurer's reference" (HOLD_COVER_REFERENCE)
+MSG-NB-226: "Choose the insurer on the account first" (INSURER_NOT_SET)
+MSG-NB-227: "Select the reason" (REASSIGN_REASON_REQUIRED)</t>
         </is>
       </c>
       <c r="M452" s="12" t="inlineStr">
@@ -49444,20 +49444,20 @@
       <c r="L453" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-237: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-238: "Missing documents: &lt;missing&gt;" (DOCUMENTS_MISSING)
-MSG-NB-239: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
-MSG-NB-240: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
-MSG-NB-241: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-242: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
-MSG-NB-243: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
-MSG-NB-244: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
-MSG-NB-245: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
-MSG-NB-246: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
-MSG-NB-247: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
-MSG-NB-248: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
-MSG-NB-249: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
-MSG-NB-250: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
+MSG-NB-235: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-236: "Missing documents: &lt;names&gt;" (DOCUMENTS_MISSING)
+MSG-NB-237: "Choose the insurer and branch on the account before placement" (INSURER_NOT_SET)
+MSG-NB-238: "Placement slip file not found: &lt;format&gt;" (NOT_FOUND)
+MSG-NB-239: "Placement slip not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-240: "The account is &lt;&gt;; a slip needs Ready for placement" (NOT_READY_FOR_PLACEMENT)
+MSG-NB-241: "The payment or client confirmation is not recorded" (PAYMENT_NOT_CONFIRMED)
+MSG-NB-242: "&lt;name&gt; is set up for &lt;placement channel&gt; placements; only e-mail is available: set the insurer to e-mail placement" (PLACEMENT_CHANNEL_PARKED)
+MSG-NB-243: "Select at least one account" (PLACEMENT_NO_ACCOUNTS)
+MSG-NB-244: "Select the accounts to place" (SLIP_NO_ACCOUNTS)
+MSG-NB-245: "Placement prerequisites not met - &lt;problems&gt;" (SLIP_PREREQUISITES_UNMET)
+MSG-NB-246: "Slip &lt;display no&gt; was already replaced" (SLIP_SUPERSEDED)
+MSG-NB-247: "Slip &lt;slip no&gt; v&lt;version no&gt; was replaced by a new version" (SLIP_SUPERSEDED)
+MSG-NB-248: "TSU clearance is required (&lt;rule&gt;) and not given" (TSU_NOT_CLEARED)</t>
         </is>
       </c>
       <c r="M453" s="12" t="inlineStr">
@@ -49532,10 +49532,10 @@
       <c r="L454" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-254: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
-MSG-NB-255: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
-MSG-NB-256: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
-MSG-NB-257: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-252: "Choose the billing file format XLSX or ODS" (BILLING_FORMAT)
+MSG-NB-253: "No CBG Fire account awaiting payment is left to bill" (BILLING_NOTHING_TO_BILL)
+MSG-NB-254: "Not CBG Fire accounts awaiting payment, or already billed: &lt;wanted&gt;" (BILLING_NOT_CANDIDATE)
+MSG-NB-255: "Billing batch not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M454" s="12" t="inlineStr">
@@ -49610,19 +49610,19 @@
       <c r="L455" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-259: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
-MSG-NB-260: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
-MSG-NB-261: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
-MSG-NB-262: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
-MSG-NB-263: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-264: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
-MSG-NB-265: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
-MSG-NB-266: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
-MSG-NB-267: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
-MSG-NB-268: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-269: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
-MSG-NB-270: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
-MSG-NB-271: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
+MSG-NB-257: "&lt;arn&gt; is &lt;&gt;, not awaiting payment" (ACCOUNT_NOT_AWAITING_PAYMENT)
+MSG-NB-258: "Billing batch &lt;batch no&gt; is closed" (BILLING_BATCH_CLOSED)
+MSG-NB-259: "Billing batch not found: &lt;batch id&gt;" (NOT_FOUND)
+MSG-NB-260: "Payment report line not found: &lt;line id&gt;" (NOT_FOUND)
+MSG-NB-261: "Payment report not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-262: "Row &lt;row no&gt; is already matched to &lt;arn&gt;" (PAYMENT_LINE_MATCHED)
+MSG-NB-263: "Choose the CLPC billing batch the report answers" (PAYMENT_REPORT_BATCH_REQUIRED)
+MSG-NB-264: "Payment report &lt;report no&gt; is &lt;status&gt;" (PAYMENT_REPORT_CLOSED)
+MSG-NB-265: "The payment report has no rows" (PAYMENT_REPORT_EMPTY)
+MSG-NB-266: "The CLPC report needs a 'PN No.' or 'Loan Application No.' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-267: "The payment report needs an 'ARN' or 'Reference' column" (PAYMENT_REPORT_LAYOUT)
+MSG-NB-268: "Row &lt;row no&gt;: '&lt;value&gt;' is not a date (yyyy-mm-dd)" (PAYMENT_REPORT_VALUE)
+MSG-NB-269: "Row &lt;row no&gt;: '&lt;value&gt;' is not an amount" (PAYMENT_REPORT_VALUE)</t>
         </is>
       </c>
       <c r="M455" s="12" t="inlineStr">
@@ -49697,14 +49697,14 @@
       <c r="L456" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-274: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
-MSG-NB-275: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
-MSG-NB-276: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
-MSG-NB-277: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
-MSG-NB-278: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
-MSG-NB-279: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-280: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
-MSG-NB-281: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-272: "No account found for &lt;file name&gt;: choose the account (ARN)" (EPOLICY_ACCOUNT_NOT_FOUND)
+MSG-NB-273: "Account &lt;arn&gt; is &lt;&gt;; an e-policy is received once placed" (EPOLICY_ACCOUNT_STATUS)
+MSG-NB-274: "Upload between 1 and 50 e-policies at a time" (EPOLICY_FILE_COUNT)
+MSG-NB-275: "The e-policy &lt;file name&gt; is already &lt;&gt;" (EPOLICY_REVIEWED)
+MSG-NB-276: "This upload is &lt;status&gt;" (EPOLICY_UPLOAD_CLOSED)
+MSG-NB-277: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-278: "E-policy upload file not found: &lt;item id&gt;" (NOT_FOUND)
+MSG-NB-279: "Epolicy not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M456" s="12" t="inlineStr">
@@ -49779,10 +49779,10 @@
       <c r="L457" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-283: "Enter one policy number per policy year."
-MSG-NB-286: "The policy numbers must be different."
-MSG-NB-287: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
-MSG-NB-288: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
+MSG-NB-281: "Enter one policy number per policy year."
+MSG-NB-284: "The policy numbers must be different."
+MSG-NB-285: "Confirm the policy data of &lt;arn&gt; before sending the e-policy" (EPOLICY_NOT_CONFIRMED)
+MSG-NB-286: "The e-policy &lt;file name&gt; of &lt;arn&gt; is already &lt;status&gt;" (EPOLICY_REVIEWED)</t>
         </is>
       </c>
       <c r="M457" s="12" t="inlineStr">
@@ -49857,10 +49857,10 @@
       <c r="L458" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-291: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
-MSG-NB-292: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
-MSG-NB-293: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
-MSG-NB-294: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-289: "Account &lt;arn&gt; is &lt;status&gt;; it must be placed first" (IA_ACCOUNT_STATUS)
+MSG-NB-290: "Account &lt;arn&gt; has no mortgagee bank: no Insurance Advice" (IA_NOT_MORTGAGED)
+MSG-NB-291: "Select between 1 and 50 Insurance Advices" (IA_SELECTION)
+MSG-NB-292: "Insurance advice not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M458" s="12" t="inlineStr">
@@ -49935,8 +49935,8 @@
       <c r="L459" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-297: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
-MSG-NB-298: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
+MSG-NB-295: "Account &lt;arn&gt; has no contact e-mail: enter the recipient" (EPOLICY_NO_RECIPIENT)
+MSG-NB-296: "Select between 1 and 200 records" (ISSUANCE_SELECTION)</t>
         </is>
       </c>
       <c r="M459" s="12" t="inlineStr">
@@ -50011,22 +50011,22 @@
       <c r="L460" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-301: "A negative endorsement reduces the sum insured (enter a minus)"
-MSG-NB-302: "A positive endorsement increases the sum insured"
-MSG-NB-303: "Choose the reason"
-MSG-NB-304: "Describe the cancellation"
-MSG-NB-305: "Describe the change"
-MSG-NB-306: "Enter a booking date that is not in the future"
-MSG-NB-307: "Enter a rate of zero or more, or leave it blank"
-MSG-NB-308: "Enter the cancellation date"
-MSG-NB-309: "Enter the change of the sum insured"
-MSG-NB-310: "Enter the effective date"
-MSG-NB-312: "The booking date cannot be in the future"
-MSG-NB-313: "No queued account to book" (BATCH_EMPTY)
-MSG-NB-314: "Select at least one account to book" (BATCH_EMPTY)
-MSG-NB-315: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-316: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-317: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
+MSG-NB-299: "A negative endorsement reduces the sum insured (enter a minus)"
+MSG-NB-300: "A positive endorsement increases the sum insured"
+MSG-NB-301: "Choose the reason"
+MSG-NB-302: "Describe the cancellation"
+MSG-NB-303: "Describe the change"
+MSG-NB-304: "Enter a booking date that is not in the future"
+MSG-NB-305: "Enter a rate of zero or more, or leave it blank"
+MSG-NB-306: "Enter the cancellation date"
+MSG-NB-307: "Enter the change of the sum insured"
+MSG-NB-308: "Enter the effective date"
+MSG-NB-310: "The booking date cannot be in the future"
+MSG-NB-311: "No queued account to book" (BATCH_EMPTY)
+MSG-NB-312: "Select at least one account to book" (BATCH_EMPTY)
+MSG-NB-313: "The booking date &lt;booking date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-314: "Booking queue not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-315: "Account &lt;arn&gt; is no longer queued (&lt;status&gt;)" (QUEUE_ENTRY_CLOSED)</t>
         </is>
       </c>
       <c r="M460" s="12" t="inlineStr">
@@ -50101,25 +50101,25 @@
       <c r="L461" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-319: "Enter a booking date that is not in the future"
-MSG-NB-320: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
-MSG-NB-321: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
-MSG-NB-322: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
-MSG-NB-323: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
-MSG-NB-324: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
-MSG-NB-325: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
-MSG-NB-326: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
-MSG-NB-327: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
-MSG-NB-328: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
-MSG-NB-329: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
-MSG-NB-330: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
-MSG-NB-331: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
-MSG-NB-332: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
-MSG-NB-333: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
-MSG-NB-334: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
-MSG-NB-335: "No invoice" (INVOICE_NOT_FOUND)
-MSG-NB-336: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
-MSG-NB-337: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
+MSG-NB-317: "Enter a booking date that is not in the future"
+MSG-NB-318: "Account &lt;arn&gt; has no insurer" (ACCOUNT_INSURER_MISSING)
+MSG-NB-319: "Account &lt;arn&gt; is &lt;&gt;: only issued policies are booked" (ACCOUNT_NOT_BOOKABLE)
+MSG-NB-320: "Account &lt;arn&gt; has no period of cover" (ACCOUNT_PERIOD_MISSING)
+MSG-NB-321: "Billing number &lt;billing no&gt; of &lt;insurer code&gt; is already on invoice &lt;invoice no&gt;" (BILLING_NO_DUPLICATE)
+MSG-NB-322: "Enter the insurer billing number" (BILLING_NO_REQUIRED)
+MSG-NB-323: "The insurer billing number has at most 60 characters" (BILLING_NO_TOO_LONG)
+MSG-NB-324: "The company has no branch to book invoices" (BOOKING_BRANCH_MISSING)
+MSG-NB-325: "The booking date &lt;date&gt; is in the future" (BOOKING_DATE_FUTURE)
+MSG-NB-326: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (CLIENT_PARTY_MISSING)
+MSG-NB-327: "Enter the cost center of account &lt;arn&gt;" (COST_CENTER_REQUIRED)
+MSG-NB-328: "Account &lt;arn&gt; is already booked" (DUPLICATE_BOOKING)
+MSG-NB-329: "No sub-ledger party &lt;code&gt; for invoice &lt;invoice no&gt;" (INSURER_PARTY_MISSING)
+MSG-NB-330: "Each insurer appears once with a positive share" (INSURER_SHARES_INVALID)
+MSG-NB-331: "Insurer shares must add up to 100% and include the lead insurer &lt;insurer code&gt;" (INSURER_SHARES_INVALID)
+MSG-NB-332: "Invoice &lt;arn&gt;/&lt;transaction no&gt; is &lt;status&gt;" (INVOICE_ALREADY_BOOKED)
+MSG-NB-333: "No invoice" (INVOICE_NOT_FOUND)
+MSG-NB-334: "Policy year &lt;policy year&gt; of &lt;arn&gt; is not due for booking" (POLICY_YEAR_NOT_DUE)
+MSG-NB-335: "Account &lt;arn&gt; has no rated premium" (PREMIUM_NOT_RATED)</t>
         </is>
       </c>
       <c r="M461" s="12" t="inlineStr">
@@ -50194,15 +50194,15 @@
       <c r="L462" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-343: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
-MSG-NB-344: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
-MSG-NB-345: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
-MSG-NB-346: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
-MSG-NB-347: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
-MSG-NB-348: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-349: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
-MSG-NB-350: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
-MSG-NB-351: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-NB-341: "Account &lt;arn&gt; is &lt;&gt;: only booked accounts are endorsed" (ACCOUNT_NOT_BOOKED)
+MSG-NB-342: "A cancellation, and only a cancellation, has a kind" (CANCELLATION_KIND_REQUIRED)
+MSG-NB-343: "Enter the change of the sum insured or the premium" (ENDORSEMENT_CHANGE_REQUIRED)
+MSG-NB-344: "The effective date &lt;effective&gt; is not within a booked policy year of &lt;arn&gt;" (ENDORSEMENT_DATE_OUTSIDE_TERM)
+MSG-NB-345: "Enter the account, type, effective date and description" (ENDORSEMENT_INCOMPLETE)
+MSG-NB-346: "A negative endorsement or cancellation must return premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-347: "A positive endorsement must add premium" (ENDORSEMENT_SIGN_MISMATCH)
+MSG-NB-348: "The return premium exceeds the premium in force of policy year &lt;year&gt;" (RETURN_EXCEEDS_PREMIUM)
+MSG-NB-349: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="M462" s="12" t="inlineStr">
@@ -50277,14 +50277,14 @@
       <c r="L463" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-353: "Give the reason of the credit"
-MSG-NB-355: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
-MSG-NB-356: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
-MSG-NB-357: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-358: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
-MSG-NB-359: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-360: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
-MSG-NB-361: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
+MSG-NB-351: "Give the reason of the credit"
+MSG-NB-353: "Service invoice &lt;si no&gt; has &lt;commission&gt; commission and &lt;vat&gt; VAT left to credit" (CREDIT_EXCEEDS_INVOICE)
+MSG-NB-354: "&lt;si no&gt; is itself a credit" (CREDIT_OF_CREDIT)
+MSG-NB-355: "Service invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-356: "Service invoice not found: &lt;si no&gt;" (NOT_FOUND)
+MSG-NB-357: "Service invoice type not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-358: "Service invoices of type &lt;type code&gt; are issued automatically with the early remittance incentive" (SERVICE_INVOICE_AUTOMATIC_ONLY)
+MSG-NB-359: "Service invoice type &lt;code&gt; is inactive" (SERVICE_INVOICE_TYPE_INACTIVE)</t>
         </is>
       </c>
       <c r="M463" s="12" t="inlineStr">
@@ -50359,12 +50359,12 @@
       <c r="L464" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-364: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-365: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
-MSG-NB-366: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
-MSG-NB-367: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-368: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-369: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-362: "Service invoice type already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-363: "The period end must not be before the period start" (INCENTIVE_PERIOD_INVALID)
+MSG-NB-364: "Incentive rules are maintained in Product Maintenance &gt; Incentive Criteria" (INCENTIVE_RULES_FROZEN)
+MSG-NB-365: "Auto-booking rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-366: "Incentive rule not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-367: "Service invoice type not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M464" s="12" t="inlineStr">
@@ -50439,32 +50439,32 @@
       <c r="L465" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-374: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
-MSG-NB-375: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
-MSG-NB-376: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
-MSG-NB-377: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
-MSG-NB-378: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
-MSG-NB-379: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
-MSG-NB-380: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
-MSG-NB-381: "The file has no data rows" (BULK_FILE_EMPTY)
-MSG-NB-382: "The file has no header row" (BULK_FILE_EMPTY)
-MSG-NB-383: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
-MSG-NB-384: "The spreadsheet has more than 100000 rows" (BULK_FILE_TOO_LARGE)
-MSG-NB-385: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
-MSG-NB-386: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
-MSG-NB-387: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
-MSG-NB-388: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
-MSG-NB-389: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
-MSG-NB-390: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
-MSG-NB-391: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
-MSG-NB-392: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
-MSG-NB-393: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
-MSG-NB-394: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
-MSG-NB-395: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
-MSG-NB-396: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-397: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
-MSG-NB-398: "Bulk job not found: &lt;job id&gt;" (NOT_FOUND)
-MSG-NB-399: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)</t>
+MSG-NB-372: "Risk groups are numbers separated by ';'" (ACCEPTANCE_GROUP_INVALID)
+MSG-NB-373: "Account &lt;arn&gt; is &lt;&gt;" (ACCOUNT_NOT_EDITABLE)
+MSG-NB-374: "Account &lt;arn&gt; belongs to another company" (ACCOUNT_OTHER_COMPANY)
+MSG-NB-375: "Business Type must be NEW_BUSINESS or RENEWAL" (BULK_BUSINESS_TYPE_INVALID)
+MSG-NB-376: "Enter an individual's name as 'Last, First'" (BULK_CLIENT_NAME_FORMAT)
+MSG-NB-377: "Give the Client Code or the Client Name" (BULK_CLIENT_REQUIRED)
+MSG-NB-378: "This file was already uploaded as &lt;job no&gt; (&lt;file name&gt;)" (BULK_DUPLICATE_FILE)
+MSG-NB-379: "The file has no data rows" (BULK_FILE_EMPTY)
+MSG-NB-380: "The file has no header row" (BULK_FILE_EMPTY)
+MSG-NB-381: "The file has &lt;size&gt; rows; the maximum is &lt;max&gt;" (BULK_FILE_TOO_LARGE)
+MSG-NB-382: "The spreadsheet has more than 100000 rows" (BULK_FILE_TOO_LARGE)
+MSG-NB-383: "Upload an Excel (.xlsx), OpenDocument (.ods), CSV (.csv) or text (.txt) file" (BULK_FILE_TYPE)
+MSG-NB-384: "The file cannot be read: &lt;message&gt;" (BULK_FILE_UNREADABLE)
+MSG-NB-385: "The file is not an OpenDocument spreadsheet" (BULK_FILE_UNREADABLE)
+MSG-NB-386: "Upload &lt;job no&gt; is already &lt;status&gt;" (BULK_JOB_CLOSED)
+MSG-NB-387: "Upload &lt;job no&gt; has not been committed yet" (BULK_JOB_NOT_COMPLETED)
+MSG-NB-388: "You are not allowed to use '&lt;title&gt;'" (BULK_NOT_PERMITTED)
+MSG-NB-389: "Choose the product of the upload" (BULK_PRODUCT_REQUIRED)
+MSG-NB-390: "The file does not follow the current template; missing column(s): &lt;missing&gt;" (BULK_TEMPLATE_MISMATCH)
+MSG-NB-391: "The fixed-width layout of this upload type has no fields" (BULK_TEXT_LAYOUT)
+MSG-NB-392: "The text file has no tab, pipe, semicolon or comma separated header line" (BULK_TEXT_LAYOUT)
+MSG-NB-393: "Action must be TAG or CANCEL" (FFY_ACTION_INVALID)
+MSG-NB-394: "No live account insures vehicle &lt;identifier&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-395: "Several accounts insure vehicle &lt;identifier&gt;: &lt;details&gt;" (FFY_VEHICLE_NOT_UNIQUE)
+MSG-NB-396: "Bulk job not found: &lt;job id&gt;" (NOT_FOUND)
+MSG-NB-397: "Bulk upload type not found: &lt;code&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M465" s="12" t="inlineStr">
@@ -50527,18 +50527,18 @@
       <c r="L466" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-401: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
-MSG-NB-402: "The file is empty" (ATTACHMENT_EMPTY)
-MSG-NB-403: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
-MSG-NB-404: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
-MSG-NB-405: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
-MSG-NB-406: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
-MSG-NB-407: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
-MSG-NB-408: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
-MSG-NB-409: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
-MSG-NB-410: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
-MSG-NB-411: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-412: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-399: "The file content does not match its .&lt;type&gt; type" (ATTACHMENT_CONTENT_MISMATCH)
+MSG-NB-400: "The file is empty" (ATTACHMENT_EMPTY)
+MSG-NB-401: "The file was rejected by the malware scan: &lt;detail&gt;" (ATTACHMENT_INFECTED)
+MSG-NB-402: "Stored file failed its checksum verification" (ATTACHMENT_INTEGRITY_FAILURE)
+MSG-NB-403: "The file exceeds the maximum size of &lt;to megabytes&gt; MB" (ATTACHMENT_TOO_LARGE)
+MSG-NB-404: "Only these file types are allowed: &lt;allowed extensions&gt;" (ATTACHMENT_TYPE_NOT_ALLOWED)
+MSG-NB-405: "Select between 1 and 50 documents" (DOCUMENT_FILE_COUNT)
+MSG-NB-406: "Upload between 1 and 50 files at a time" (DOCUMENT_FILE_COUNT)
+MSG-NB-407: "A reference is needed to nominate the file names" (DOCUMENT_REFERENCE_REQUIRED)
+MSG-NB-408: "Invalid entity type or id" (INVALID_ATTACHMENT_TARGET)
+MSG-NB-409: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-410: "Attachment content not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M466" s="12" t="inlineStr">
@@ -50601,16 +50601,16 @@
       <c r="L467" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-414: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-415: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-416: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-417: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
-MSG-NB-418: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
-MSG-NB-419: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
-MSG-NB-420: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
-MSG-NB-421: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
-MSG-NB-422: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
-MSG-NB-423: "The item is closed" (WORK_CASE_CLOSED)</t>
+MSG-NB-412: "&lt;entity type&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-413: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-414: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-415: "Workflow not found: &lt;workflow code&gt;" (NOT_FOUND)
+MSG-NB-416: "Workflow stage not found: &lt;stage code&gt;" (NOT_FOUND)
+MSG-NB-417: "'&lt;label&gt;' must be done from the record screen" (WORKFLOW_ACTION_NOT_GENERIC)
+MSG-NB-418: "You are not allowed to '&lt;label&gt;'" (WORKFLOW_ACTION_NOT_PERMITTED)
+MSG-NB-419: "Select a reason for '&lt;label&gt;'" (WORKFLOW_REASON_REQUIRED)
+MSG-NB-420: "'&lt;action&gt;' is not allowed while &lt;reference&gt; is in stage &lt;name&gt;" (WORKFLOW_TRANSITION_NOT_ALLOWED)
+MSG-NB-421: "The item is closed" (WORK_CASE_CLOSED)</t>
         </is>
       </c>
       <c r="M467" s="12" t="inlineStr">
@@ -50685,10 +50685,10 @@
       <c r="L468" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-426: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
-MSG-NB-427: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
-MSG-NB-428: "The item is closed" (WORK_CASE_CLOSED)
-MSG-NB-429: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
+MSG-NB-424: "Work item not found: &lt;case id&gt;" (NOT_FOUND)
+MSG-NB-425: "&lt;assignee&gt; does not work this queue" (WORK_ASSIGNEE_NOT_ELIGIBLE)
+MSG-NB-426: "The item is closed" (WORK_CASE_CLOSED)
+MSG-NB-427: "This item is not in your queue" (WORK_CLAIM_NOT_ALLOWED)</t>
         </is>
       </c>
       <c r="M468" s="12" t="inlineStr">
@@ -50763,14 +50763,14 @@
       <c r="L469" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-432: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
-MSG-NB-433: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
-MSG-NB-434: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
-MSG-NB-435: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
-MSG-NB-436: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
-MSG-NB-437: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
-MSG-NB-438: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
-MSG-NB-439: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-430: "&lt;file name&gt; cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE)
+MSG-NB-431: "Could not protect &lt;file name&gt;: &lt;message&gt;" (DOCUMENT_PROTECTION_FAILED)
+MSG-NB-432: "Invalid e-mail address: &lt;a&gt;" (EMAIL_ADDRESS_INVALID)
+MSG-NB-433: "Enter the &lt;field&gt;" (EMAIL_CONTENT_REQUIRED)
+MSG-NB-434: "Enter at least one recipient" (EMAIL_RECIPIENT_REQUIRED)
+MSG-NB-435: "Too many recipients" (EMAIL_TOO_MANY_RECIPIENTS)
+MSG-NB-436: "Only a failed message can be resent" (MESSAGE_NOT_FAILED)
+MSG-NB-437: "&lt;entity&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M469" s="12" t="inlineStr">
@@ -50845,17 +50845,17 @@
       <c r="L470" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-441: "Enter a whole number"
-MSG-NB-442: "Enter the first valid date"
-MSG-NB-443: "Enter the label"
-MSG-NB-444: "Must not be before the first valid date"
-MSG-NB-445: "Use capital letters, digits and _ (up to 40)"
-MSG-NB-446: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-NB-447: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
-MSG-NB-448: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
-MSG-NB-449: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
-MSG-NB-450: "List type not found: &lt;type code&gt;" (NOT_FOUND)
-MSG-NB-451: "List value not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-NB-439: "Enter a whole number"
+MSG-NB-440: "Enter the first valid date"
+MSG-NB-441: "Enter the label"
+MSG-NB-442: "Must not be before the first valid date"
+MSG-NB-443: "Use capital letters, digits and _ (up to 40)"
+MSG-NB-444: "&lt;type code&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-NB-445: "The effective-to date is before the effective-from date" (LOV_EFFECTIVITY_INVALID)
+MSG-NB-446: "The list &lt;type code&gt; is maintained by the system" (LOV_NOT_MAINTAINABLE)
+MSG-NB-447: "'&lt;code&gt;' is not a valid value of &lt;type code&gt; on &lt;date&gt;" (LOV_VALUE_INVALID)
+MSG-NB-448: "List type not found: &lt;type code&gt;" (NOT_FOUND)
+MSG-NB-449: "List value not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M470" s="12" t="inlineStr">
@@ -50930,13 +50930,13 @@
       <c r="L471" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-452: "Enter a whole number of bookings (0 or more)"
-MSG-NB-453: "Enter an amount of 0 or more"
-MSG-NB-454: "Enter the period"
-MSG-NB-455: "Enter the unit code or the officer username"
-MSG-NB-458: "The period end must not be before the start"
-MSG-NB-459: "Targets cannot be negative" (TARGET_NEGATIVE)
-MSG-NB-460: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
+MSG-NB-450: "Enter a whole number of bookings (0 or more)"
+MSG-NB-451: "Enter an amount of 0 or more"
+MSG-NB-452: "Enter the period"
+MSG-NB-453: "Enter the unit code or the officer username"
+MSG-NB-456: "The period end must not be before the start"
+MSG-NB-457: "Targets cannot be negative" (TARGET_NEGATIVE)
+MSG-NB-458: "The period end must not be before the period start" (TARGET_PERIOD_INVALID)</t>
         </is>
       </c>
       <c r="M471" s="12" t="inlineStr">
@@ -51011,11 +51011,11 @@
       <c r="L472" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-461: "Enter a name"
-MSG-NB-462: "The saved parameter variant is deleted."
-MSG-NB-465: "Report variant not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-466: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
-MSG-NB-467: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
+MSG-NB-459: "Enter a name"
+MSG-NB-460: "The saved parameter variant is deleted."
+MSG-NB-463: "Report variant not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-464: "Report &lt;report code&gt; is not available to you" (REPORT_NOT_AVAILABLE)
+MSG-NB-465: "Only the user who saved a report variant may delete it" (VARIANT_NOT_OWNER)</t>
         </is>
       </c>
       <c r="M472" s="12" t="inlineStr">
@@ -51090,13 +51090,13 @@
       <c r="L473" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-471: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
-MSG-NB-472: "Document template not found: &lt;code&gt;" (NOT_FOUND)
-MSG-NB-473: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-474: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
-MSG-NB-475: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
-MSG-NB-476: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
-MSG-NB-477: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
+MSG-NB-469: "This document cannot be produced in Word" (DOCUMENT_WORD_UNAVAILABLE)
+MSG-NB-470: "Document template not found: &lt;code&gt;" (NOT_FOUND)
+MSG-NB-471: "Document template not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-472: "Word copy of document not found: &lt;D&gt;" (NOT_FOUND)
+MSG-NB-473: "Enter the template text" (TEMPLATE_BODY_REQUIRED)
+MSG-NB-474: "The Word file needs the title in its first paragraph and the text below it" (TEMPLATE_WORD_INVALID)
+MSG-NB-475: "The file is not a Word (.docx) document" (TEMPLATE_WORD_INVALID)</t>
         </is>
       </c>
       <c r="M473" s="12" t="inlineStr">
@@ -51171,10 +51171,10 @@
       <c r="L474" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-479: "Between 0 and 50 years"
-MSG-NB-480: "Between 1 and 50 years"
-MSG-NB-481: "Enter a description"
-MSG-NB-482: "Enter at least one status"</t>
+MSG-NB-477: "Between 0 and 50 years"
+MSG-NB-478: "Between 1 and 50 years"
+MSG-NB-479: "Enter a description"
+MSG-NB-480: "Enter at least one status"</t>
         </is>
       </c>
       <c r="M474" s="12" t="inlineStr">
@@ -51237,13 +51237,13 @@
       <c r="L475" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-487: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-NB-488: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-NB-489: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-NB-490: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-NB-491: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-NB-492: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-NB-493: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-NB-485: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-NB-486: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-NB-487: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-NB-488: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-NB-489: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-NB-490: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-NB-491: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M475" s="12" t="inlineStr">
@@ -51318,8 +51318,8 @@
       <c r="L476" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-501: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-NB-502: "&lt;Column&gt; is mandatory"</t>
+MSG-NB-499: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-NB-500: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M476" s="12" t="inlineStr">
@@ -51394,7 +51394,7 @@
       <c r="L477" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-503: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
+MSG-NB-501: "&lt;quotation no&gt; is &lt;&gt;, not sent to the client"</t>
         </is>
       </c>
       <c r="M477" s="12" t="inlineStr">
@@ -51469,8 +51469,8 @@
       <c r="L478" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-504: "Account &lt;arn&gt; belongs to another company"
-MSG-NB-507: "The booking date &lt;date&gt; is in the future"</t>
+MSG-NB-502: "Account &lt;arn&gt; belongs to another company"
+MSG-NB-505: "The booking date &lt;date&gt; is in the future"</t>
         </is>
       </c>
       <c r="M478" s="12" t="inlineStr">
@@ -51545,9 +51545,9 @@
       <c r="L479" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-505: "Client Type must be INDIVIDUAL or CORPORATE"
-MSG-NB-506: "Client code &lt;code&gt; does not exist"
-MSG-NB-508: "The row matches several clients: &lt;details&gt;"</t>
+MSG-NB-503: "Client Type must be INDIVIDUAL or CORPORATE"
+MSG-NB-504: "Client code &lt;code&gt; does not exist"
+MSG-NB-506: "The row matches several clients: &lt;details&gt;"</t>
         </is>
       </c>
       <c r="M479" s="12" t="inlineStr">
@@ -51610,26 +51610,26 @@
       <c r="L480" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-NB-509: "Legacy policy &lt;legacy ref&gt; is already imported" (ACCOUNT_LEGACY_IMPORTED)
-MSG-NB-510: "Account &lt;arn&gt; was not imported from legacy" (ACCOUNT_NOT_MIGRATED)
-MSG-NB-511: "Client &lt;code&gt; was not migrated" (CLIENT_NOT_MIGRATED)
-MSG-NB-512: "A migrated client needs its source system and legacy code" (CLIENT_ORIGIN_REQUIRED)
-MSG-NB-513: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
-MSG-NB-514: "Account not found: &lt;account id&gt;" (NOT_FOUND)
-MSG-NB-515: "Account not found: &lt;arn&gt;" (NOT_FOUND)
-MSG-NB-516: "Account not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-517: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
-MSG-NB-518: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-519: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
-MSG-NB-520: "Client not found: &lt;client id&gt;" (NOT_FOUND)
-MSG-NB-521: "Company not found: &lt;company id&gt;" (NOT_FOUND)
-MSG-NB-522: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
-MSG-NB-523: "Notification not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-524: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-525: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
-MSG-NB-526: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
-MSG-NB-527: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-NB-528: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
+MSG-NB-507: "Legacy policy &lt;legacy ref&gt; is already imported" (ACCOUNT_LEGACY_IMPORTED)
+MSG-NB-508: "Account &lt;arn&gt; was not imported from legacy" (ACCOUNT_NOT_MIGRATED)
+MSG-NB-509: "Client &lt;code&gt; was not migrated" (CLIENT_NOT_MIGRATED)
+MSG-NB-510: "A migrated client needs its source system and legacy code" (CLIENT_ORIGIN_REQUIRED)
+MSG-NB-511: "&lt;entity type&gt; work item not found: &lt;entity id&gt;" (NOT_FOUND)
+MSG-NB-512: "Account not found: &lt;account id&gt;" (NOT_FOUND)
+MSG-NB-513: "Account not found: &lt;arn&gt;" (NOT_FOUND)
+MSG-NB-514: "Account not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-515: "Batch run not found: &lt;run no&gt;" (NOT_FOUND)
+MSG-NB-516: "Booked invoice not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-517: "Booked invoice not found: &lt;invoice no&gt;" (NOT_FOUND)
+MSG-NB-518: "Client not found: &lt;client id&gt;" (NOT_FOUND)
+MSG-NB-519: "Company not found: &lt;company id&gt;" (NOT_FOUND)
+MSG-NB-520: "Legacy account header not found: &lt;account id&gt;" (NOT_FOUND)
+MSG-NB-521: "Notification not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-522: "Proposal request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-523: "Quotation not found: &lt;id&gt;" (NOT_FOUND)
+MSG-NB-524: "Quotation not found: &lt;key&gt;" (NOT_FOUND)
+MSG-NB-525: "Quotation version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-NB-526: "Work item not found: &lt;case id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="M480" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/04_BIBS_TestPlan_BRD-01_New_Business_v2.0.xlsx
@@ -40480,7 +40480,7 @@
       </c>
       <c r="K338" s="12" t="inlineStr">
         <is>
-          <t>1. Book an account on a Motor package covered by CPC2 (seed); open the invoice and the Booked Accounts Register.</t>
+          <t>1. Book an account on a Motor package covered by CPC2; open the invoice and the Booked Accounts Register.</t>
         </is>
       </c>
       <c r="L338" s="12" t="inlineStr">
